--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127036675</v>
       </c>
       <c r="B2" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>127034383</v>
       </c>
       <c r="B3" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -889,53 +889,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127035882</v>
+        <v>127029075</v>
       </c>
       <c r="B4" t="n">
-        <v>56849</v>
+        <v>78770</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428512</v>
+        <v>428374</v>
       </c>
       <c r="R4" t="n">
-        <v>6799960</v>
+        <v>6799811</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,48 +996,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127029075</v>
+        <v>127035882</v>
       </c>
       <c r="B5" t="n">
-        <v>78739</v>
+        <v>56849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428374</v>
+        <v>428512</v>
       </c>
       <c r="R5" t="n">
-        <v>6799811</v>
+        <v>6799960</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127028820</v>
+        <v>127028288</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>79629</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>428394</v>
+        <v>428389</v>
       </c>
       <c r="R6" t="n">
-        <v>6799781</v>
+        <v>6799724</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,12 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i hela området.</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127028288</v>
+        <v>127031272</v>
       </c>
       <c r="B7" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,14 +1246,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>428389</v>
+        <v>428677</v>
       </c>
       <c r="R7" t="n">
-        <v>6799724</v>
+        <v>6799834</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1290,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127031272</v>
+        <v>127028820</v>
       </c>
       <c r="B8" t="n">
-        <v>79598</v>
+        <v>79011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,37 +1333,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>428677</v>
+        <v>428394</v>
       </c>
       <c r="R8" t="n">
-        <v>6799834</v>
+        <v>6799781</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1397,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1402,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i hela området.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,7 +1437,7 @@
         <v>127032866</v>
       </c>
       <c r="B9" t="n">
-        <v>78981</v>
+        <v>79012</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>127036174</v>
       </c>
       <c r="B10" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>127032352</v>
       </c>
       <c r="B11" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>127030417</v>
       </c>
       <c r="B12" t="n">
-        <v>78738</v>
+        <v>78769</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127033062</v>
+        <v>127029492</v>
       </c>
       <c r="B13" t="n">
-        <v>57654</v>
+        <v>79011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,39 +1873,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>428840</v>
+        <v>428422</v>
       </c>
       <c r="R13" t="n">
-        <v>6799855</v>
+        <v>6799802</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1937,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1947,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127029492</v>
+        <v>127033062</v>
       </c>
       <c r="B14" t="n">
-        <v>78980</v>
+        <v>57654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,34 +1980,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>428422</v>
+        <v>428840</v>
       </c>
       <c r="R14" t="n">
-        <v>6799802</v>
+        <v>6799855</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127028962</v>
+        <v>127033222</v>
       </c>
       <c r="B15" t="n">
-        <v>78739</v>
+        <v>78769</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,34 +2092,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>428394</v>
+        <v>428831</v>
       </c>
       <c r="R15" t="n">
-        <v>6799781</v>
+        <v>6799894</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2188,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127033222</v>
+        <v>127028962</v>
       </c>
       <c r="B16" t="n">
-        <v>78738</v>
+        <v>78770</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,34 +2199,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>428831</v>
+        <v>428394</v>
       </c>
       <c r="R16" t="n">
-        <v>6799894</v>
+        <v>6799781</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127033408</v>
+        <v>127028974</v>
       </c>
       <c r="B17" t="n">
-        <v>78980</v>
+        <v>78769</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2306,37 +2306,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>428788</v>
+        <v>428374</v>
       </c>
       <c r="R17" t="n">
-        <v>6799983</v>
+        <v>6799811</v>
       </c>
       <c r="S17" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2402,10 +2402,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127030319</v>
+        <v>127033408</v>
       </c>
       <c r="B18" t="n">
-        <v>79569</v>
+        <v>79011</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2413,37 +2413,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>428422</v>
+        <v>428788</v>
       </c>
       <c r="R18" t="n">
-        <v>6799802</v>
+        <v>6799983</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2509,10 +2509,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127028974</v>
+        <v>127030319</v>
       </c>
       <c r="B19" t="n">
-        <v>78738</v>
+        <v>79600</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,21 +2520,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>428374</v>
+        <v>428422</v>
       </c>
       <c r="R19" t="n">
-        <v>6799811</v>
+        <v>6799802</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2616,10 +2616,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127032907</v>
+        <v>127033867</v>
       </c>
       <c r="B20" t="n">
-        <v>78980</v>
+        <v>78769</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2627,21 +2627,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2651,13 +2651,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>428763</v>
+        <v>428801</v>
       </c>
       <c r="R20" t="n">
-        <v>6799813</v>
+        <v>6800075</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2723,10 +2723,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127033349</v>
+        <v>127032907</v>
       </c>
       <c r="B21" t="n">
-        <v>57654</v>
+        <v>79011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2734,39 +2734,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>428792</v>
+        <v>428763</v>
       </c>
       <c r="R21" t="n">
-        <v>6799956</v>
+        <v>6799813</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2798,7 +2793,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2808,7 +2803,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2835,53 +2830,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127028936</v>
+        <v>127035403</v>
       </c>
       <c r="B22" t="n">
-        <v>8447</v>
+        <v>79011</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>428394</v>
+        <v>428610</v>
       </c>
       <c r="R22" t="n">
-        <v>6799781</v>
+        <v>6800197</v>
       </c>
       <c r="S22" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2910,7 +2900,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2920,7 +2910,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2947,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127034314</v>
+        <v>127033349</v>
       </c>
       <c r="B23" t="n">
-        <v>78739</v>
+        <v>57654</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2958,37 +2948,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>428856</v>
+        <v>428792</v>
       </c>
       <c r="R23" t="n">
-        <v>6800220</v>
+        <v>6799956</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3017,7 +3012,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3027,7 +3022,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3054,48 +3049,53 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127033867</v>
+        <v>127028936</v>
       </c>
       <c r="B24" t="n">
-        <v>78738</v>
+        <v>8447</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>428801</v>
+        <v>428394</v>
       </c>
       <c r="R24" t="n">
-        <v>6800075</v>
+        <v>6799781</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3161,10 +3161,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127035403</v>
+        <v>127031042</v>
       </c>
       <c r="B25" t="n">
-        <v>78980</v>
+        <v>78770</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3172,21 +3172,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3196,13 +3196,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>428610</v>
+        <v>428677</v>
       </c>
       <c r="R25" t="n">
-        <v>6800197</v>
+        <v>6799834</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3268,10 +3268,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127031042</v>
+        <v>127034314</v>
       </c>
       <c r="B26" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3303,13 +3303,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>428677</v>
+        <v>428856</v>
       </c>
       <c r="R26" t="n">
-        <v>6799834</v>
+        <v>6800220</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3378,7 +3378,7 @@
         <v>127031710</v>
       </c>
       <c r="B27" t="n">
-        <v>78738</v>
+        <v>78769</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3482,10 +3482,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127028434</v>
+        <v>127034644</v>
       </c>
       <c r="B28" t="n">
-        <v>78980</v>
+        <v>91339</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3493,37 +3493,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>428388</v>
+        <v>428786</v>
       </c>
       <c r="R28" t="n">
-        <v>6799765</v>
+        <v>6800327</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3592,7 +3592,7 @@
         <v>127033497</v>
       </c>
       <c r="B29" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127034644</v>
+        <v>127028434</v>
       </c>
       <c r="B30" t="n">
-        <v>91265</v>
+        <v>79011</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3707,37 +3707,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>428786</v>
+        <v>428388</v>
       </c>
       <c r="R30" t="n">
-        <v>6800327</v>
+        <v>6799765</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3918,7 +3918,7 @@
         <v>127035723</v>
       </c>
       <c r="B32" t="n">
-        <v>91265</v>
+        <v>91339</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>127034901</v>
       </c>
       <c r="B33" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>127033824</v>
       </c>
       <c r="B34" t="n">
-        <v>78738</v>
+        <v>78769</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>127035734</v>
       </c>
       <c r="B35" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4343,10 +4343,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127034208</v>
+        <v>127030918</v>
       </c>
       <c r="B36" t="n">
-        <v>78980</v>
+        <v>78769</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4354,37 +4354,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>428809</v>
+        <v>428644</v>
       </c>
       <c r="R36" t="n">
-        <v>6800173</v>
+        <v>6799825</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4450,10 +4450,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127030918</v>
+        <v>127036021</v>
       </c>
       <c r="B37" t="n">
-        <v>78738</v>
+        <v>78769</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4485,10 +4485,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>428644</v>
+        <v>428467</v>
       </c>
       <c r="R37" t="n">
-        <v>6799825</v>
+        <v>6799920</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4557,10 +4557,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127036021</v>
+        <v>127034208</v>
       </c>
       <c r="B38" t="n">
-        <v>78738</v>
+        <v>79011</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4568,37 +4568,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>428467</v>
+        <v>428809</v>
       </c>
       <c r="R38" t="n">
-        <v>6799920</v>
+        <v>6800173</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4664,10 +4664,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127033133</v>
+        <v>127026773</v>
       </c>
       <c r="B39" t="n">
-        <v>78980</v>
+        <v>57654</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4675,37 +4675,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>428813</v>
+        <v>428345</v>
       </c>
       <c r="R39" t="n">
-        <v>6799900</v>
+        <v>6799714</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4734,7 +4739,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4744,7 +4749,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4771,10 +4776,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127026773</v>
+        <v>127033133</v>
       </c>
       <c r="B40" t="n">
-        <v>57654</v>
+        <v>79011</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4782,42 +4787,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>428345</v>
+        <v>428813</v>
       </c>
       <c r="R40" t="n">
-        <v>6799714</v>
+        <v>6799900</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4883,10 +4883,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127032439</v>
+        <v>127032393</v>
       </c>
       <c r="B41" t="n">
-        <v>78738</v>
+        <v>79011</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4894,21 +4894,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4918,10 +4918,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>428752</v>
+        <v>428755</v>
       </c>
       <c r="R41" t="n">
-        <v>6799795</v>
+        <v>6799817</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4990,10 +4990,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127032393</v>
+        <v>127032439</v>
       </c>
       <c r="B42" t="n">
-        <v>78980</v>
+        <v>78769</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5001,21 +5001,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>428755</v>
+        <v>428752</v>
       </c>
       <c r="R42" t="n">
-        <v>6799817</v>
+        <v>6799795</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5100,7 +5100,7 @@
         <v>127035229</v>
       </c>
       <c r="B43" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>127034191</v>
       </c>
       <c r="B44" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>127030347</v>
       </c>
       <c r="B45" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         <v>127033191</v>
       </c>
       <c r="B46" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5525,10 +5525,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127030990</v>
+        <v>127030905</v>
       </c>
       <c r="B47" t="n">
-        <v>78738</v>
+        <v>78770</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5536,34 +5536,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>428677</v>
+        <v>428635</v>
       </c>
       <c r="R47" t="n">
-        <v>6799834</v>
+        <v>6799822</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5632,10 +5632,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127030905</v>
+        <v>127034565</v>
       </c>
       <c r="B48" t="n">
-        <v>78739</v>
+        <v>79011</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5643,37 +5643,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>428635</v>
+        <v>428780</v>
       </c>
       <c r="R48" t="n">
-        <v>6799822</v>
+        <v>6800319</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5739,10 +5739,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127034565</v>
+        <v>127030990</v>
       </c>
       <c r="B49" t="n">
-        <v>78980</v>
+        <v>78769</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5750,21 +5750,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5774,13 +5774,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>428780</v>
+        <v>428677</v>
       </c>
       <c r="R49" t="n">
-        <v>6800319</v>
+        <v>6799834</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5846,10 +5846,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127034235</v>
+        <v>127032317</v>
       </c>
       <c r="B50" t="n">
-        <v>57654</v>
+        <v>79011</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5857,42 +5857,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>428843</v>
+        <v>428727</v>
       </c>
       <c r="R50" t="n">
-        <v>6800159</v>
+        <v>6799838</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5921,7 +5916,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5931,7 +5926,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5958,10 +5953,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127032317</v>
+        <v>127034235</v>
       </c>
       <c r="B51" t="n">
-        <v>78980</v>
+        <v>57654</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5969,37 +5964,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>428727</v>
+        <v>428843</v>
       </c>
       <c r="R51" t="n">
-        <v>6799838</v>
+        <v>6800159</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6068,7 +6068,7 @@
         <v>127027998</v>
       </c>
       <c r="B52" t="n">
-        <v>78738</v>
+        <v>78769</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6172,53 +6172,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127033713</v>
+        <v>127033102</v>
       </c>
       <c r="B53" t="n">
-        <v>8447</v>
+        <v>79011</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>428806</v>
+        <v>428821</v>
       </c>
       <c r="R53" t="n">
-        <v>6800045</v>
+        <v>6799886</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6247,7 +6242,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6257,7 +6252,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6284,10 +6279,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127035441</v>
+        <v>127034263</v>
       </c>
       <c r="B54" t="n">
-        <v>57654</v>
+        <v>79011</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6295,42 +6290,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>428586</v>
+        <v>428826</v>
       </c>
       <c r="R54" t="n">
-        <v>6800175</v>
+        <v>6800180</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6359,7 +6349,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6369,7 +6359,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Garnlav mer eller mindre över hela området.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6396,10 +6391,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127034263</v>
+        <v>127035441</v>
       </c>
       <c r="B55" t="n">
-        <v>78980</v>
+        <v>57654</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6407,37 +6402,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>428826</v>
+        <v>428586</v>
       </c>
       <c r="R55" t="n">
-        <v>6800180</v>
+        <v>6800175</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6476,12 +6476,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Garnlav mer eller mindre över hela området.</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6508,48 +6503,53 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127033102</v>
+        <v>127033713</v>
       </c>
       <c r="B56" t="n">
-        <v>78980</v>
+        <v>8447</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>428821</v>
+        <v>428806</v>
       </c>
       <c r="R56" t="n">
-        <v>6799886</v>
+        <v>6800045</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -675,48 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127036675</v>
+        <v>127035882</v>
       </c>
       <c r="B2" t="n">
-        <v>79011</v>
+        <v>56849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>428222</v>
+        <v>428512</v>
       </c>
       <c r="R2" t="n">
-        <v>6799847</v>
+        <v>6799960</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127034383</v>
+        <v>127036675</v>
       </c>
       <c r="B3" t="n">
-        <v>78770</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,37 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>428839</v>
+        <v>428222</v>
       </c>
       <c r="R3" t="n">
-        <v>6800310</v>
+        <v>6799847</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127029075</v>
+        <v>127034383</v>
       </c>
       <c r="B4" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,17 +925,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428374</v>
+        <v>428839</v>
       </c>
       <c r="R4" t="n">
-        <v>6799811</v>
+        <v>6800310</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,53 +1001,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127035882</v>
+        <v>127029075</v>
       </c>
       <c r="B5" t="n">
-        <v>56849</v>
+        <v>78773</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428512</v>
+        <v>428374</v>
       </c>
       <c r="R5" t="n">
-        <v>6799960</v>
+        <v>6799811</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127028288</v>
+        <v>127028820</v>
       </c>
       <c r="B6" t="n">
-        <v>79629</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>428389</v>
+        <v>428394</v>
       </c>
       <c r="R6" t="n">
-        <v>6799724</v>
+        <v>6799781</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i hela området.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127031272</v>
+        <v>127028288</v>
       </c>
       <c r="B7" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,14 +1251,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>428677</v>
+        <v>428389</v>
       </c>
       <c r="R7" t="n">
-        <v>6799834</v>
+        <v>6799724</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1285,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127028820</v>
+        <v>127031272</v>
       </c>
       <c r="B8" t="n">
-        <v>79011</v>
+        <v>79632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,37 +1338,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>428394</v>
+        <v>428677</v>
       </c>
       <c r="R8" t="n">
-        <v>6799781</v>
+        <v>6799834</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1392,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1402,12 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i hela området.</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,7 +1437,7 @@
         <v>127032866</v>
       </c>
       <c r="B9" t="n">
-        <v>79012</v>
+        <v>79015</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>127036174</v>
       </c>
       <c r="B10" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>127032352</v>
       </c>
       <c r="B11" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>127030417</v>
       </c>
       <c r="B12" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127029492</v>
+        <v>127033062</v>
       </c>
       <c r="B13" t="n">
-        <v>79011</v>
+        <v>57654</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,34 +1873,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>428422</v>
+        <v>428840</v>
       </c>
       <c r="R13" t="n">
-        <v>6799802</v>
+        <v>6799855</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1932,7 +1937,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1947,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127033062</v>
+        <v>127033222</v>
       </c>
       <c r="B14" t="n">
-        <v>57654</v>
+        <v>78772</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,42 +1985,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>428840</v>
+        <v>428831</v>
       </c>
       <c r="R14" t="n">
-        <v>6799855</v>
+        <v>6799894</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127033222</v>
+        <v>127029492</v>
       </c>
       <c r="B15" t="n">
-        <v>78769</v>
+        <v>79014</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,37 +2092,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>428831</v>
+        <v>428422</v>
       </c>
       <c r="R15" t="n">
-        <v>6799894</v>
+        <v>6799802</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2191,7 +2191,7 @@
         <v>127028962</v>
       </c>
       <c r="B16" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2295,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127028974</v>
+        <v>127030319</v>
       </c>
       <c r="B17" t="n">
-        <v>78769</v>
+        <v>79603</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2306,21 +2306,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2330,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>428374</v>
+        <v>428422</v>
       </c>
       <c r="R17" t="n">
-        <v>6799811</v>
+        <v>6799802</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2402,10 +2402,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127033408</v>
+        <v>127028974</v>
       </c>
       <c r="B18" t="n">
-        <v>79011</v>
+        <v>78772</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2413,37 +2413,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>428788</v>
+        <v>428374</v>
       </c>
       <c r="R18" t="n">
-        <v>6799983</v>
+        <v>6799811</v>
       </c>
       <c r="S18" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2509,10 +2509,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127030319</v>
+        <v>127033408</v>
       </c>
       <c r="B19" t="n">
-        <v>79600</v>
+        <v>79014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,37 +2520,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>428422</v>
+        <v>428788</v>
       </c>
       <c r="R19" t="n">
-        <v>6799802</v>
+        <v>6799983</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2619,7 +2619,7 @@
         <v>127033867</v>
       </c>
       <c r="B20" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>127032907</v>
       </c>
       <c r="B21" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>127035403</v>
       </c>
       <c r="B22" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3161,10 +3161,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127031042</v>
+        <v>127034314</v>
       </c>
       <c r="B25" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3196,13 +3196,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>428677</v>
+        <v>428856</v>
       </c>
       <c r="R25" t="n">
-        <v>6799834</v>
+        <v>6800220</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3268,10 +3268,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127034314</v>
+        <v>127031042</v>
       </c>
       <c r="B26" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3303,13 +3303,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>428856</v>
+        <v>428677</v>
       </c>
       <c r="R26" t="n">
-        <v>6800220</v>
+        <v>6799834</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3378,7 +3378,7 @@
         <v>127031710</v>
       </c>
       <c r="B27" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3482,10 +3482,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127034644</v>
+        <v>127033497</v>
       </c>
       <c r="B28" t="n">
-        <v>91339</v>
+        <v>79014</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3493,21 +3493,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>428786</v>
+        <v>428803</v>
       </c>
       <c r="R28" t="n">
-        <v>6800327</v>
+        <v>6799992</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3589,10 +3589,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127033497</v>
+        <v>127028434</v>
       </c>
       <c r="B29" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3620,17 +3620,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>428803</v>
+        <v>428388</v>
       </c>
       <c r="R29" t="n">
-        <v>6799992</v>
+        <v>6799765</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3696,10 +3696,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127028434</v>
+        <v>127034644</v>
       </c>
       <c r="B30" t="n">
-        <v>79011</v>
+        <v>91345</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3707,37 +3707,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>428388</v>
+        <v>428786</v>
       </c>
       <c r="R30" t="n">
-        <v>6799765</v>
+        <v>6800327</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3918,7 +3918,7 @@
         <v>127035723</v>
       </c>
       <c r="B32" t="n">
-        <v>91339</v>
+        <v>91345</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>127034901</v>
       </c>
       <c r="B33" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4129,10 +4129,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127033824</v>
+        <v>127035734</v>
       </c>
       <c r="B34" t="n">
-        <v>78769</v>
+        <v>79014</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4140,34 +4140,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>428807</v>
+        <v>428511</v>
       </c>
       <c r="R34" t="n">
-        <v>6800084</v>
+        <v>6799990</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4236,10 +4236,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127035734</v>
+        <v>127033824</v>
       </c>
       <c r="B35" t="n">
-        <v>79011</v>
+        <v>78772</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4247,34 +4247,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>428511</v>
+        <v>428807</v>
       </c>
       <c r="R35" t="n">
-        <v>6799990</v>
+        <v>6800084</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4346,7 +4346,7 @@
         <v>127030918</v>
       </c>
       <c r="B36" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>127036021</v>
       </c>
       <c r="B37" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>127034208</v>
       </c>
       <c r="B38" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4664,10 +4664,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127026773</v>
+        <v>127033133</v>
       </c>
       <c r="B39" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4675,42 +4675,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>428345</v>
+        <v>428813</v>
       </c>
       <c r="R39" t="n">
-        <v>6799714</v>
+        <v>6799900</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4739,7 +4734,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4749,7 +4744,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4776,10 +4771,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127033133</v>
+        <v>127026773</v>
       </c>
       <c r="B40" t="n">
-        <v>79011</v>
+        <v>57654</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4787,37 +4782,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>428813</v>
+        <v>428345</v>
       </c>
       <c r="R40" t="n">
-        <v>6799900</v>
+        <v>6799714</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4886,7 +4886,7 @@
         <v>127032393</v>
       </c>
       <c r="B41" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>127032439</v>
       </c>
       <c r="B42" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5097,10 +5097,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127035229</v>
+        <v>127033191</v>
       </c>
       <c r="B43" t="n">
-        <v>79011</v>
+        <v>78773</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5108,21 +5108,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5132,10 +5132,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>428628</v>
+        <v>428831</v>
       </c>
       <c r="R43" t="n">
-        <v>6800237</v>
+        <v>6799894</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5204,10 +5204,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127034191</v>
+        <v>127030347</v>
       </c>
       <c r="B44" t="n">
-        <v>79011</v>
+        <v>78773</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5215,37 +5215,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>428821</v>
+        <v>428422</v>
       </c>
       <c r="R44" t="n">
-        <v>6800164</v>
+        <v>6799802</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5311,10 +5311,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127030347</v>
+        <v>127035229</v>
       </c>
       <c r="B45" t="n">
-        <v>78770</v>
+        <v>79014</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5322,34 +5322,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>428422</v>
+        <v>428628</v>
       </c>
       <c r="R45" t="n">
-        <v>6799802</v>
+        <v>6800237</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5418,10 +5418,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127033191</v>
+        <v>127034191</v>
       </c>
       <c r="B46" t="n">
-        <v>78770</v>
+        <v>79014</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5429,21 +5429,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5453,13 +5453,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>428831</v>
+        <v>428821</v>
       </c>
       <c r="R46" t="n">
-        <v>6799894</v>
+        <v>6800164</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5525,10 +5525,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127030905</v>
+        <v>127034565</v>
       </c>
       <c r="B47" t="n">
-        <v>78770</v>
+        <v>79014</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5536,37 +5536,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>428635</v>
+        <v>428780</v>
       </c>
       <c r="R47" t="n">
-        <v>6799822</v>
+        <v>6800319</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5632,10 +5632,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127034565</v>
+        <v>127030990</v>
       </c>
       <c r="B48" t="n">
-        <v>79011</v>
+        <v>78772</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5643,21 +5643,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5667,13 +5667,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>428780</v>
+        <v>428677</v>
       </c>
       <c r="R48" t="n">
-        <v>6800319</v>
+        <v>6799834</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5739,10 +5739,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127030990</v>
+        <v>127030905</v>
       </c>
       <c r="B49" t="n">
-        <v>78769</v>
+        <v>78773</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5750,34 +5750,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>428677</v>
+        <v>428635</v>
       </c>
       <c r="R49" t="n">
-        <v>6799834</v>
+        <v>6799822</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5849,7 +5849,7 @@
         <v>127032317</v>
       </c>
       <c r="B50" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>127027998</v>
       </c>
       <c r="B52" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6172,48 +6172,53 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127033102</v>
+        <v>127033713</v>
       </c>
       <c r="B53" t="n">
-        <v>79011</v>
+        <v>8447</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>428821</v>
+        <v>428806</v>
       </c>
       <c r="R53" t="n">
-        <v>6799886</v>
+        <v>6800045</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6242,7 +6247,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6252,7 +6257,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6279,10 +6284,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127034263</v>
+        <v>127033102</v>
       </c>
       <c r="B54" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6314,10 +6319,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>428826</v>
+        <v>428821</v>
       </c>
       <c r="R54" t="n">
-        <v>6800180</v>
+        <v>6799886</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6349,7 +6354,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6359,12 +6364,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Garnlav mer eller mindre över hela området.</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6391,10 +6391,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127035441</v>
+        <v>127034263</v>
       </c>
       <c r="B55" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6402,42 +6402,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>428586</v>
+        <v>428826</v>
       </c>
       <c r="R55" t="n">
-        <v>6800175</v>
+        <v>6800180</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6466,7 +6461,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6476,7 +6471,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Garnlav mer eller mindre över hela området.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6503,38 +6503,38 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127033713</v>
+        <v>127035441</v>
       </c>
       <c r="B56" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6543,10 +6543,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>428806</v>
+        <v>428586</v>
       </c>
       <c r="R56" t="n">
-        <v>6800045</v>
+        <v>6800175</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127036675</v>
+        <v>127034383</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,37 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>428222</v>
+        <v>428839</v>
       </c>
       <c r="R3" t="n">
-        <v>6799847</v>
+        <v>6800310</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,7 +894,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127034383</v>
+        <v>127029075</v>
       </c>
       <c r="B4" t="n">
         <v>78773</v>
@@ -925,17 +925,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428839</v>
+        <v>428374</v>
       </c>
       <c r="R4" t="n">
-        <v>6800310</v>
+        <v>6799811</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127029075</v>
+        <v>127036675</v>
       </c>
       <c r="B5" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428374</v>
+        <v>428222</v>
       </c>
       <c r="R5" t="n">
-        <v>6799811</v>
+        <v>6799847</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127028820</v>
+        <v>127032866</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>79015</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,16 +1119,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1139,17 +1139,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>428394</v>
+        <v>428752</v>
       </c>
       <c r="R6" t="n">
-        <v>6799781</v>
+        <v>6799795</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,12 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i hela området.</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1327,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127031272</v>
+        <v>127028820</v>
       </c>
       <c r="B8" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,37 +1333,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>428677</v>
+        <v>428394</v>
       </c>
       <c r="R8" t="n">
-        <v>6799834</v>
+        <v>6799781</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1397,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1402,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i hela området.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127032866</v>
+        <v>127031272</v>
       </c>
       <c r="B9" t="n">
-        <v>79015</v>
+        <v>79632</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,21 +1445,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>230405</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,13 +1469,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>428752</v>
+        <v>428677</v>
       </c>
       <c r="R9" t="n">
-        <v>6799795</v>
+        <v>6799834</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1862,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127033062</v>
+        <v>127033222</v>
       </c>
       <c r="B13" t="n">
-        <v>57654</v>
+        <v>78772</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,42 +1873,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>428840</v>
+        <v>428831</v>
       </c>
       <c r="R13" t="n">
-        <v>6799855</v>
+        <v>6799894</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1937,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1947,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127033222</v>
+        <v>127029492</v>
       </c>
       <c r="B14" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,37 +1980,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>428831</v>
+        <v>428422</v>
       </c>
       <c r="R14" t="n">
-        <v>6799894</v>
+        <v>6799802</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2044,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,7 +2049,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127029492</v>
+        <v>127033062</v>
       </c>
       <c r="B15" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,34 +2087,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>428422</v>
+        <v>428840</v>
       </c>
       <c r="R15" t="n">
-        <v>6799802</v>
+        <v>6799855</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2402,10 +2402,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127028974</v>
+        <v>127033408</v>
       </c>
       <c r="B18" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2413,37 +2413,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>428374</v>
+        <v>428788</v>
       </c>
       <c r="R18" t="n">
-        <v>6799811</v>
+        <v>6799983</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2509,10 +2509,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127033408</v>
+        <v>127028974</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,37 +2520,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>428788</v>
+        <v>428374</v>
       </c>
       <c r="R19" t="n">
-        <v>6799983</v>
+        <v>6799811</v>
       </c>
       <c r="S19" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3482,7 +3482,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127033497</v>
+        <v>127028434</v>
       </c>
       <c r="B28" t="n">
         <v>79014</v>
@@ -3513,17 +3513,17 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>428803</v>
+        <v>428388</v>
       </c>
       <c r="R28" t="n">
-        <v>6799992</v>
+        <v>6799765</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3589,10 +3589,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127028434</v>
+        <v>127034644</v>
       </c>
       <c r="B29" t="n">
-        <v>79014</v>
+        <v>91345</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3600,37 +3600,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>428388</v>
+        <v>428786</v>
       </c>
       <c r="R29" t="n">
-        <v>6799765</v>
+        <v>6800327</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3696,10 +3696,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127034644</v>
+        <v>127033497</v>
       </c>
       <c r="B30" t="n">
-        <v>91345</v>
+        <v>79014</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>428786</v>
+        <v>428803</v>
       </c>
       <c r="R30" t="n">
-        <v>6800327</v>
+        <v>6799992</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3803,10 +3803,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127030793</v>
+        <v>127035723</v>
       </c>
       <c r="B31" t="n">
-        <v>56840</v>
+        <v>91345</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3814,42 +3814,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102612</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>428603</v>
+        <v>428586</v>
       </c>
       <c r="R31" t="n">
-        <v>6799810</v>
+        <v>6800175</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3878,7 +3873,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3888,7 +3883,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3915,10 +3910,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127035723</v>
+        <v>127030793</v>
       </c>
       <c r="B32" t="n">
-        <v>91345</v>
+        <v>56840</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3926,37 +3921,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>102612</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>428586</v>
+        <v>428603</v>
       </c>
       <c r="R32" t="n">
-        <v>6800175</v>
+        <v>6799810</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4129,10 +4129,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127035734</v>
+        <v>127033824</v>
       </c>
       <c r="B34" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4140,34 +4140,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>428511</v>
+        <v>428807</v>
       </c>
       <c r="R34" t="n">
-        <v>6799990</v>
+        <v>6800084</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4236,10 +4236,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127033824</v>
+        <v>127035734</v>
       </c>
       <c r="B35" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4247,34 +4247,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>428807</v>
+        <v>428511</v>
       </c>
       <c r="R35" t="n">
-        <v>6800084</v>
+        <v>6799990</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4450,10 +4450,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127036021</v>
+        <v>127034208</v>
       </c>
       <c r="B37" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4461,37 +4461,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>428467</v>
+        <v>428809</v>
       </c>
       <c r="R37" t="n">
-        <v>6799920</v>
+        <v>6800173</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4557,10 +4557,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127034208</v>
+        <v>127036021</v>
       </c>
       <c r="B38" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4568,37 +4568,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>428809</v>
+        <v>428467</v>
       </c>
       <c r="R38" t="n">
-        <v>6800173</v>
+        <v>6799920</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4883,10 +4883,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127032393</v>
+        <v>127032439</v>
       </c>
       <c r="B41" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4894,21 +4894,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4918,10 +4918,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>428755</v>
+        <v>428752</v>
       </c>
       <c r="R41" t="n">
-        <v>6799817</v>
+        <v>6799795</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4990,10 +4990,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127032439</v>
+        <v>127032393</v>
       </c>
       <c r="B42" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5001,21 +5001,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>428752</v>
+        <v>428755</v>
       </c>
       <c r="R42" t="n">
-        <v>6799795</v>
+        <v>6799817</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5097,10 +5097,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127033191</v>
+        <v>127035229</v>
       </c>
       <c r="B43" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5108,21 +5108,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5132,10 +5132,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>428831</v>
+        <v>428628</v>
       </c>
       <c r="R43" t="n">
-        <v>6799894</v>
+        <v>6800237</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5204,10 +5204,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127030347</v>
+        <v>127034191</v>
       </c>
       <c r="B44" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5215,37 +5215,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>428422</v>
+        <v>428821</v>
       </c>
       <c r="R44" t="n">
-        <v>6799802</v>
+        <v>6800164</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5311,10 +5311,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127035229</v>
+        <v>127033191</v>
       </c>
       <c r="B45" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5322,21 +5322,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>428628</v>
+        <v>428831</v>
       </c>
       <c r="R45" t="n">
-        <v>6800237</v>
+        <v>6799894</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5418,10 +5418,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127034191</v>
+        <v>127030347</v>
       </c>
       <c r="B46" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5429,37 +5429,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>428821</v>
+        <v>428422</v>
       </c>
       <c r="R46" t="n">
-        <v>6800164</v>
+        <v>6799802</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5525,10 +5525,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127034565</v>
+        <v>127030905</v>
       </c>
       <c r="B47" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5536,37 +5536,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>428780</v>
+        <v>428635</v>
       </c>
       <c r="R47" t="n">
-        <v>6800319</v>
+        <v>6799822</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5632,10 +5632,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127030990</v>
+        <v>127034565</v>
       </c>
       <c r="B48" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5643,21 +5643,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5667,13 +5667,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>428677</v>
+        <v>428780</v>
       </c>
       <c r="R48" t="n">
-        <v>6799834</v>
+        <v>6800319</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5739,10 +5739,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127030905</v>
+        <v>127030990</v>
       </c>
       <c r="B49" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5750,34 +5750,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>428635</v>
+        <v>428677</v>
       </c>
       <c r="R49" t="n">
-        <v>6799822</v>
+        <v>6799834</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6172,38 +6172,38 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127033713</v>
+        <v>127035441</v>
       </c>
       <c r="B53" t="n">
-        <v>8447</v>
+        <v>57654</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6212,10 +6212,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>428806</v>
+        <v>428586</v>
       </c>
       <c r="R53" t="n">
-        <v>6800045</v>
+        <v>6800175</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6284,48 +6284,53 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127033102</v>
+        <v>127033713</v>
       </c>
       <c r="B54" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>428821</v>
+        <v>428806</v>
       </c>
       <c r="R54" t="n">
-        <v>6799886</v>
+        <v>6800045</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6354,7 +6359,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6364,7 +6369,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6503,10 +6508,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127035441</v>
+        <v>127033102</v>
       </c>
       <c r="B56" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6514,42 +6519,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>428586</v>
+        <v>428821</v>
       </c>
       <c r="R56" t="n">
-        <v>6800175</v>
+        <v>6799886</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -2616,48 +2616,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127033867</v>
+        <v>127028936</v>
       </c>
       <c r="B20" t="n">
-        <v>78772</v>
+        <v>8447</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>428801</v>
+        <v>428394</v>
       </c>
       <c r="R20" t="n">
-        <v>6800075</v>
+        <v>6799781</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2686,7 +2691,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2696,7 +2701,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2723,10 +2728,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127032907</v>
+        <v>127034314</v>
       </c>
       <c r="B21" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2734,21 +2739,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2758,13 +2763,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>428763</v>
+        <v>428856</v>
       </c>
       <c r="R21" t="n">
-        <v>6799813</v>
+        <v>6800220</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2793,7 +2798,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2803,7 +2808,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2830,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127035403</v>
+        <v>127031042</v>
       </c>
       <c r="B22" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2841,21 +2846,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2865,13 +2870,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>428610</v>
+        <v>428677</v>
       </c>
       <c r="R22" t="n">
-        <v>6800197</v>
+        <v>6799834</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2900,7 +2905,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2910,7 +2915,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2937,10 +2942,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127033349</v>
+        <v>127033867</v>
       </c>
       <c r="B23" t="n">
-        <v>57654</v>
+        <v>78772</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2948,42 +2953,37 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>428792</v>
+        <v>428801</v>
       </c>
       <c r="R23" t="n">
-        <v>6799956</v>
+        <v>6800075</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3049,53 +3049,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127028936</v>
+        <v>127032907</v>
       </c>
       <c r="B24" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>428394</v>
+        <v>428763</v>
       </c>
       <c r="R24" t="n">
-        <v>6799781</v>
+        <v>6799813</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3124,7 +3119,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3134,7 +3129,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3161,10 +3156,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127034314</v>
+        <v>127035403</v>
       </c>
       <c r="B25" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3172,21 +3167,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3196,13 +3191,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>428856</v>
+        <v>428610</v>
       </c>
       <c r="R25" t="n">
-        <v>6800220</v>
+        <v>6800197</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3231,7 +3226,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3241,7 +3236,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3268,10 +3263,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127031042</v>
+        <v>127033349</v>
       </c>
       <c r="B26" t="n">
-        <v>78773</v>
+        <v>57654</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3279,37 +3274,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>428677</v>
+        <v>428792</v>
       </c>
       <c r="R26" t="n">
-        <v>6799834</v>
+        <v>6799956</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -4664,10 +4664,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127033133</v>
+        <v>127026773</v>
       </c>
       <c r="B39" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4675,37 +4675,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>428813</v>
+        <v>428345</v>
       </c>
       <c r="R39" t="n">
-        <v>6799900</v>
+        <v>6799714</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4734,7 +4739,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4744,7 +4749,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4771,10 +4776,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127026773</v>
+        <v>127033133</v>
       </c>
       <c r="B40" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4782,42 +4787,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>428345</v>
+        <v>428813</v>
       </c>
       <c r="R40" t="n">
-        <v>6799714</v>
+        <v>6799900</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5846,10 +5846,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127032317</v>
+        <v>127034235</v>
       </c>
       <c r="B50" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5857,37 +5857,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>428727</v>
+        <v>428843</v>
       </c>
       <c r="R50" t="n">
-        <v>6799838</v>
+        <v>6800159</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5916,7 +5921,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5926,7 +5931,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5953,10 +5958,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127034235</v>
+        <v>127032317</v>
       </c>
       <c r="B51" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5964,42 +5969,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>428843</v>
+        <v>428727</v>
       </c>
       <c r="R51" t="n">
-        <v>6800159</v>
+        <v>6799838</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127034383</v>
+        <v>127036675</v>
       </c>
       <c r="B3" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,37 +798,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>428839</v>
+        <v>428222</v>
       </c>
       <c r="R3" t="n">
-        <v>6800310</v>
+        <v>6799847</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,7 +894,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127029075</v>
+        <v>127034383</v>
       </c>
       <c r="B4" t="n">
         <v>78773</v>
@@ -925,17 +925,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428374</v>
+        <v>428839</v>
       </c>
       <c r="R4" t="n">
-        <v>6799811</v>
+        <v>6800310</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127036675</v>
+        <v>127029075</v>
       </c>
       <c r="B5" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,21 +1012,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428222</v>
+        <v>428374</v>
       </c>
       <c r="R5" t="n">
-        <v>6799847</v>
+        <v>6799811</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127032866</v>
+        <v>127028820</v>
       </c>
       <c r="B6" t="n">
-        <v>79015</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,16 +1119,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1139,17 +1139,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>428752</v>
+        <v>428394</v>
       </c>
       <c r="R6" t="n">
-        <v>6799795</v>
+        <v>6799781</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i hela området.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1322,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127028820</v>
+        <v>127031272</v>
       </c>
       <c r="B8" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,37 +1338,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>428394</v>
+        <v>428677</v>
       </c>
       <c r="R8" t="n">
-        <v>6799781</v>
+        <v>6799834</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1392,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1402,12 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i hela området.</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127031272</v>
+        <v>127032866</v>
       </c>
       <c r="B9" t="n">
-        <v>79632</v>
+        <v>79015</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,21 +1445,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>230405</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,13 +1469,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>428677</v>
+        <v>428752</v>
       </c>
       <c r="R9" t="n">
-        <v>6799834</v>
+        <v>6799795</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1862,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127033222</v>
+        <v>127033062</v>
       </c>
       <c r="B13" t="n">
-        <v>78772</v>
+        <v>57654</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,37 +1873,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>428831</v>
+        <v>428840</v>
       </c>
       <c r="R13" t="n">
-        <v>6799894</v>
+        <v>6799855</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1932,7 +1937,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1947,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2076,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127033062</v>
+        <v>127033222</v>
       </c>
       <c r="B15" t="n">
-        <v>57654</v>
+        <v>78772</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2087,42 +2092,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>428840</v>
+        <v>428831</v>
       </c>
       <c r="R15" t="n">
-        <v>6799855</v>
+        <v>6799894</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2616,53 +2616,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127028936</v>
+        <v>127032907</v>
       </c>
       <c r="B20" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>428394</v>
+        <v>428763</v>
       </c>
       <c r="R20" t="n">
-        <v>6799781</v>
+        <v>6799813</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2691,7 +2686,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2701,7 +2696,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2728,10 +2723,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127034314</v>
+        <v>127035403</v>
       </c>
       <c r="B21" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2739,21 +2734,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2763,13 +2758,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>428856</v>
+        <v>428610</v>
       </c>
       <c r="R21" t="n">
-        <v>6800220</v>
+        <v>6800197</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2798,7 +2793,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2808,7 +2803,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2835,10 +2830,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127031042</v>
+        <v>127033867</v>
       </c>
       <c r="B22" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2846,21 +2841,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2870,10 +2865,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>428677</v>
+        <v>428801</v>
       </c>
       <c r="R22" t="n">
-        <v>6799834</v>
+        <v>6800075</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2905,7 +2900,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2915,7 +2910,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2942,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127033867</v>
+        <v>127033349</v>
       </c>
       <c r="B23" t="n">
-        <v>78772</v>
+        <v>57654</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2953,37 +2948,42 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>428801</v>
+        <v>428792</v>
       </c>
       <c r="R23" t="n">
-        <v>6800075</v>
+        <v>6799956</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3049,48 +3049,53 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127032907</v>
+        <v>127028936</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>8447</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>428763</v>
+        <v>428394</v>
       </c>
       <c r="R24" t="n">
-        <v>6799813</v>
+        <v>6799781</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3119,7 +3124,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3129,7 +3134,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3156,10 +3161,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127035403</v>
+        <v>127034314</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3167,21 +3172,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3191,13 +3196,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>428610</v>
+        <v>428856</v>
       </c>
       <c r="R25" t="n">
-        <v>6800197</v>
+        <v>6800220</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3226,7 +3231,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3236,7 +3241,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3263,10 +3268,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127033349</v>
+        <v>127031042</v>
       </c>
       <c r="B26" t="n">
-        <v>57654</v>
+        <v>78773</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3274,42 +3279,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>428792</v>
+        <v>428677</v>
       </c>
       <c r="R26" t="n">
-        <v>6799956</v>
+        <v>6799834</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3482,10 +3482,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127028434</v>
+        <v>127034644</v>
       </c>
       <c r="B28" t="n">
-        <v>79014</v>
+        <v>91346</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3493,37 +3493,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>428388</v>
+        <v>428786</v>
       </c>
       <c r="R28" t="n">
-        <v>6799765</v>
+        <v>6800327</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3589,10 +3589,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127034644</v>
+        <v>127033497</v>
       </c>
       <c r="B29" t="n">
-        <v>91345</v>
+        <v>79014</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3600,21 +3600,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3624,10 +3624,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>428786</v>
+        <v>428803</v>
       </c>
       <c r="R29" t="n">
-        <v>6800327</v>
+        <v>6799992</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3696,7 +3696,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127033497</v>
+        <v>127028434</v>
       </c>
       <c r="B30" t="n">
         <v>79014</v>
@@ -3727,17 +3727,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>428803</v>
+        <v>428388</v>
       </c>
       <c r="R30" t="n">
-        <v>6799992</v>
+        <v>6799765</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3803,10 +3803,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127035723</v>
+        <v>127030793</v>
       </c>
       <c r="B31" t="n">
-        <v>91345</v>
+        <v>56840</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3814,37 +3814,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>102612</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>428586</v>
+        <v>428603</v>
       </c>
       <c r="R31" t="n">
-        <v>6800175</v>
+        <v>6799810</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3873,7 +3878,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3883,7 +3888,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3910,10 +3915,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127030793</v>
+        <v>127035723</v>
       </c>
       <c r="B32" t="n">
-        <v>56840</v>
+        <v>91346</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3921,42 +3926,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102612</v>
+        <v>5442</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>428603</v>
+        <v>428586</v>
       </c>
       <c r="R32" t="n">
-        <v>6799810</v>
+        <v>6800175</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4450,10 +4450,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127034208</v>
+        <v>127036021</v>
       </c>
       <c r="B37" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4461,37 +4461,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>428809</v>
+        <v>428467</v>
       </c>
       <c r="R37" t="n">
-        <v>6800173</v>
+        <v>6799920</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4557,10 +4557,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127036021</v>
+        <v>127034208</v>
       </c>
       <c r="B38" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4568,37 +4568,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>428467</v>
+        <v>428809</v>
       </c>
       <c r="R38" t="n">
-        <v>6799920</v>
+        <v>6800173</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4664,10 +4664,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127026773</v>
+        <v>127033133</v>
       </c>
       <c r="B39" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4675,42 +4675,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>428345</v>
+        <v>428813</v>
       </c>
       <c r="R39" t="n">
-        <v>6799714</v>
+        <v>6799900</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4739,7 +4734,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4749,7 +4744,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4776,10 +4771,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127033133</v>
+        <v>127026773</v>
       </c>
       <c r="B40" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4787,37 +4782,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>428813</v>
+        <v>428345</v>
       </c>
       <c r="R40" t="n">
-        <v>6799900</v>
+        <v>6799714</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5097,10 +5097,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127035229</v>
+        <v>127033191</v>
       </c>
       <c r="B43" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5108,21 +5108,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5132,10 +5132,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>428628</v>
+        <v>428831</v>
       </c>
       <c r="R43" t="n">
-        <v>6800237</v>
+        <v>6799894</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5204,10 +5204,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127034191</v>
+        <v>127030347</v>
       </c>
       <c r="B44" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5215,37 +5215,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>428821</v>
+        <v>428422</v>
       </c>
       <c r="R44" t="n">
-        <v>6800164</v>
+        <v>6799802</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5311,10 +5311,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127033191</v>
+        <v>127035229</v>
       </c>
       <c r="B45" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5322,21 +5322,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>428831</v>
+        <v>428628</v>
       </c>
       <c r="R45" t="n">
-        <v>6799894</v>
+        <v>6800237</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5418,10 +5418,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127030347</v>
+        <v>127034191</v>
       </c>
       <c r="B46" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5429,37 +5429,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>428422</v>
+        <v>428821</v>
       </c>
       <c r="R46" t="n">
-        <v>6799802</v>
+        <v>6800164</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5525,10 +5525,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127030905</v>
+        <v>127034565</v>
       </c>
       <c r="B47" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5536,37 +5536,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>428635</v>
+        <v>428780</v>
       </c>
       <c r="R47" t="n">
-        <v>6799822</v>
+        <v>6800319</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5632,10 +5632,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127034565</v>
+        <v>127030905</v>
       </c>
       <c r="B48" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5643,37 +5643,37 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>428780</v>
+        <v>428635</v>
       </c>
       <c r="R48" t="n">
-        <v>6800319</v>
+        <v>6799822</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5846,10 +5846,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127034235</v>
+        <v>127032317</v>
       </c>
       <c r="B50" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5857,42 +5857,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>428843</v>
+        <v>428727</v>
       </c>
       <c r="R50" t="n">
-        <v>6800159</v>
+        <v>6799838</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5921,7 +5916,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5931,7 +5926,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5958,10 +5953,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127032317</v>
+        <v>127034235</v>
       </c>
       <c r="B51" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5969,37 +5964,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>428727</v>
+        <v>428843</v>
       </c>
       <c r="R51" t="n">
-        <v>6799838</v>
+        <v>6800159</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6172,38 +6172,38 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127035441</v>
+        <v>127033713</v>
       </c>
       <c r="B53" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6212,10 +6212,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>428586</v>
+        <v>428806</v>
       </c>
       <c r="R53" t="n">
-        <v>6800175</v>
+        <v>6800045</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6284,53 +6284,48 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127033713</v>
+        <v>127033102</v>
       </c>
       <c r="B54" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>428806</v>
+        <v>428821</v>
       </c>
       <c r="R54" t="n">
-        <v>6800045</v>
+        <v>6799886</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6359,7 +6354,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6369,7 +6364,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6508,10 +6503,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127033102</v>
+        <v>127035441</v>
       </c>
       <c r="B56" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6519,37 +6514,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>428821</v>
+        <v>428586</v>
       </c>
       <c r="R56" t="n">
-        <v>6799886</v>
+        <v>6800175</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -2295,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127030319</v>
+        <v>127033408</v>
       </c>
       <c r="B17" t="n">
-        <v>79603</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2306,37 +2306,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>428422</v>
+        <v>428788</v>
       </c>
       <c r="R17" t="n">
-        <v>6799802</v>
+        <v>6799983</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2402,10 +2402,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127033408</v>
+        <v>127028974</v>
       </c>
       <c r="B18" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2413,37 +2413,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>428788</v>
+        <v>428374</v>
       </c>
       <c r="R18" t="n">
-        <v>6799983</v>
+        <v>6799811</v>
       </c>
       <c r="S18" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2509,10 +2509,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127028974</v>
+        <v>127030319</v>
       </c>
       <c r="B19" t="n">
-        <v>78772</v>
+        <v>79603</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,21 +2520,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>428374</v>
+        <v>428422</v>
       </c>
       <c r="R19" t="n">
-        <v>6799811</v>
+        <v>6799802</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -4129,10 +4129,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127033824</v>
+        <v>127035734</v>
       </c>
       <c r="B34" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4140,34 +4140,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>428807</v>
+        <v>428511</v>
       </c>
       <c r="R34" t="n">
-        <v>6800084</v>
+        <v>6799990</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4236,10 +4236,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127035734</v>
+        <v>127033824</v>
       </c>
       <c r="B35" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4247,34 +4247,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>428511</v>
+        <v>428807</v>
       </c>
       <c r="R35" t="n">
-        <v>6799990</v>
+        <v>6800084</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4343,10 +4343,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127030918</v>
+        <v>127034208</v>
       </c>
       <c r="B36" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4354,37 +4354,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>428644</v>
+        <v>428809</v>
       </c>
       <c r="R36" t="n">
-        <v>6799825</v>
+        <v>6800173</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4450,7 +4450,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127036021</v>
+        <v>127030918</v>
       </c>
       <c r="B37" t="n">
         <v>78772</v>
@@ -4485,10 +4485,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>428467</v>
+        <v>428644</v>
       </c>
       <c r="R37" t="n">
-        <v>6799920</v>
+        <v>6799825</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4557,10 +4557,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127034208</v>
+        <v>127036021</v>
       </c>
       <c r="B38" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4568,37 +4568,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>428809</v>
+        <v>428467</v>
       </c>
       <c r="R38" t="n">
-        <v>6800173</v>
+        <v>6799920</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4883,10 +4883,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127032439</v>
+        <v>127032393</v>
       </c>
       <c r="B41" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4894,21 +4894,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4918,10 +4918,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>428752</v>
+        <v>428755</v>
       </c>
       <c r="R41" t="n">
-        <v>6799795</v>
+        <v>6799817</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4990,10 +4990,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127032393</v>
+        <v>127032439</v>
       </c>
       <c r="B42" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5001,21 +5001,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>428755</v>
+        <v>428752</v>
       </c>
       <c r="R42" t="n">
-        <v>6799817</v>
+        <v>6799795</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5097,10 +5097,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127033191</v>
+        <v>127035229</v>
       </c>
       <c r="B43" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5108,21 +5108,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5132,10 +5132,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>428831</v>
+        <v>428628</v>
       </c>
       <c r="R43" t="n">
-        <v>6799894</v>
+        <v>6800237</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5204,10 +5204,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127030347</v>
+        <v>127034191</v>
       </c>
       <c r="B44" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5215,37 +5215,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>428422</v>
+        <v>428821</v>
       </c>
       <c r="R44" t="n">
-        <v>6799802</v>
+        <v>6800164</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5311,10 +5311,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127035229</v>
+        <v>127033191</v>
       </c>
       <c r="B45" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5322,21 +5322,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>428628</v>
+        <v>428831</v>
       </c>
       <c r="R45" t="n">
-        <v>6800237</v>
+        <v>6799894</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5418,10 +5418,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127034191</v>
+        <v>127030347</v>
       </c>
       <c r="B46" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5429,37 +5429,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>428821</v>
+        <v>428422</v>
       </c>
       <c r="R46" t="n">
-        <v>6800164</v>
+        <v>6799802</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127035882</v>
+        <v>127036675</v>
       </c>
       <c r="B2" t="n">
-        <v>56849</v>
+        <v>79014</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>428512</v>
+        <v>428222</v>
       </c>
       <c r="R2" t="n">
-        <v>6799960</v>
+        <v>6799847</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127036675</v>
+        <v>127034383</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,37 +793,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>428222</v>
+        <v>428839</v>
       </c>
       <c r="R3" t="n">
-        <v>6799847</v>
+        <v>6800310</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,7 +889,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127034383</v>
+        <v>127029075</v>
       </c>
       <c r="B4" t="n">
         <v>78773</v>
@@ -925,17 +920,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428839</v>
+        <v>428374</v>
       </c>
       <c r="R4" t="n">
-        <v>6800310</v>
+        <v>6799811</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,48 +996,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127029075</v>
+        <v>127035882</v>
       </c>
       <c r="B5" t="n">
-        <v>78773</v>
+        <v>56849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428374</v>
+        <v>428512</v>
       </c>
       <c r="R5" t="n">
-        <v>6799811</v>
+        <v>6799960</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1862,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127033062</v>
+        <v>127028962</v>
       </c>
       <c r="B13" t="n">
-        <v>57654</v>
+        <v>78773</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,42 +1873,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>428840</v>
+        <v>428394</v>
       </c>
       <c r="R13" t="n">
-        <v>6799855</v>
+        <v>6799781</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1937,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1947,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2188,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127028962</v>
+        <v>127033062</v>
       </c>
       <c r="B16" t="n">
-        <v>78773</v>
+        <v>57654</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,37 +2194,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>428394</v>
+        <v>428840</v>
       </c>
       <c r="R16" t="n">
-        <v>6799781</v>
+        <v>6799855</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127033408</v>
+        <v>127030319</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>79603</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2306,37 +2306,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>428788</v>
+        <v>428422</v>
       </c>
       <c r="R17" t="n">
-        <v>6799983</v>
+        <v>6799802</v>
       </c>
       <c r="S17" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2509,10 +2509,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127030319</v>
+        <v>127033408</v>
       </c>
       <c r="B19" t="n">
-        <v>79603</v>
+        <v>79014</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,37 +2520,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>428422</v>
+        <v>428788</v>
       </c>
       <c r="R19" t="n">
-        <v>6799802</v>
+        <v>6799983</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2616,7 +2616,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127032907</v>
+        <v>127035403</v>
       </c>
       <c r="B20" t="n">
         <v>79014</v>
@@ -2651,10 +2651,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>428763</v>
+        <v>428610</v>
       </c>
       <c r="R20" t="n">
-        <v>6799813</v>
+        <v>6800197</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2723,7 +2723,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127035403</v>
+        <v>127032907</v>
       </c>
       <c r="B21" t="n">
         <v>79014</v>
@@ -2758,10 +2758,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>428610</v>
+        <v>428763</v>
       </c>
       <c r="R21" t="n">
-        <v>6800197</v>
+        <v>6799813</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3589,7 +3589,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127033497</v>
+        <v>127028434</v>
       </c>
       <c r="B29" t="n">
         <v>79014</v>
@@ -3620,17 +3620,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>428803</v>
+        <v>428388</v>
       </c>
       <c r="R29" t="n">
-        <v>6799992</v>
+        <v>6799765</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3696,7 +3696,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127028434</v>
+        <v>127033497</v>
       </c>
       <c r="B30" t="n">
         <v>79014</v>
@@ -3727,17 +3727,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>428388</v>
+        <v>428803</v>
       </c>
       <c r="R30" t="n">
-        <v>6799765</v>
+        <v>6799992</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -5632,10 +5632,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127030905</v>
+        <v>127030990</v>
       </c>
       <c r="B48" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5643,34 +5643,34 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>428635</v>
+        <v>428677</v>
       </c>
       <c r="R48" t="n">
-        <v>6799822</v>
+        <v>6799834</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5739,10 +5739,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127030990</v>
+        <v>127030905</v>
       </c>
       <c r="B49" t="n">
-        <v>78772</v>
+        <v>78773</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5750,34 +5750,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>428677</v>
+        <v>428635</v>
       </c>
       <c r="R49" t="n">
-        <v>6799834</v>
+        <v>6799822</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6172,53 +6172,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127033713</v>
+        <v>127033102</v>
       </c>
       <c r="B53" t="n">
-        <v>8447</v>
+        <v>79014</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>428806</v>
+        <v>428821</v>
       </c>
       <c r="R53" t="n">
-        <v>6800045</v>
+        <v>6799886</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6247,7 +6242,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6257,7 +6252,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6284,7 +6279,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127033102</v>
+        <v>127034263</v>
       </c>
       <c r="B54" t="n">
         <v>79014</v>
@@ -6319,10 +6314,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>428821</v>
+        <v>428826</v>
       </c>
       <c r="R54" t="n">
-        <v>6799886</v>
+        <v>6800180</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6354,7 +6349,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6364,7 +6359,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Garnlav mer eller mindre över hela området.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6391,10 +6391,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127034263</v>
+        <v>127035441</v>
       </c>
       <c r="B55" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6402,37 +6402,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>428826</v>
+        <v>428586</v>
       </c>
       <c r="R55" t="n">
-        <v>6800180</v>
+        <v>6800175</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6461,7 +6466,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6471,12 +6476,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Garnlav mer eller mindre över hela området.</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6503,38 +6503,38 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127035441</v>
+        <v>127033713</v>
       </c>
       <c r="B56" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6543,10 +6543,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>428586</v>
+        <v>428806</v>
       </c>
       <c r="R56" t="n">
-        <v>6800175</v>
+        <v>6800045</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127028820</v>
+        <v>127028288</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>79632</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>428394</v>
+        <v>428389</v>
       </c>
       <c r="R6" t="n">
-        <v>6799781</v>
+        <v>6799724</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,12 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i hela området.</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,7 +1215,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127028288</v>
+        <v>127031272</v>
       </c>
       <c r="B7" t="n">
         <v>79632</v>
@@ -1251,14 +1246,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>428389</v>
+        <v>428677</v>
       </c>
       <c r="R7" t="n">
-        <v>6799724</v>
+        <v>6799834</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1290,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127031272</v>
+        <v>127032866</v>
       </c>
       <c r="B8" t="n">
-        <v>79632</v>
+        <v>79015</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>230405</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1362,13 +1357,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>428677</v>
+        <v>428752</v>
       </c>
       <c r="R8" t="n">
-        <v>6799834</v>
+        <v>6799795</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1397,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1402,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127032866</v>
+        <v>127028820</v>
       </c>
       <c r="B9" t="n">
-        <v>79015</v>
+        <v>79014</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,16 +1440,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1465,17 +1460,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>428752</v>
+        <v>428394</v>
       </c>
       <c r="R9" t="n">
-        <v>6799795</v>
+        <v>6799781</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1504,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1509,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i hela området.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -2616,10 +2616,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127035403</v>
+        <v>127034314</v>
       </c>
       <c r="B20" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2627,21 +2627,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2651,13 +2651,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>428610</v>
+        <v>428856</v>
       </c>
       <c r="R20" t="n">
-        <v>6800197</v>
+        <v>6800220</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2723,10 +2723,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127032907</v>
+        <v>127031042</v>
       </c>
       <c r="B21" t="n">
-        <v>79014</v>
+        <v>78773</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2734,21 +2734,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2758,13 +2758,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>428763</v>
+        <v>428677</v>
       </c>
       <c r="R21" t="n">
-        <v>6799813</v>
+        <v>6799834</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2830,10 +2830,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127033867</v>
+        <v>127035403</v>
       </c>
       <c r="B22" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2841,21 +2841,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2865,13 +2865,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>428801</v>
+        <v>428610</v>
       </c>
       <c r="R22" t="n">
-        <v>6800075</v>
+        <v>6800197</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2937,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127033349</v>
+        <v>127032907</v>
       </c>
       <c r="B23" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2948,39 +2948,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>428792</v>
+        <v>428763</v>
       </c>
       <c r="R23" t="n">
-        <v>6799956</v>
+        <v>6799813</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3012,7 +3007,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3022,7 +3017,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3161,10 +3156,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127034314</v>
+        <v>127033867</v>
       </c>
       <c r="B25" t="n">
-        <v>78773</v>
+        <v>78772</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3172,21 +3167,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3196,13 +3191,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>428856</v>
+        <v>428801</v>
       </c>
       <c r="R25" t="n">
-        <v>6800220</v>
+        <v>6800075</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3231,7 +3226,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3241,7 +3236,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3268,10 +3263,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127031042</v>
+        <v>127033349</v>
       </c>
       <c r="B26" t="n">
-        <v>78773</v>
+        <v>57654</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3279,37 +3274,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>428677</v>
+        <v>428792</v>
       </c>
       <c r="R26" t="n">
-        <v>6799834</v>
+        <v>6799956</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -5846,10 +5846,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127032317</v>
+        <v>127034235</v>
       </c>
       <c r="B50" t="n">
-        <v>79014</v>
+        <v>57654</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5857,37 +5857,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>428727</v>
+        <v>428843</v>
       </c>
       <c r="R50" t="n">
-        <v>6799838</v>
+        <v>6800159</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5916,7 +5921,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5926,7 +5931,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5953,10 +5958,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127034235</v>
+        <v>127032317</v>
       </c>
       <c r="B51" t="n">
-        <v>57654</v>
+        <v>79014</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5964,42 +5969,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>428843</v>
+        <v>428727</v>
       </c>
       <c r="R51" t="n">
-        <v>6800159</v>
+        <v>6799838</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD51" t="b">

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127028288</v>
+        <v>127028820</v>
       </c>
       <c r="B6" t="n">
-        <v>79632</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>428389</v>
+        <v>428394</v>
       </c>
       <c r="R6" t="n">
-        <v>6799724</v>
+        <v>6799781</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i hela området.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,7 +1220,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127031272</v>
+        <v>127028288</v>
       </c>
       <c r="B7" t="n">
         <v>79632</v>
@@ -1246,14 +1251,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>428677</v>
+        <v>428389</v>
       </c>
       <c r="R7" t="n">
-        <v>6799834</v>
+        <v>6799724</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1285,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127032866</v>
+        <v>127031272</v>
       </c>
       <c r="B8" t="n">
-        <v>79015</v>
+        <v>79632</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,21 +1338,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>230405</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,13 +1362,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>428752</v>
+        <v>428677</v>
       </c>
       <c r="R8" t="n">
-        <v>6799795</v>
+        <v>6799834</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1392,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1402,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127028820</v>
+        <v>127032866</v>
       </c>
       <c r="B9" t="n">
-        <v>79014</v>
+        <v>79015</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1440,16 +1445,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1460,17 +1465,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>428394</v>
+        <v>428752</v>
       </c>
       <c r="R9" t="n">
-        <v>6799781</v>
+        <v>6799795</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1499,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,12 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i hela området.</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127032352</v>
+        <v>127030417</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1659,37 +1659,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>428730</v>
+        <v>428422</v>
       </c>
       <c r="R11" t="n">
-        <v>6799840</v>
+        <v>6799802</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127030417</v>
+        <v>127032352</v>
       </c>
       <c r="B12" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,37 +1766,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>428422</v>
+        <v>428730</v>
       </c>
       <c r="R12" t="n">
-        <v>6799802</v>
+        <v>6799840</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127028962</v>
+        <v>127029492</v>
       </c>
       <c r="B13" t="n">
-        <v>78773</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,21 +1873,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,13 +1897,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>428394</v>
+        <v>428422</v>
       </c>
       <c r="R13" t="n">
-        <v>6799781</v>
+        <v>6799802</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127029492</v>
+        <v>127033222</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,37 +1980,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>428422</v>
+        <v>428831</v>
       </c>
       <c r="R14" t="n">
-        <v>6799802</v>
+        <v>6799894</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127033222</v>
+        <v>127033062</v>
       </c>
       <c r="B15" t="n">
-        <v>78772</v>
+        <v>57654</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2087,37 +2087,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>428831</v>
+        <v>428840</v>
       </c>
       <c r="R15" t="n">
-        <v>6799894</v>
+        <v>6799855</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2146,7 +2151,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2156,7 +2161,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2183,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127033062</v>
+        <v>127028962</v>
       </c>
       <c r="B16" t="n">
-        <v>57654</v>
+        <v>78773</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2194,42 +2199,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>428840</v>
+        <v>428394</v>
       </c>
       <c r="R16" t="n">
-        <v>6799855</v>
+        <v>6799781</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127030319</v>
+        <v>127033408</v>
       </c>
       <c r="B17" t="n">
-        <v>79603</v>
+        <v>79014</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2306,37 +2306,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>428422</v>
+        <v>428788</v>
       </c>
       <c r="R17" t="n">
-        <v>6799802</v>
+        <v>6799983</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2509,10 +2509,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127033408</v>
+        <v>127030319</v>
       </c>
       <c r="B19" t="n">
-        <v>79014</v>
+        <v>79603</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,37 +2520,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>428788</v>
+        <v>428422</v>
       </c>
       <c r="R19" t="n">
-        <v>6799983</v>
+        <v>6799802</v>
       </c>
       <c r="S19" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3044,53 +3044,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127028936</v>
+        <v>127033867</v>
       </c>
       <c r="B24" t="n">
-        <v>8447</v>
+        <v>78772</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>428394</v>
+        <v>428801</v>
       </c>
       <c r="R24" t="n">
-        <v>6799781</v>
+        <v>6800075</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3119,7 +3114,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3129,7 +3124,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3156,10 +3151,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127033867</v>
+        <v>127033349</v>
       </c>
       <c r="B25" t="n">
-        <v>78772</v>
+        <v>57654</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3167,37 +3162,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>428801</v>
+        <v>428792</v>
       </c>
       <c r="R25" t="n">
-        <v>6800075</v>
+        <v>6799956</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3263,53 +3263,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127033349</v>
+        <v>127028936</v>
       </c>
       <c r="B26" t="n">
-        <v>57654</v>
+        <v>8447</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>428792</v>
+        <v>428394</v>
       </c>
       <c r="R26" t="n">
-        <v>6799956</v>
+        <v>6799781</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -5525,10 +5525,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127034565</v>
+        <v>127030990</v>
       </c>
       <c r="B47" t="n">
-        <v>79014</v>
+        <v>78772</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5536,21 +5536,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5560,13 +5560,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>428780</v>
+        <v>428677</v>
       </c>
       <c r="R47" t="n">
-        <v>6800319</v>
+        <v>6799834</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5632,10 +5632,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127030990</v>
+        <v>127034565</v>
       </c>
       <c r="B48" t="n">
-        <v>78772</v>
+        <v>79014</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5643,21 +5643,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5667,13 +5667,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>428677</v>
+        <v>428780</v>
       </c>
       <c r="R48" t="n">
-        <v>6799834</v>
+        <v>6800319</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD48" t="b">

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127036675</v>
+        <v>127034383</v>
       </c>
       <c r="B2" t="n">
-        <v>79014</v>
+        <v>78777</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>428222</v>
+        <v>428839</v>
       </c>
       <c r="R2" t="n">
-        <v>6799847</v>
+        <v>6800310</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127034383</v>
+        <v>127029075</v>
       </c>
       <c r="B3" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,17 +813,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>428839</v>
+        <v>428374</v>
       </c>
       <c r="R3" t="n">
-        <v>6800310</v>
+        <v>6799811</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127029075</v>
+        <v>127036675</v>
       </c>
       <c r="B4" t="n">
-        <v>78773</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428374</v>
+        <v>428222</v>
       </c>
       <c r="R4" t="n">
-        <v>6799811</v>
+        <v>6799847</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,7 +999,7 @@
         <v>127035882</v>
       </c>
       <c r="B5" t="n">
-        <v>56849</v>
+        <v>56853</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127028820</v>
+        <v>127031272</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>79636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,37 +1119,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>428394</v>
+        <v>428677</v>
       </c>
       <c r="R6" t="n">
-        <v>6799781</v>
+        <v>6799834</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,12 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i hela området.</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127028288</v>
+        <v>127028820</v>
       </c>
       <c r="B7" t="n">
-        <v>79632</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,13 +1250,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>428389</v>
+        <v>428394</v>
       </c>
       <c r="R7" t="n">
-        <v>6799724</v>
+        <v>6799781</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1290,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1295,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i hela området.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127031272</v>
+        <v>127028288</v>
       </c>
       <c r="B8" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,14 +1358,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>428677</v>
+        <v>428389</v>
       </c>
       <c r="R8" t="n">
-        <v>6799834</v>
+        <v>6799724</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,7 +1437,7 @@
         <v>127032866</v>
       </c>
       <c r="B9" t="n">
-        <v>79015</v>
+        <v>79019</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>127036174</v>
       </c>
       <c r="B10" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1648,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127030417</v>
+        <v>127032352</v>
       </c>
       <c r="B11" t="n">
-        <v>78772</v>
+        <v>79018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1659,37 +1659,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>428422</v>
+        <v>428730</v>
       </c>
       <c r="R11" t="n">
-        <v>6799802</v>
+        <v>6799840</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127032352</v>
+        <v>127030417</v>
       </c>
       <c r="B12" t="n">
-        <v>79014</v>
+        <v>78776</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,37 +1766,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>428730</v>
+        <v>428422</v>
       </c>
       <c r="R12" t="n">
-        <v>6799840</v>
+        <v>6799802</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127029492</v>
+        <v>127033222</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>78776</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,37 +1873,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>428422</v>
+        <v>428831</v>
       </c>
       <c r="R13" t="n">
-        <v>6799802</v>
+        <v>6799894</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127033222</v>
+        <v>127029492</v>
       </c>
       <c r="B14" t="n">
-        <v>78772</v>
+        <v>79018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,37 +1980,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>428831</v>
+        <v>428422</v>
       </c>
       <c r="R14" t="n">
-        <v>6799894</v>
+        <v>6799802</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2079,7 +2079,7 @@
         <v>127033062</v>
       </c>
       <c r="B15" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2191,7 +2191,7 @@
         <v>127028962</v>
       </c>
       <c r="B16" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2295,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127033408</v>
+        <v>127028974</v>
       </c>
       <c r="B17" t="n">
-        <v>79014</v>
+        <v>78776</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2306,37 +2306,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>428788</v>
+        <v>428374</v>
       </c>
       <c r="R17" t="n">
-        <v>6799983</v>
+        <v>6799811</v>
       </c>
       <c r="S17" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2402,10 +2402,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127028974</v>
+        <v>127033408</v>
       </c>
       <c r="B18" t="n">
-        <v>78772</v>
+        <v>79018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2413,37 +2413,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>428374</v>
+        <v>428788</v>
       </c>
       <c r="R18" t="n">
-        <v>6799811</v>
+        <v>6799983</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2512,7 +2512,7 @@
         <v>127030319</v>
       </c>
       <c r="B19" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2616,45 +2616,50 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127034314</v>
+        <v>127028936</v>
       </c>
       <c r="B20" t="n">
-        <v>78773</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>428856</v>
+        <v>428394</v>
       </c>
       <c r="R20" t="n">
-        <v>6800220</v>
+        <v>6799781</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2686,7 +2691,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2696,7 +2701,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2723,10 +2728,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127031042</v>
+        <v>127035403</v>
       </c>
       <c r="B21" t="n">
-        <v>78773</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2734,21 +2739,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2758,13 +2763,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>428677</v>
+        <v>428610</v>
       </c>
       <c r="R21" t="n">
-        <v>6799834</v>
+        <v>6800197</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2793,7 +2798,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2803,7 +2808,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2830,10 +2835,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127035403</v>
+        <v>127033867</v>
       </c>
       <c r="B22" t="n">
-        <v>79014</v>
+        <v>78776</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2841,21 +2846,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2865,13 +2870,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>428610</v>
+        <v>428801</v>
       </c>
       <c r="R22" t="n">
-        <v>6800197</v>
+        <v>6800075</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2900,7 +2905,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2910,7 +2915,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2940,7 +2945,7 @@
         <v>127032907</v>
       </c>
       <c r="B23" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3044,10 +3049,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127033867</v>
+        <v>127033349</v>
       </c>
       <c r="B24" t="n">
-        <v>78772</v>
+        <v>57658</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3055,37 +3060,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>428801</v>
+        <v>428792</v>
       </c>
       <c r="R24" t="n">
-        <v>6800075</v>
+        <v>6799956</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3114,7 +3124,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3124,7 +3134,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3151,10 +3161,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127033349</v>
+        <v>127034314</v>
       </c>
       <c r="B25" t="n">
-        <v>57654</v>
+        <v>78777</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3162,42 +3172,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>428792</v>
+        <v>428856</v>
       </c>
       <c r="R25" t="n">
-        <v>6799956</v>
+        <v>6800220</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3226,7 +3231,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3236,7 +3241,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3263,53 +3268,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127028936</v>
+        <v>127031042</v>
       </c>
       <c r="B26" t="n">
-        <v>8447</v>
+        <v>78777</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>428394</v>
+        <v>428677</v>
       </c>
       <c r="R26" t="n">
-        <v>6799781</v>
+        <v>6799834</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3378,7 +3378,7 @@
         <v>127031710</v>
       </c>
       <c r="B27" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>127034644</v>
       </c>
       <c r="B28" t="n">
-        <v>91346</v>
+        <v>91350</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>127028434</v>
       </c>
       <c r="B29" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>127033497</v>
       </c>
       <c r="B30" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3803,10 +3803,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127030793</v>
+        <v>127035723</v>
       </c>
       <c r="B31" t="n">
-        <v>56840</v>
+        <v>91350</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3814,42 +3814,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102612</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>428603</v>
+        <v>428586</v>
       </c>
       <c r="R31" t="n">
-        <v>6799810</v>
+        <v>6800175</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3878,7 +3873,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3888,7 +3883,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3915,10 +3910,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127035723</v>
+        <v>127030793</v>
       </c>
       <c r="B32" t="n">
-        <v>91346</v>
+        <v>56844</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3926,37 +3921,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>102612</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>428586</v>
+        <v>428603</v>
       </c>
       <c r="R32" t="n">
-        <v>6800175</v>
+        <v>6799810</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4025,7 +4025,7 @@
         <v>127034901</v>
       </c>
       <c r="B33" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4129,10 +4129,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127035734</v>
+        <v>127033824</v>
       </c>
       <c r="B34" t="n">
-        <v>79014</v>
+        <v>78776</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4140,34 +4140,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>428511</v>
+        <v>428807</v>
       </c>
       <c r="R34" t="n">
-        <v>6799990</v>
+        <v>6800084</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4236,10 +4236,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127033824</v>
+        <v>127035734</v>
       </c>
       <c r="B35" t="n">
-        <v>78772</v>
+        <v>79018</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4247,34 +4247,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>428807</v>
+        <v>428511</v>
       </c>
       <c r="R35" t="n">
-        <v>6800084</v>
+        <v>6799990</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4343,10 +4343,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127034208</v>
+        <v>127030918</v>
       </c>
       <c r="B36" t="n">
-        <v>79014</v>
+        <v>78776</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4354,37 +4354,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>428809</v>
+        <v>428644</v>
       </c>
       <c r="R36" t="n">
-        <v>6800173</v>
+        <v>6799825</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4450,10 +4450,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>127030918</v>
+        <v>127036021</v>
       </c>
       <c r="B37" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4485,10 +4485,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>428644</v>
+        <v>428467</v>
       </c>
       <c r="R37" t="n">
-        <v>6799825</v>
+        <v>6799920</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4520,7 +4520,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>19:35</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4557,10 +4557,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127036021</v>
+        <v>127034208</v>
       </c>
       <c r="B38" t="n">
-        <v>78772</v>
+        <v>79018</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4568,37 +4568,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>428467</v>
+        <v>428809</v>
       </c>
       <c r="R38" t="n">
-        <v>6799920</v>
+        <v>6800173</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>19:35</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4667,7 +4667,7 @@
         <v>127033133</v>
       </c>
       <c r="B39" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>127026773</v>
       </c>
       <c r="B40" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4883,10 +4883,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127032393</v>
+        <v>127032439</v>
       </c>
       <c r="B41" t="n">
-        <v>79014</v>
+        <v>78776</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4894,21 +4894,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4918,10 +4918,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>428755</v>
+        <v>428752</v>
       </c>
       <c r="R41" t="n">
-        <v>6799817</v>
+        <v>6799795</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4990,10 +4990,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127032439</v>
+        <v>127032393</v>
       </c>
       <c r="B42" t="n">
-        <v>78772</v>
+        <v>79018</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5001,21 +5001,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>428752</v>
+        <v>428755</v>
       </c>
       <c r="R42" t="n">
-        <v>6799795</v>
+        <v>6799817</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5100,7 +5100,7 @@
         <v>127035229</v>
       </c>
       <c r="B43" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>127034191</v>
       </c>
       <c r="B44" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5314,7 +5314,7 @@
         <v>127033191</v>
       </c>
       <c r="B45" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         <v>127030347</v>
       </c>
       <c r="B46" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5525,10 +5525,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127030990</v>
+        <v>127034565</v>
       </c>
       <c r="B47" t="n">
-        <v>78772</v>
+        <v>79018</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5536,21 +5536,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5560,13 +5560,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>428677</v>
+        <v>428780</v>
       </c>
       <c r="R47" t="n">
-        <v>6799834</v>
+        <v>6800319</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5632,10 +5632,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127034565</v>
+        <v>127030990</v>
       </c>
       <c r="B48" t="n">
-        <v>79014</v>
+        <v>78776</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5643,21 +5643,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5667,13 +5667,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>428780</v>
+        <v>428677</v>
       </c>
       <c r="R48" t="n">
-        <v>6800319</v>
+        <v>6799834</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5742,7 +5742,7 @@
         <v>127030905</v>
       </c>
       <c r="B49" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>127034235</v>
       </c>
       <c r="B50" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
         <v>127032317</v>
       </c>
       <c r="B51" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>127027998</v>
       </c>
       <c r="B52" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6175,7 +6175,7 @@
         <v>127033102</v>
       </c>
       <c r="B53" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6282,7 +6282,7 @@
         <v>127034263</v>
       </c>
       <c r="B54" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
         <v>127035441</v>
       </c>
       <c r="B55" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6506,7 +6506,7 @@
         <v>127033713</v>
       </c>
       <c r="B56" t="n">
-        <v>8447</v>
+        <v>8450</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127034383</v>
+        <v>127036675</v>
       </c>
       <c r="B2" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>428839</v>
+        <v>428222</v>
       </c>
       <c r="R2" t="n">
-        <v>6800310</v>
+        <v>6799847</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,48 +782,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127029075</v>
+        <v>127035882</v>
       </c>
       <c r="B3" t="n">
-        <v>78777</v>
+        <v>56853</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>428374</v>
+        <v>428512</v>
       </c>
       <c r="R3" t="n">
-        <v>6799811</v>
+        <v>6799960</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127036675</v>
+        <v>127034383</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,37 +905,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428222</v>
+        <v>428839</v>
       </c>
       <c r="R4" t="n">
-        <v>6799847</v>
+        <v>6800310</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,53 +1001,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127035882</v>
+        <v>127029075</v>
       </c>
       <c r="B5" t="n">
-        <v>56853</v>
+        <v>78777</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428512</v>
+        <v>428374</v>
       </c>
       <c r="R5" t="n">
-        <v>6799960</v>
+        <v>6799811</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127031272</v>
+        <v>127032866</v>
       </c>
       <c r="B6" t="n">
-        <v>79636</v>
+        <v>79019</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>230405</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>428677</v>
+        <v>428752</v>
       </c>
       <c r="R6" t="n">
-        <v>6799834</v>
+        <v>6799795</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127032866</v>
+        <v>127031272</v>
       </c>
       <c r="B9" t="n">
-        <v>79019</v>
+        <v>79636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,21 +1445,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>230405</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,13 +1469,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>428752</v>
+        <v>428677</v>
       </c>
       <c r="R9" t="n">
-        <v>6799795</v>
+        <v>6799834</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1862,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127033222</v>
+        <v>127029492</v>
       </c>
       <c r="B13" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,37 +1873,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>428831</v>
+        <v>428422</v>
       </c>
       <c r="R13" t="n">
-        <v>6799894</v>
+        <v>6799802</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127029492</v>
+        <v>127033062</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,34 +1980,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>428422</v>
+        <v>428840</v>
       </c>
       <c r="R14" t="n">
-        <v>6799802</v>
+        <v>6799855</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2039,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,7 +2054,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127033062</v>
+        <v>127028962</v>
       </c>
       <c r="B15" t="n">
-        <v>57658</v>
+        <v>78777</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2087,42 +2092,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>428840</v>
+        <v>428394</v>
       </c>
       <c r="R15" t="n">
-        <v>6799855</v>
+        <v>6799781</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2188,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127028962</v>
+        <v>127033222</v>
       </c>
       <c r="B16" t="n">
-        <v>78777</v>
+        <v>78776</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,34 +2199,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>428394</v>
+        <v>428831</v>
       </c>
       <c r="R16" t="n">
-        <v>6799781</v>
+        <v>6799894</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2616,53 +2616,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127028936</v>
+        <v>127033867</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>78776</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>428394</v>
+        <v>428801</v>
       </c>
       <c r="R20" t="n">
-        <v>6799781</v>
+        <v>6800075</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2691,7 +2686,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2701,7 +2696,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2728,7 +2723,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127035403</v>
+        <v>127032907</v>
       </c>
       <c r="B21" t="n">
         <v>79018</v>
@@ -2763,10 +2758,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>428610</v>
+        <v>428763</v>
       </c>
       <c r="R21" t="n">
-        <v>6800197</v>
+        <v>6799813</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2798,7 +2793,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2808,7 +2803,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2835,10 +2830,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127033867</v>
+        <v>127035403</v>
       </c>
       <c r="B22" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2846,21 +2841,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2870,13 +2865,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>428801</v>
+        <v>428610</v>
       </c>
       <c r="R22" t="n">
-        <v>6800075</v>
+        <v>6800197</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2905,7 +2900,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2915,7 +2910,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2942,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127032907</v>
+        <v>127033349</v>
       </c>
       <c r="B23" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2953,34 +2948,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>428763</v>
+        <v>428792</v>
       </c>
       <c r="R23" t="n">
-        <v>6799813</v>
+        <v>6799956</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3049,53 +3049,53 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127033349</v>
+        <v>127028936</v>
       </c>
       <c r="B24" t="n">
-        <v>57658</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>428792</v>
+        <v>428394</v>
       </c>
       <c r="R24" t="n">
-        <v>6799956</v>
+        <v>6799781</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3482,10 +3482,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127034644</v>
+        <v>127028434</v>
       </c>
       <c r="B28" t="n">
-        <v>91350</v>
+        <v>79018</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3493,37 +3493,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>428786</v>
+        <v>428388</v>
       </c>
       <c r="R28" t="n">
-        <v>6800327</v>
+        <v>6799765</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3589,10 +3589,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127028434</v>
+        <v>127034644</v>
       </c>
       <c r="B29" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3600,37 +3600,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>428388</v>
+        <v>428786</v>
       </c>
       <c r="R29" t="n">
-        <v>6799765</v>
+        <v>6800327</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4129,10 +4129,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127033824</v>
+        <v>127035734</v>
       </c>
       <c r="B34" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4140,34 +4140,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>428807</v>
+        <v>428511</v>
       </c>
       <c r="R34" t="n">
-        <v>6800084</v>
+        <v>6799990</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4236,10 +4236,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127035734</v>
+        <v>127033824</v>
       </c>
       <c r="B35" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4247,34 +4247,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>428511</v>
+        <v>428807</v>
       </c>
       <c r="R35" t="n">
-        <v>6799990</v>
+        <v>6800084</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4883,10 +4883,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127032439</v>
+        <v>127032393</v>
       </c>
       <c r="B41" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4894,21 +4894,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4918,10 +4918,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>428752</v>
+        <v>428755</v>
       </c>
       <c r="R41" t="n">
-        <v>6799795</v>
+        <v>6799817</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4990,10 +4990,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127032393</v>
+        <v>127032439</v>
       </c>
       <c r="B42" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5001,21 +5001,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>428755</v>
+        <v>428752</v>
       </c>
       <c r="R42" t="n">
-        <v>6799817</v>
+        <v>6799795</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5525,10 +5525,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127034565</v>
+        <v>127030990</v>
       </c>
       <c r="B47" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5536,21 +5536,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5560,13 +5560,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>428780</v>
+        <v>428677</v>
       </c>
       <c r="R47" t="n">
-        <v>6800319</v>
+        <v>6799834</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5632,10 +5632,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127030990</v>
+        <v>127034565</v>
       </c>
       <c r="B48" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5643,21 +5643,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5667,13 +5667,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>428677</v>
+        <v>428780</v>
       </c>
       <c r="R48" t="n">
-        <v>6799834</v>
+        <v>6800319</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5846,10 +5846,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127034235</v>
+        <v>127032317</v>
       </c>
       <c r="B50" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5857,42 +5857,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>428843</v>
+        <v>428727</v>
       </c>
       <c r="R50" t="n">
-        <v>6800159</v>
+        <v>6799838</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5921,7 +5916,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5931,7 +5926,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5958,10 +5953,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127032317</v>
+        <v>127034235</v>
       </c>
       <c r="B51" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5969,37 +5964,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>428727</v>
+        <v>428843</v>
       </c>
       <c r="R51" t="n">
-        <v>6799838</v>
+        <v>6800159</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6172,10 +6172,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127033102</v>
+        <v>127035441</v>
       </c>
       <c r="B53" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6183,37 +6183,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>428821</v>
+        <v>428586</v>
       </c>
       <c r="R53" t="n">
-        <v>6799886</v>
+        <v>6800175</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6242,7 +6247,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6252,7 +6257,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6279,7 +6284,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127034263</v>
+        <v>127033102</v>
       </c>
       <c r="B54" t="n">
         <v>79018</v>
@@ -6314,10 +6319,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>428826</v>
+        <v>428821</v>
       </c>
       <c r="R54" t="n">
-        <v>6800180</v>
+        <v>6799886</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6349,7 +6354,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6359,12 +6364,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Garnlav mer eller mindre över hela området.</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6391,10 +6391,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127035441</v>
+        <v>127034263</v>
       </c>
       <c r="B55" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6402,42 +6402,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>428586</v>
+        <v>428826</v>
       </c>
       <c r="R55" t="n">
-        <v>6800175</v>
+        <v>6800180</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6466,7 +6461,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6476,7 +6471,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Garnlav mer eller mindre över hela området.</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127028820</v>
+        <v>127028288</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>428394</v>
+        <v>428389</v>
       </c>
       <c r="R7" t="n">
-        <v>6799781</v>
+        <v>6799724</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,12 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i hela området.</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,7 +1322,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127028288</v>
+        <v>127031272</v>
       </c>
       <c r="B8" t="n">
         <v>79636</v>
@@ -1358,14 +1353,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>428389</v>
+        <v>428677</v>
       </c>
       <c r="R8" t="n">
-        <v>6799724</v>
+        <v>6799834</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1397,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1402,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,10 +1429,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127031272</v>
+        <v>127028820</v>
       </c>
       <c r="B9" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,37 +1440,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>428677</v>
+        <v>428394</v>
       </c>
       <c r="R9" t="n">
-        <v>6799834</v>
+        <v>6799781</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1504,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1509,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i hela området.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127032352</v>
+        <v>127030417</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1659,37 +1659,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>428730</v>
+        <v>428422</v>
       </c>
       <c r="R11" t="n">
-        <v>6799840</v>
+        <v>6799802</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127030417</v>
+        <v>127032352</v>
       </c>
       <c r="B12" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,37 +1766,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>428422</v>
+        <v>428730</v>
       </c>
       <c r="R12" t="n">
-        <v>6799802</v>
+        <v>6799840</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127029492</v>
+        <v>127028962</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,21 +1873,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,13 +1897,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>428422</v>
+        <v>428394</v>
       </c>
       <c r="R13" t="n">
-        <v>6799802</v>
+        <v>6799781</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127033062</v>
+        <v>127029492</v>
       </c>
       <c r="B14" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,39 +1980,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>428840</v>
+        <v>428422</v>
       </c>
       <c r="R14" t="n">
-        <v>6799855</v>
+        <v>6799802</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2044,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,7 +2049,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127028962</v>
+        <v>127033222</v>
       </c>
       <c r="B15" t="n">
-        <v>78777</v>
+        <v>78776</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,34 +2087,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>428394</v>
+        <v>428831</v>
       </c>
       <c r="R15" t="n">
-        <v>6799781</v>
+        <v>6799894</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2151,7 +2146,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2161,7 +2156,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2188,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127033222</v>
+        <v>127033062</v>
       </c>
       <c r="B16" t="n">
-        <v>78776</v>
+        <v>57658</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,37 +2194,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>428831</v>
+        <v>428840</v>
       </c>
       <c r="R16" t="n">
-        <v>6799894</v>
+        <v>6799855</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2616,48 +2616,53 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127033867</v>
+        <v>127028936</v>
       </c>
       <c r="B20" t="n">
-        <v>78776</v>
+        <v>8450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>428801</v>
+        <v>428394</v>
       </c>
       <c r="R20" t="n">
-        <v>6800075</v>
+        <v>6799781</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2686,7 +2691,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2696,7 +2701,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2723,10 +2728,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127032907</v>
+        <v>127033349</v>
       </c>
       <c r="B21" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2734,34 +2739,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>428763</v>
+        <v>428792</v>
       </c>
       <c r="R21" t="n">
-        <v>6799813</v>
+        <v>6799956</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2793,7 +2803,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2803,7 +2813,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2830,10 +2840,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127035403</v>
+        <v>127033867</v>
       </c>
       <c r="B22" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2841,21 +2851,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2865,13 +2875,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>428610</v>
+        <v>428801</v>
       </c>
       <c r="R22" t="n">
-        <v>6800197</v>
+        <v>6800075</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2900,7 +2910,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2910,7 +2920,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2937,10 +2947,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127033349</v>
+        <v>127032907</v>
       </c>
       <c r="B23" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2948,39 +2958,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>428792</v>
+        <v>428763</v>
       </c>
       <c r="R23" t="n">
-        <v>6799956</v>
+        <v>6799813</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3012,7 +3017,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3022,7 +3027,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3049,53 +3054,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127028936</v>
+        <v>127035403</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>428394</v>
+        <v>428610</v>
       </c>
       <c r="R24" t="n">
-        <v>6799781</v>
+        <v>6800197</v>
       </c>
       <c r="S24" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3482,10 +3482,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127028434</v>
+        <v>127034644</v>
       </c>
       <c r="B28" t="n">
-        <v>79018</v>
+        <v>91350</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3493,37 +3493,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>428388</v>
+        <v>428786</v>
       </c>
       <c r="R28" t="n">
-        <v>6799765</v>
+        <v>6800327</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3589,10 +3589,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127034644</v>
+        <v>127033497</v>
       </c>
       <c r="B29" t="n">
-        <v>91350</v>
+        <v>79018</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3600,21 +3600,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3624,10 +3624,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>428786</v>
+        <v>428803</v>
       </c>
       <c r="R29" t="n">
-        <v>6800327</v>
+        <v>6799992</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3696,7 +3696,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127033497</v>
+        <v>127028434</v>
       </c>
       <c r="B30" t="n">
         <v>79018</v>
@@ -3727,17 +3727,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>428803</v>
+        <v>428388</v>
       </c>
       <c r="R30" t="n">
-        <v>6799992</v>
+        <v>6799765</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -5525,10 +5525,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127030990</v>
+        <v>127034565</v>
       </c>
       <c r="B47" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5536,21 +5536,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5560,13 +5560,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>428677</v>
+        <v>428780</v>
       </c>
       <c r="R47" t="n">
-        <v>6799834</v>
+        <v>6800319</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5632,10 +5632,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127034565</v>
+        <v>127030990</v>
       </c>
       <c r="B48" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5643,21 +5643,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5667,13 +5667,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>428780</v>
+        <v>428677</v>
       </c>
       <c r="R48" t="n">
-        <v>6800319</v>
+        <v>6799834</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6172,38 +6172,38 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127035441</v>
+        <v>127033713</v>
       </c>
       <c r="B53" t="n">
-        <v>57658</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6212,10 +6212,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>428586</v>
+        <v>428806</v>
       </c>
       <c r="R53" t="n">
-        <v>6800175</v>
+        <v>6800045</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6503,38 +6503,38 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127033713</v>
+        <v>127035441</v>
       </c>
       <c r="B56" t="n">
-        <v>8450</v>
+        <v>57658</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6543,10 +6543,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>428806</v>
+        <v>428586</v>
       </c>
       <c r="R56" t="n">
-        <v>6800045</v>
+        <v>6800175</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127028288</v>
+        <v>127028820</v>
       </c>
       <c r="B7" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>428389</v>
+        <v>428394</v>
       </c>
       <c r="R7" t="n">
-        <v>6799724</v>
+        <v>6799781</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1295,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i hela området.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,7 +1327,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127031272</v>
+        <v>127028288</v>
       </c>
       <c r="B8" t="n">
         <v>79636</v>
@@ -1353,14 +1358,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>428677</v>
+        <v>428389</v>
       </c>
       <c r="R8" t="n">
-        <v>6799834</v>
+        <v>6799724</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1392,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1402,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1429,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127028820</v>
+        <v>127031272</v>
       </c>
       <c r="B9" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1440,37 +1445,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>428394</v>
+        <v>428677</v>
       </c>
       <c r="R9" t="n">
-        <v>6799781</v>
+        <v>6799834</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1499,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1509,12 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i hela området.</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1862,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127028962</v>
+        <v>127029492</v>
       </c>
       <c r="B13" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,21 +1873,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,13 +1897,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>428394</v>
+        <v>428422</v>
       </c>
       <c r="R13" t="n">
-        <v>6799781</v>
+        <v>6799802</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127029492</v>
+        <v>127033062</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,34 +1980,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>428422</v>
+        <v>428840</v>
       </c>
       <c r="R14" t="n">
-        <v>6799802</v>
+        <v>6799855</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2039,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,7 +2054,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127033222</v>
+        <v>127028962</v>
       </c>
       <c r="B15" t="n">
-        <v>78776</v>
+        <v>78777</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2087,34 +2092,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>428831</v>
+        <v>428394</v>
       </c>
       <c r="R15" t="n">
-        <v>6799894</v>
+        <v>6799781</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2146,7 +2151,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2156,7 +2161,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2183,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127033062</v>
+        <v>127033222</v>
       </c>
       <c r="B16" t="n">
-        <v>57658</v>
+        <v>78776</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2194,42 +2199,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>428840</v>
+        <v>428831</v>
       </c>
       <c r="R16" t="n">
-        <v>6799855</v>
+        <v>6799894</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2616,50 +2616,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127028936</v>
+        <v>127034314</v>
       </c>
       <c r="B20" t="n">
-        <v>8450</v>
+        <v>78777</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>428394</v>
+        <v>428856</v>
       </c>
       <c r="R20" t="n">
-        <v>6799781</v>
+        <v>6800220</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2691,7 +2686,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2701,7 +2696,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2728,10 +2723,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127033349</v>
+        <v>127031042</v>
       </c>
       <c r="B21" t="n">
-        <v>57658</v>
+        <v>78777</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2739,42 +2734,37 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>428792</v>
+        <v>428677</v>
       </c>
       <c r="R21" t="n">
-        <v>6799956</v>
+        <v>6799834</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2803,7 +2793,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2813,7 +2803,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3161,10 +3151,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127034314</v>
+        <v>127033349</v>
       </c>
       <c r="B25" t="n">
-        <v>78777</v>
+        <v>57658</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3172,37 +3162,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>428856</v>
+        <v>428792</v>
       </c>
       <c r="R25" t="n">
-        <v>6800220</v>
+        <v>6799956</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3231,7 +3226,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3241,7 +3236,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3268,48 +3263,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127031042</v>
+        <v>127028936</v>
       </c>
       <c r="B26" t="n">
-        <v>78777</v>
+        <v>8450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>428677</v>
+        <v>428394</v>
       </c>
       <c r="R26" t="n">
-        <v>6799834</v>
+        <v>6799781</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -5525,10 +5525,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127034565</v>
+        <v>127030990</v>
       </c>
       <c r="B47" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5536,21 +5536,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5560,13 +5560,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>428780</v>
+        <v>428677</v>
       </c>
       <c r="R47" t="n">
-        <v>6800319</v>
+        <v>6799834</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5632,10 +5632,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127030990</v>
+        <v>127034565</v>
       </c>
       <c r="B48" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5643,21 +5643,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5667,13 +5667,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>428677</v>
+        <v>428780</v>
       </c>
       <c r="R48" t="n">
-        <v>6799834</v>
+        <v>6800319</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6172,38 +6172,38 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127033713</v>
+        <v>127035441</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>57658</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6212,10 +6212,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>428806</v>
+        <v>428586</v>
       </c>
       <c r="R53" t="n">
-        <v>6800045</v>
+        <v>6800175</v>
       </c>
       <c r="S53" t="n">
         <v>20</v>
@@ -6247,7 +6247,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6257,7 +6257,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6503,38 +6503,38 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127035441</v>
+        <v>127033713</v>
       </c>
       <c r="B56" t="n">
-        <v>57658</v>
+        <v>8450</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6543,10 +6543,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>428586</v>
+        <v>428806</v>
       </c>
       <c r="R56" t="n">
-        <v>6800175</v>
+        <v>6800045</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127036675</v>
+        <v>127034383</v>
       </c>
       <c r="B2" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>428222</v>
+        <v>428839</v>
       </c>
       <c r="R2" t="n">
-        <v>6799847</v>
+        <v>6800310</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,53 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127035882</v>
+        <v>127029075</v>
       </c>
       <c r="B3" t="n">
-        <v>56853</v>
+        <v>78777</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>428512</v>
+        <v>428374</v>
       </c>
       <c r="R3" t="n">
-        <v>6799960</v>
+        <v>6799811</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127034383</v>
+        <v>127036675</v>
       </c>
       <c r="B4" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,37 +900,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428839</v>
+        <v>428222</v>
       </c>
       <c r="R4" t="n">
-        <v>6800310</v>
+        <v>6799847</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,48 +996,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127029075</v>
+        <v>127035882</v>
       </c>
       <c r="B5" t="n">
-        <v>78777</v>
+        <v>56853</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428374</v>
+        <v>428512</v>
       </c>
       <c r="R5" t="n">
-        <v>6799811</v>
+        <v>6799960</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127032866</v>
+        <v>127028288</v>
       </c>
       <c r="B6" t="n">
-        <v>79019</v>
+        <v>79636</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,37 +1119,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>230405</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>428752</v>
+        <v>428389</v>
       </c>
       <c r="R6" t="n">
-        <v>6799795</v>
+        <v>6799724</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127028820</v>
+        <v>127031272</v>
       </c>
       <c r="B7" t="n">
-        <v>79018</v>
+        <v>79636</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,37 +1226,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>428394</v>
+        <v>428677</v>
       </c>
       <c r="R7" t="n">
-        <v>6799781</v>
+        <v>6799834</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,12 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i hela området.</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127028288</v>
+        <v>127028820</v>
       </c>
       <c r="B8" t="n">
-        <v>79636</v>
+        <v>79018</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,21 +1333,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1362,13 +1357,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>428389</v>
+        <v>428394</v>
       </c>
       <c r="R8" t="n">
-        <v>6799724</v>
+        <v>6799781</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1397,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1402,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i hela området.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127031272</v>
+        <v>127032866</v>
       </c>
       <c r="B9" t="n">
-        <v>79636</v>
+        <v>79019</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,21 +1445,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>230405</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,13 +1469,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>428677</v>
+        <v>428752</v>
       </c>
       <c r="R9" t="n">
-        <v>6799834</v>
+        <v>6799795</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1648,10 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127030417</v>
+        <v>127032352</v>
       </c>
       <c r="B11" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1659,37 +1659,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>428422</v>
+        <v>428730</v>
       </c>
       <c r="R11" t="n">
-        <v>6799802</v>
+        <v>6799840</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1755,10 +1755,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127032352</v>
+        <v>127030417</v>
       </c>
       <c r="B12" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1766,37 +1766,37 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>428730</v>
+        <v>428422</v>
       </c>
       <c r="R12" t="n">
-        <v>6799840</v>
+        <v>6799802</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1862,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127029492</v>
+        <v>127033222</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,37 +1873,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>428422</v>
+        <v>428831</v>
       </c>
       <c r="R13" t="n">
-        <v>6799802</v>
+        <v>6799894</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2081,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127028962</v>
+        <v>127029492</v>
       </c>
       <c r="B15" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,21 +2092,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2116,13 +2116,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>428394</v>
+        <v>428422</v>
       </c>
       <c r="R15" t="n">
-        <v>6799781</v>
+        <v>6799802</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2188,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127033222</v>
+        <v>127028962</v>
       </c>
       <c r="B16" t="n">
-        <v>78776</v>
+        <v>78777</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,34 +2199,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>428831</v>
+        <v>428394</v>
       </c>
       <c r="R16" t="n">
-        <v>6799894</v>
+        <v>6799781</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127028974</v>
+        <v>127030319</v>
       </c>
       <c r="B17" t="n">
-        <v>78776</v>
+        <v>79607</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2306,21 +2306,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2330,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>428374</v>
+        <v>428422</v>
       </c>
       <c r="R17" t="n">
-        <v>6799811</v>
+        <v>6799802</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2402,10 +2402,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127033408</v>
+        <v>127028974</v>
       </c>
       <c r="B18" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2413,37 +2413,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>428788</v>
+        <v>428374</v>
       </c>
       <c r="R18" t="n">
-        <v>6799983</v>
+        <v>6799811</v>
       </c>
       <c r="S18" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2509,10 +2509,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127030319</v>
+        <v>127033408</v>
       </c>
       <c r="B19" t="n">
-        <v>79607</v>
+        <v>79018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,37 +2520,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>428422</v>
+        <v>428788</v>
       </c>
       <c r="R19" t="n">
-        <v>6799802</v>
+        <v>6799983</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2616,10 +2616,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127034314</v>
+        <v>127033867</v>
       </c>
       <c r="B20" t="n">
-        <v>78777</v>
+        <v>78776</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2627,21 +2627,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2651,13 +2651,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>428856</v>
+        <v>428801</v>
       </c>
       <c r="R20" t="n">
-        <v>6800220</v>
+        <v>6800075</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2723,10 +2723,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127031042</v>
+        <v>127032907</v>
       </c>
       <c r="B21" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2734,21 +2734,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2758,13 +2758,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>428677</v>
+        <v>428763</v>
       </c>
       <c r="R21" t="n">
-        <v>6799834</v>
+        <v>6799813</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2830,10 +2830,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127033867</v>
+        <v>127035403</v>
       </c>
       <c r="B22" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2841,21 +2841,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2865,13 +2865,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>428801</v>
+        <v>428610</v>
       </c>
       <c r="R22" t="n">
-        <v>6800075</v>
+        <v>6800197</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2910,7 +2910,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2937,48 +2937,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127032907</v>
+        <v>127028936</v>
       </c>
       <c r="B23" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>428763</v>
+        <v>428394</v>
       </c>
       <c r="R23" t="n">
-        <v>6799813</v>
+        <v>6799781</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3007,7 +3012,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3017,7 +3022,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3044,10 +3049,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127035403</v>
+        <v>127034314</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>78777</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3055,21 +3060,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3079,13 +3084,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>428610</v>
+        <v>428856</v>
       </c>
       <c r="R24" t="n">
-        <v>6800197</v>
+        <v>6800220</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3114,7 +3119,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3124,7 +3129,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3151,10 +3156,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127033349</v>
+        <v>127031042</v>
       </c>
       <c r="B25" t="n">
-        <v>57658</v>
+        <v>78777</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3162,42 +3167,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>428792</v>
+        <v>428677</v>
       </c>
       <c r="R25" t="n">
-        <v>6799956</v>
+        <v>6799834</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3263,53 +3263,53 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127028936</v>
+        <v>127033349</v>
       </c>
       <c r="B26" t="n">
-        <v>8450</v>
+        <v>57658</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>428394</v>
+        <v>428792</v>
       </c>
       <c r="R26" t="n">
-        <v>6799781</v>
+        <v>6799956</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3803,10 +3803,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127035723</v>
+        <v>127030793</v>
       </c>
       <c r="B31" t="n">
-        <v>91350</v>
+        <v>56844</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3814,37 +3814,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>102612</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>428586</v>
+        <v>428603</v>
       </c>
       <c r="R31" t="n">
-        <v>6800175</v>
+        <v>6799810</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3873,7 +3878,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3883,7 +3888,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3910,10 +3915,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127030793</v>
+        <v>127035723</v>
       </c>
       <c r="B32" t="n">
-        <v>56844</v>
+        <v>91350</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3921,42 +3926,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102612</v>
+        <v>5442</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>428603</v>
+        <v>428586</v>
       </c>
       <c r="R32" t="n">
-        <v>6799810</v>
+        <v>6800175</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4883,10 +4883,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127032393</v>
+        <v>127032439</v>
       </c>
       <c r="B41" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4894,21 +4894,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4918,10 +4918,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>428755</v>
+        <v>428752</v>
       </c>
       <c r="R41" t="n">
-        <v>6799817</v>
+        <v>6799795</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4990,10 +4990,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127032439</v>
+        <v>127032393</v>
       </c>
       <c r="B42" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5001,21 +5001,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>428752</v>
+        <v>428755</v>
       </c>
       <c r="R42" t="n">
-        <v>6799795</v>
+        <v>6799817</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5525,10 +5525,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127030990</v>
+        <v>127034565</v>
       </c>
       <c r="B47" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5536,21 +5536,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5560,13 +5560,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>428677</v>
+        <v>428780</v>
       </c>
       <c r="R47" t="n">
-        <v>6799834</v>
+        <v>6800319</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5632,10 +5632,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127034565</v>
+        <v>127030990</v>
       </c>
       <c r="B48" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5643,21 +5643,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5667,13 +5667,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>428780</v>
+        <v>428677</v>
       </c>
       <c r="R48" t="n">
-        <v>6800319</v>
+        <v>6799834</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6172,10 +6172,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127035441</v>
+        <v>127034263</v>
       </c>
       <c r="B53" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6183,42 +6183,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>428586</v>
+        <v>428826</v>
       </c>
       <c r="R53" t="n">
-        <v>6800175</v>
+        <v>6800180</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6247,7 +6242,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6257,7 +6252,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Garnlav mer eller mindre över hela området.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6284,10 +6284,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127033102</v>
+        <v>127035441</v>
       </c>
       <c r="B54" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6295,37 +6295,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>428821</v>
+        <v>428586</v>
       </c>
       <c r="R54" t="n">
-        <v>6799886</v>
+        <v>6800175</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6354,7 +6359,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6364,7 +6369,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6391,7 +6396,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127034263</v>
+        <v>127033102</v>
       </c>
       <c r="B55" t="n">
         <v>79018</v>
@@ -6426,10 +6431,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>428826</v>
+        <v>428821</v>
       </c>
       <c r="R55" t="n">
-        <v>6800180</v>
+        <v>6799886</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6461,7 +6466,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6471,12 +6476,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Garnlav mer eller mindre över hela området.</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -1862,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127033222</v>
+        <v>127028962</v>
       </c>
       <c r="B13" t="n">
-        <v>78776</v>
+        <v>78777</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,34 +1873,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>428831</v>
+        <v>428394</v>
       </c>
       <c r="R13" t="n">
-        <v>6799894</v>
+        <v>6799781</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127033062</v>
+        <v>127033222</v>
       </c>
       <c r="B14" t="n">
-        <v>57658</v>
+        <v>78776</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,42 +1980,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>428840</v>
+        <v>428831</v>
       </c>
       <c r="R14" t="n">
-        <v>6799855</v>
+        <v>6799894</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2044,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,7 +2049,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127029492</v>
+        <v>127033062</v>
       </c>
       <c r="B15" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,34 +2087,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>428422</v>
+        <v>428840</v>
       </c>
       <c r="R15" t="n">
-        <v>6799802</v>
+        <v>6799855</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2188,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127028962</v>
+        <v>127029492</v>
       </c>
       <c r="B16" t="n">
-        <v>78777</v>
+        <v>79018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,21 +2199,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2223,13 +2223,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>428394</v>
+        <v>428422</v>
       </c>
       <c r="R16" t="n">
-        <v>6799781</v>
+        <v>6799802</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -4129,10 +4129,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127035734</v>
+        <v>127033824</v>
       </c>
       <c r="B34" t="n">
-        <v>79018</v>
+        <v>78776</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4140,34 +4140,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>428511</v>
+        <v>428807</v>
       </c>
       <c r="R34" t="n">
-        <v>6799990</v>
+        <v>6800084</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4236,10 +4236,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127033824</v>
+        <v>127035734</v>
       </c>
       <c r="B35" t="n">
-        <v>78776</v>
+        <v>79018</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4247,34 +4247,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>428807</v>
+        <v>428511</v>
       </c>
       <c r="R35" t="n">
-        <v>6800084</v>
+        <v>6799990</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4664,10 +4664,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127033133</v>
+        <v>127026773</v>
       </c>
       <c r="B39" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4675,37 +4675,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>428813</v>
+        <v>428345</v>
       </c>
       <c r="R39" t="n">
-        <v>6799900</v>
+        <v>6799714</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4734,7 +4739,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4744,7 +4749,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4771,10 +4776,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127026773</v>
+        <v>127033133</v>
       </c>
       <c r="B40" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4782,42 +4787,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>428345</v>
+        <v>428813</v>
       </c>
       <c r="R40" t="n">
-        <v>6799714</v>
+        <v>6799900</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5846,10 +5846,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127032317</v>
+        <v>127034235</v>
       </c>
       <c r="B50" t="n">
-        <v>79018</v>
+        <v>57658</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5857,37 +5857,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>428727</v>
+        <v>428843</v>
       </c>
       <c r="R50" t="n">
-        <v>6799838</v>
+        <v>6800159</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5916,7 +5921,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5926,7 +5931,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5953,10 +5958,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127034235</v>
+        <v>127032317</v>
       </c>
       <c r="B51" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5964,42 +5969,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>428843</v>
+        <v>428727</v>
       </c>
       <c r="R51" t="n">
-        <v>6800159</v>
+        <v>6799838</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6172,48 +6172,53 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127034263</v>
+        <v>127033713</v>
       </c>
       <c r="B53" t="n">
-        <v>79018</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>428826</v>
+        <v>428806</v>
       </c>
       <c r="R53" t="n">
-        <v>6800180</v>
+        <v>6800045</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6242,7 +6247,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6252,12 +6257,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Garnlav mer eller mindre över hela området.</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6284,10 +6284,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127035441</v>
+        <v>127033102</v>
       </c>
       <c r="B54" t="n">
-        <v>57658</v>
+        <v>79018</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6295,42 +6295,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>428586</v>
+        <v>428821</v>
       </c>
       <c r="R54" t="n">
-        <v>6800175</v>
+        <v>6799886</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6359,7 +6354,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6369,7 +6364,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6396,7 +6391,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127033102</v>
+        <v>127034263</v>
       </c>
       <c r="B55" t="n">
         <v>79018</v>
@@ -6431,10 +6426,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>428821</v>
+        <v>428826</v>
       </c>
       <c r="R55" t="n">
-        <v>6799886</v>
+        <v>6800180</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6466,7 +6461,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6476,7 +6471,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Garnlav mer eller mindre över hela området.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6503,38 +6503,38 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127033713</v>
+        <v>127035441</v>
       </c>
       <c r="B56" t="n">
-        <v>8450</v>
+        <v>57658</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6543,10 +6543,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>428806</v>
+        <v>428586</v>
       </c>
       <c r="R56" t="n">
-        <v>6800045</v>
+        <v>6800175</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127034383</v>
+        <v>127036675</v>
       </c>
       <c r="B2" t="n">
-        <v>78777</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,37 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>428839</v>
+        <v>428222</v>
       </c>
       <c r="R2" t="n">
-        <v>6800310</v>
+        <v>6799847</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127029075</v>
+        <v>127034383</v>
       </c>
       <c r="B3" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,17 +813,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>428374</v>
+        <v>428839</v>
       </c>
       <c r="R3" t="n">
-        <v>6799811</v>
+        <v>6800310</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127036675</v>
+        <v>127029075</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>78779</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428222</v>
+        <v>428374</v>
       </c>
       <c r="R4" t="n">
-        <v>6799847</v>
+        <v>6799811</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -959,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,7 +999,7 @@
         <v>127035882</v>
       </c>
       <c r="B5" t="n">
-        <v>56853</v>
+        <v>56855</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127028288</v>
+        <v>127032866</v>
       </c>
       <c r="B6" t="n">
-        <v>79636</v>
+        <v>79021</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,37 +1119,37 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>230405</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>428389</v>
+        <v>428752</v>
       </c>
       <c r="R6" t="n">
-        <v>6799724</v>
+        <v>6799795</v>
       </c>
       <c r="S6" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127031272</v>
+        <v>127028820</v>
       </c>
       <c r="B7" t="n">
-        <v>79636</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,37 +1226,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>428677</v>
+        <v>428394</v>
       </c>
       <c r="R7" t="n">
-        <v>6799834</v>
+        <v>6799781</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1285,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,7 +1295,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i hela området.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1322,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127028820</v>
+        <v>127028288</v>
       </c>
       <c r="B8" t="n">
-        <v>79018</v>
+        <v>79638</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1333,21 +1338,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1357,13 +1362,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>428394</v>
+        <v>428389</v>
       </c>
       <c r="R8" t="n">
-        <v>6799781</v>
+        <v>6799724</v>
       </c>
       <c r="S8" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1392,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1402,12 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i hela området.</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127032866</v>
+        <v>127031272</v>
       </c>
       <c r="B9" t="n">
-        <v>79019</v>
+        <v>79638</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,21 +1445,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>230405</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,13 +1469,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>428752</v>
+        <v>428677</v>
       </c>
       <c r="R9" t="n">
-        <v>6799795</v>
+        <v>6799834</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1544,7 +1544,7 @@
         <v>127036174</v>
       </c>
       <c r="B10" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>127032352</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>127030417</v>
       </c>
       <c r="B12" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127028962</v>
+        <v>127033062</v>
       </c>
       <c r="B13" t="n">
-        <v>78777</v>
+        <v>57660</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,37 +1873,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>428394</v>
+        <v>428840</v>
       </c>
       <c r="R13" t="n">
-        <v>6799781</v>
+        <v>6799855</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1932,7 +1937,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1947,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,10 +1974,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127033222</v>
+        <v>127028962</v>
       </c>
       <c r="B14" t="n">
-        <v>78776</v>
+        <v>78779</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,34 +1985,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>428831</v>
+        <v>428394</v>
       </c>
       <c r="R14" t="n">
-        <v>6799894</v>
+        <v>6799781</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2039,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,7 +2054,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127033062</v>
+        <v>127033222</v>
       </c>
       <c r="B15" t="n">
-        <v>57658</v>
+        <v>78778</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2087,42 +2092,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>428840</v>
+        <v>428831</v>
       </c>
       <c r="R15" t="n">
-        <v>6799855</v>
+        <v>6799894</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2191,7 +2191,7 @@
         <v>127029492</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>127030319</v>
       </c>
       <c r="B17" t="n">
-        <v>79607</v>
+        <v>79609</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2402,10 +2402,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127028974</v>
+        <v>127033408</v>
       </c>
       <c r="B18" t="n">
-        <v>78776</v>
+        <v>79020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2413,37 +2413,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>428374</v>
+        <v>428788</v>
       </c>
       <c r="R18" t="n">
-        <v>6799811</v>
+        <v>6799983</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2509,10 +2509,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127033408</v>
+        <v>127028974</v>
       </c>
       <c r="B19" t="n">
-        <v>79018</v>
+        <v>78778</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,37 +2520,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>428788</v>
+        <v>428374</v>
       </c>
       <c r="R19" t="n">
-        <v>6799983</v>
+        <v>6799811</v>
       </c>
       <c r="S19" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2619,7 +2619,7 @@
         <v>127033867</v>
       </c>
       <c r="B20" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>127032907</v>
       </c>
       <c r="B21" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2833,7 +2833,7 @@
         <v>127035403</v>
       </c>
       <c r="B22" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2937,53 +2937,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127028936</v>
+        <v>127033349</v>
       </c>
       <c r="B23" t="n">
-        <v>8450</v>
+        <v>57660</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>428394</v>
+        <v>428792</v>
       </c>
       <c r="R23" t="n">
-        <v>6799781</v>
+        <v>6799956</v>
       </c>
       <c r="S23" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3049,45 +3049,50 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127034314</v>
+        <v>127028936</v>
       </c>
       <c r="B24" t="n">
-        <v>78777</v>
+        <v>8450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>106545</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>428856</v>
+        <v>428394</v>
       </c>
       <c r="R24" t="n">
-        <v>6800220</v>
+        <v>6799781</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3119,7 +3124,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3129,7 +3134,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3156,10 +3161,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127031042</v>
+        <v>127034314</v>
       </c>
       <c r="B25" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3191,13 +3196,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>428677</v>
+        <v>428856</v>
       </c>
       <c r="R25" t="n">
-        <v>6799834</v>
+        <v>6800220</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3226,7 +3231,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3236,7 +3241,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3263,10 +3268,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127033349</v>
+        <v>127031042</v>
       </c>
       <c r="B26" t="n">
-        <v>57658</v>
+        <v>78779</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3274,42 +3279,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>428792</v>
+        <v>428677</v>
       </c>
       <c r="R26" t="n">
-        <v>6799956</v>
+        <v>6799834</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3378,7 +3378,7 @@
         <v>127031710</v>
       </c>
       <c r="B27" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3482,10 +3482,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127034644</v>
+        <v>127028434</v>
       </c>
       <c r="B28" t="n">
-        <v>91350</v>
+        <v>79020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3493,37 +3493,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>428786</v>
+        <v>428388</v>
       </c>
       <c r="R28" t="n">
-        <v>6800327</v>
+        <v>6799765</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3589,10 +3589,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127033497</v>
+        <v>127034644</v>
       </c>
       <c r="B29" t="n">
-        <v>79018</v>
+        <v>91352</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3600,21 +3600,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3624,10 +3624,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>428803</v>
+        <v>428786</v>
       </c>
       <c r="R29" t="n">
-        <v>6799992</v>
+        <v>6800327</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3696,10 +3696,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127028434</v>
+        <v>127033497</v>
       </c>
       <c r="B30" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3727,17 +3727,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>428388</v>
+        <v>428803</v>
       </c>
       <c r="R30" t="n">
-        <v>6799765</v>
+        <v>6799992</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3803,10 +3803,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127030793</v>
+        <v>127035723</v>
       </c>
       <c r="B31" t="n">
-        <v>56844</v>
+        <v>91352</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3814,42 +3814,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102612</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>428603</v>
+        <v>428586</v>
       </c>
       <c r="R31" t="n">
-        <v>6799810</v>
+        <v>6800175</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3878,7 +3873,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3888,7 +3883,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3915,10 +3910,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127035723</v>
+        <v>127030793</v>
       </c>
       <c r="B32" t="n">
-        <v>91350</v>
+        <v>56846</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3926,37 +3921,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>102612</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>428586</v>
+        <v>428603</v>
       </c>
       <c r="R32" t="n">
-        <v>6800175</v>
+        <v>6799810</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4025,7 +4025,7 @@
         <v>127034901</v>
       </c>
       <c r="B33" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>127033824</v>
       </c>
       <c r="B34" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4239,7 +4239,7 @@
         <v>127035734</v>
       </c>
       <c r="B35" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4343,10 +4343,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127030918</v>
+        <v>127034208</v>
       </c>
       <c r="B36" t="n">
-        <v>78776</v>
+        <v>79020</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4354,37 +4354,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>428644</v>
+        <v>428809</v>
       </c>
       <c r="R36" t="n">
-        <v>6799825</v>
+        <v>6800173</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4453,7 +4453,7 @@
         <v>127036021</v>
       </c>
       <c r="B37" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4557,10 +4557,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127034208</v>
+        <v>127030918</v>
       </c>
       <c r="B38" t="n">
-        <v>79018</v>
+        <v>78778</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4568,37 +4568,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>428809</v>
+        <v>428644</v>
       </c>
       <c r="R38" t="n">
-        <v>6800173</v>
+        <v>6799825</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4664,10 +4664,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127026773</v>
+        <v>127033133</v>
       </c>
       <c r="B39" t="n">
-        <v>57658</v>
+        <v>79020</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4675,42 +4675,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>428345</v>
+        <v>428813</v>
       </c>
       <c r="R39" t="n">
-        <v>6799714</v>
+        <v>6799900</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4739,7 +4734,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4749,7 +4744,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4776,10 +4771,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127033133</v>
+        <v>127026773</v>
       </c>
       <c r="B40" t="n">
-        <v>79018</v>
+        <v>57660</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4787,37 +4782,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>428813</v>
+        <v>428345</v>
       </c>
       <c r="R40" t="n">
-        <v>6799900</v>
+        <v>6799714</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4883,10 +4883,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>127032439</v>
+        <v>127032393</v>
       </c>
       <c r="B41" t="n">
-        <v>78776</v>
+        <v>79020</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4894,21 +4894,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4918,10 +4918,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>428752</v>
+        <v>428755</v>
       </c>
       <c r="R41" t="n">
-        <v>6799795</v>
+        <v>6799817</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4953,7 +4953,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:38</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4990,10 +4990,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>127032393</v>
+        <v>127032439</v>
       </c>
       <c r="B42" t="n">
-        <v>79018</v>
+        <v>78778</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5001,21 +5001,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5025,10 +5025,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>428755</v>
+        <v>428752</v>
       </c>
       <c r="R42" t="n">
-        <v>6799817</v>
+        <v>6799795</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5097,10 +5097,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127035229</v>
+        <v>127033191</v>
       </c>
       <c r="B43" t="n">
-        <v>79018</v>
+        <v>78779</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5108,21 +5108,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5132,10 +5132,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>428628</v>
+        <v>428831</v>
       </c>
       <c r="R43" t="n">
-        <v>6800237</v>
+        <v>6799894</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5204,10 +5204,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127034191</v>
+        <v>127030347</v>
       </c>
       <c r="B44" t="n">
-        <v>79018</v>
+        <v>78779</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5215,37 +5215,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>428821</v>
+        <v>428422</v>
       </c>
       <c r="R44" t="n">
-        <v>6800164</v>
+        <v>6799802</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5311,10 +5311,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127033191</v>
+        <v>127035229</v>
       </c>
       <c r="B45" t="n">
-        <v>78777</v>
+        <v>79020</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5322,21 +5322,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>428831</v>
+        <v>428628</v>
       </c>
       <c r="R45" t="n">
-        <v>6799894</v>
+        <v>6800237</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5418,10 +5418,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127030347</v>
+        <v>127034191</v>
       </c>
       <c r="B46" t="n">
-        <v>78777</v>
+        <v>79020</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5429,37 +5429,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>428422</v>
+        <v>428821</v>
       </c>
       <c r="R46" t="n">
-        <v>6799802</v>
+        <v>6800164</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5525,10 +5525,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127034565</v>
+        <v>127030905</v>
       </c>
       <c r="B47" t="n">
-        <v>79018</v>
+        <v>78779</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5536,37 +5536,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>428780</v>
+        <v>428635</v>
       </c>
       <c r="R47" t="n">
-        <v>6800319</v>
+        <v>6799822</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5632,10 +5632,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127030990</v>
+        <v>127034565</v>
       </c>
       <c r="B48" t="n">
-        <v>78776</v>
+        <v>79020</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5643,21 +5643,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5667,13 +5667,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>428677</v>
+        <v>428780</v>
       </c>
       <c r="R48" t="n">
-        <v>6799834</v>
+        <v>6800319</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5739,10 +5739,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127030905</v>
+        <v>127030990</v>
       </c>
       <c r="B49" t="n">
-        <v>78777</v>
+        <v>78778</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5750,34 +5750,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>428635</v>
+        <v>428677</v>
       </c>
       <c r="R49" t="n">
-        <v>6799822</v>
+        <v>6799834</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5846,10 +5846,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127034235</v>
+        <v>127032317</v>
       </c>
       <c r="B50" t="n">
-        <v>57658</v>
+        <v>79020</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5857,42 +5857,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>428843</v>
+        <v>428727</v>
       </c>
       <c r="R50" t="n">
-        <v>6800159</v>
+        <v>6799838</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5921,7 +5916,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5931,7 +5926,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5958,10 +5953,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127032317</v>
+        <v>127034235</v>
       </c>
       <c r="B51" t="n">
-        <v>79018</v>
+        <v>57660</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5969,37 +5964,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>428727</v>
+        <v>428843</v>
       </c>
       <c r="R51" t="n">
-        <v>6799838</v>
+        <v>6800159</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6068,7 +6068,7 @@
         <v>127027998</v>
       </c>
       <c r="B52" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6172,53 +6172,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127033713</v>
+        <v>127034263</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>428806</v>
+        <v>428826</v>
       </c>
       <c r="R53" t="n">
-        <v>6800045</v>
+        <v>6800180</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6247,7 +6242,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6257,7 +6252,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Garnlav mer eller mindre över hela området.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6287,7 +6287,7 @@
         <v>127033102</v>
       </c>
       <c r="B54" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6391,10 +6391,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127034263</v>
+        <v>127035441</v>
       </c>
       <c r="B55" t="n">
-        <v>79018</v>
+        <v>57660</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6402,37 +6402,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>428826</v>
+        <v>428586</v>
       </c>
       <c r="R55" t="n">
-        <v>6800180</v>
+        <v>6800175</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6461,7 +6466,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6471,12 +6476,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Garnlav mer eller mindre över hela området.</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6503,38 +6503,38 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127035441</v>
+        <v>127033713</v>
       </c>
       <c r="B56" t="n">
-        <v>57658</v>
+        <v>8450</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="M56" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -6543,10 +6543,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>428586</v>
+        <v>428806</v>
       </c>
       <c r="R56" t="n">
-        <v>6800175</v>
+        <v>6800045</v>
       </c>
       <c r="S56" t="n">
         <v>20</v>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6588,7 +6588,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -782,48 +782,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127034383</v>
+        <v>127035882</v>
       </c>
       <c r="B3" t="n">
-        <v>78779</v>
+        <v>56855</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>428839</v>
+        <v>428512</v>
       </c>
       <c r="R3" t="n">
-        <v>6800310</v>
+        <v>6799960</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,7 +894,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127029075</v>
+        <v>127034383</v>
       </c>
       <c r="B4" t="n">
         <v>78779</v>
@@ -920,17 +925,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428374</v>
+        <v>428839</v>
       </c>
       <c r="R4" t="n">
-        <v>6799811</v>
+        <v>6800310</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -959,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -969,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -996,53 +1001,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127035882</v>
+        <v>127029075</v>
       </c>
       <c r="B5" t="n">
-        <v>56855</v>
+        <v>78779</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428512</v>
+        <v>428374</v>
       </c>
       <c r="R5" t="n">
-        <v>6799960</v>
+        <v>6799811</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127032866</v>
+        <v>127028820</v>
       </c>
       <c r="B6" t="n">
-        <v>79021</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,16 +1119,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1139,17 +1139,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>428752</v>
+        <v>428394</v>
       </c>
       <c r="R6" t="n">
-        <v>6799795</v>
+        <v>6799781</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i hela området.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127028820</v>
+        <v>127028288</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,21 +1231,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,13 +1255,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>428394</v>
+        <v>428389</v>
       </c>
       <c r="R7" t="n">
-        <v>6799781</v>
+        <v>6799724</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1285,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,12 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i hela området.</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,7 +1327,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127028288</v>
+        <v>127031272</v>
       </c>
       <c r="B8" t="n">
         <v>79638</v>
@@ -1358,14 +1358,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>428389</v>
+        <v>428677</v>
       </c>
       <c r="R8" t="n">
-        <v>6799724</v>
+        <v>6799834</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127031272</v>
+        <v>127032866</v>
       </c>
       <c r="B9" t="n">
-        <v>79638</v>
+        <v>79021</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,21 +1445,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>230405</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,13 +1469,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>428677</v>
+        <v>428752</v>
       </c>
       <c r="R9" t="n">
-        <v>6799834</v>
+        <v>6799795</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1862,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127033062</v>
+        <v>127028962</v>
       </c>
       <c r="B13" t="n">
-        <v>57660</v>
+        <v>78779</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,42 +1873,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>428840</v>
+        <v>428394</v>
       </c>
       <c r="R13" t="n">
-        <v>6799855</v>
+        <v>6799781</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1937,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1947,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127028962</v>
+        <v>127029492</v>
       </c>
       <c r="B14" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,21 +1980,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2009,13 +2004,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>428394</v>
+        <v>428422</v>
       </c>
       <c r="R14" t="n">
-        <v>6799781</v>
+        <v>6799802</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2044,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,7 +2049,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2188,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127029492</v>
+        <v>127033062</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,34 +2194,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>428422</v>
+        <v>428840</v>
       </c>
       <c r="R16" t="n">
-        <v>6799802</v>
+        <v>6799855</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127030319</v>
+        <v>127028974</v>
       </c>
       <c r="B17" t="n">
-        <v>79609</v>
+        <v>78778</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2306,21 +2306,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2330,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>428422</v>
+        <v>428374</v>
       </c>
       <c r="R17" t="n">
-        <v>6799802</v>
+        <v>6799811</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2509,10 +2509,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127028974</v>
+        <v>127030319</v>
       </c>
       <c r="B19" t="n">
-        <v>78778</v>
+        <v>79609</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,21 +2520,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>428374</v>
+        <v>428422</v>
       </c>
       <c r="R19" t="n">
-        <v>6799811</v>
+        <v>6799802</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2616,10 +2616,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127033867</v>
+        <v>127032907</v>
       </c>
       <c r="B20" t="n">
-        <v>78778</v>
+        <v>79020</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2627,21 +2627,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2651,13 +2651,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>428801</v>
+        <v>428763</v>
       </c>
       <c r="R20" t="n">
-        <v>6800075</v>
+        <v>6799813</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2696,7 +2696,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2723,10 +2723,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127032907</v>
+        <v>127033867</v>
       </c>
       <c r="B21" t="n">
-        <v>79020</v>
+        <v>78778</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2734,21 +2734,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2758,13 +2758,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>428763</v>
+        <v>428801</v>
       </c>
       <c r="R21" t="n">
-        <v>6799813</v>
+        <v>6800075</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2803,7 +2803,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4129,10 +4129,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127033824</v>
+        <v>127035734</v>
       </c>
       <c r="B34" t="n">
-        <v>78778</v>
+        <v>79020</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4140,34 +4140,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>428807</v>
+        <v>428511</v>
       </c>
       <c r="R34" t="n">
-        <v>6800084</v>
+        <v>6799990</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4236,10 +4236,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127035734</v>
+        <v>127033824</v>
       </c>
       <c r="B35" t="n">
-        <v>79020</v>
+        <v>78778</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4247,34 +4247,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>428511</v>
+        <v>428807</v>
       </c>
       <c r="R35" t="n">
-        <v>6799990</v>
+        <v>6800084</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4343,10 +4343,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>127034208</v>
+        <v>127030918</v>
       </c>
       <c r="B36" t="n">
-        <v>79020</v>
+        <v>78778</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4354,37 +4354,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>428809</v>
+        <v>428644</v>
       </c>
       <c r="R36" t="n">
-        <v>6800173</v>
+        <v>6799825</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:07</t>
+          <t>15:25</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4557,10 +4557,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>127030918</v>
+        <v>127034208</v>
       </c>
       <c r="B38" t="n">
-        <v>78778</v>
+        <v>79020</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4568,37 +4568,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>428644</v>
+        <v>428809</v>
       </c>
       <c r="R38" t="n">
-        <v>6799825</v>
+        <v>6800173</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4627,7 +4627,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4637,7 +4637,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:25</t>
+          <t>18:07</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5097,10 +5097,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>127033191</v>
+        <v>127035229</v>
       </c>
       <c r="B43" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5108,21 +5108,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5132,10 +5132,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>428831</v>
+        <v>428628</v>
       </c>
       <c r="R43" t="n">
-        <v>6799894</v>
+        <v>6800237</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:57</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5204,10 +5204,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127030347</v>
+        <v>127034191</v>
       </c>
       <c r="B44" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5215,37 +5215,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>428422</v>
+        <v>428821</v>
       </c>
       <c r="R44" t="n">
-        <v>6799802</v>
+        <v>6800164</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5311,10 +5311,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127035229</v>
+        <v>127033191</v>
       </c>
       <c r="B45" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5322,21 +5322,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5346,10 +5346,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>428628</v>
+        <v>428831</v>
       </c>
       <c r="R45" t="n">
-        <v>6800237</v>
+        <v>6799894</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>18:57</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5418,10 +5418,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127034191</v>
+        <v>127030347</v>
       </c>
       <c r="B46" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5429,37 +5429,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>428821</v>
+        <v>428422</v>
       </c>
       <c r="R46" t="n">
-        <v>6800164</v>
+        <v>6799802</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5525,10 +5525,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127030905</v>
+        <v>127034565</v>
       </c>
       <c r="B47" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5536,37 +5536,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>428635</v>
+        <v>428780</v>
       </c>
       <c r="R47" t="n">
-        <v>6799822</v>
+        <v>6800319</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5632,10 +5632,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127034565</v>
+        <v>127030990</v>
       </c>
       <c r="B48" t="n">
-        <v>79020</v>
+        <v>78778</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5643,21 +5643,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5667,13 +5667,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>428780</v>
+        <v>428677</v>
       </c>
       <c r="R48" t="n">
-        <v>6800319</v>
+        <v>6799834</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5739,10 +5739,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127030990</v>
+        <v>127030905</v>
       </c>
       <c r="B49" t="n">
-        <v>78778</v>
+        <v>78779</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5750,34 +5750,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>428677</v>
+        <v>428635</v>
       </c>
       <c r="R49" t="n">
-        <v>6799834</v>
+        <v>6799822</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6172,7 +6172,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127034263</v>
+        <v>127033102</v>
       </c>
       <c r="B53" t="n">
         <v>79020</v>
@@ -6207,10 +6207,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>428826</v>
+        <v>428821</v>
       </c>
       <c r="R53" t="n">
-        <v>6800180</v>
+        <v>6799886</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6252,12 +6252,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Garnlav mer eller mindre över hela området.</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6284,7 +6279,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127033102</v>
+        <v>127034263</v>
       </c>
       <c r="B54" t="n">
         <v>79020</v>
@@ -6319,10 +6314,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>428821</v>
+        <v>428826</v>
       </c>
       <c r="R54" t="n">
-        <v>6799886</v>
+        <v>6800180</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6354,7 +6349,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6364,7 +6359,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Garnlav mer eller mindre över hela området.</t>
         </is>
       </c>
       <c r="AD54" t="b">

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -1862,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127028962</v>
+        <v>127029492</v>
       </c>
       <c r="B13" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,21 +1873,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,13 +1897,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>428394</v>
+        <v>428422</v>
       </c>
       <c r="R13" t="n">
-        <v>6799781</v>
+        <v>6799802</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1969,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127029492</v>
+        <v>127033222</v>
       </c>
       <c r="B14" t="n">
-        <v>79020</v>
+        <v>78778</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1980,37 +1980,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>428422</v>
+        <v>428831</v>
       </c>
       <c r="R14" t="n">
-        <v>6799802</v>
+        <v>6799894</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2039,7 +2039,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2076,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127033222</v>
+        <v>127033062</v>
       </c>
       <c r="B15" t="n">
-        <v>78778</v>
+        <v>57660</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2087,37 +2087,42 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>428831</v>
+        <v>428840</v>
       </c>
       <c r="R15" t="n">
-        <v>6799894</v>
+        <v>6799855</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2146,7 +2151,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2156,7 +2161,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2183,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127033062</v>
+        <v>127028962</v>
       </c>
       <c r="B16" t="n">
-        <v>57660</v>
+        <v>78779</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2194,42 +2199,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>428840</v>
+        <v>428394</v>
       </c>
       <c r="R16" t="n">
-        <v>6799855</v>
+        <v>6799781</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127028974</v>
+        <v>127030319</v>
       </c>
       <c r="B17" t="n">
-        <v>78778</v>
+        <v>79609</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2306,21 +2306,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2330,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>428374</v>
+        <v>428422</v>
       </c>
       <c r="R17" t="n">
-        <v>6799811</v>
+        <v>6799802</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2402,10 +2402,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127033408</v>
+        <v>127028974</v>
       </c>
       <c r="B18" t="n">
-        <v>79020</v>
+        <v>78778</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2413,37 +2413,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>428788</v>
+        <v>428374</v>
       </c>
       <c r="R18" t="n">
-        <v>6799983</v>
+        <v>6799811</v>
       </c>
       <c r="S18" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2509,10 +2509,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127030319</v>
+        <v>127033408</v>
       </c>
       <c r="B19" t="n">
-        <v>79609</v>
+        <v>79020</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,37 +2520,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>428422</v>
+        <v>428788</v>
       </c>
       <c r="R19" t="n">
-        <v>6799802</v>
+        <v>6799983</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3482,10 +3482,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127028434</v>
+        <v>127034644</v>
       </c>
       <c r="B28" t="n">
-        <v>79020</v>
+        <v>91352</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3493,37 +3493,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>428388</v>
+        <v>428786</v>
       </c>
       <c r="R28" t="n">
-        <v>6799765</v>
+        <v>6800327</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3589,10 +3589,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127034644</v>
+        <v>127033497</v>
       </c>
       <c r="B29" t="n">
-        <v>91352</v>
+        <v>79020</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3600,21 +3600,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3624,10 +3624,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>428786</v>
+        <v>428803</v>
       </c>
       <c r="R29" t="n">
-        <v>6800327</v>
+        <v>6799992</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3696,7 +3696,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127033497</v>
+        <v>127028434</v>
       </c>
       <c r="B30" t="n">
         <v>79020</v>
@@ -3727,17 +3727,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>428803</v>
+        <v>428388</v>
       </c>
       <c r="R30" t="n">
-        <v>6799992</v>
+        <v>6799765</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3803,10 +3803,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127035723</v>
+        <v>127030793</v>
       </c>
       <c r="B31" t="n">
-        <v>91352</v>
+        <v>56846</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3814,37 +3814,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>102612</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>428586</v>
+        <v>428603</v>
       </c>
       <c r="R31" t="n">
-        <v>6800175</v>
+        <v>6799810</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3873,7 +3878,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3883,7 +3888,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3910,10 +3915,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127030793</v>
+        <v>127035723</v>
       </c>
       <c r="B32" t="n">
-        <v>56846</v>
+        <v>91352</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3921,42 +3926,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102612</v>
+        <v>5442</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>428603</v>
+        <v>428586</v>
       </c>
       <c r="R32" t="n">
-        <v>6799810</v>
+        <v>6800175</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5846,10 +5846,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127032317</v>
+        <v>127034235</v>
       </c>
       <c r="B50" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5857,37 +5857,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>428727</v>
+        <v>428843</v>
       </c>
       <c r="R50" t="n">
-        <v>6799838</v>
+        <v>6800159</v>
       </c>
       <c r="S50" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5916,7 +5921,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5926,7 +5931,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5953,10 +5958,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127034235</v>
+        <v>127032317</v>
       </c>
       <c r="B51" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5964,42 +5969,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>428843</v>
+        <v>428727</v>
       </c>
       <c r="R51" t="n">
-        <v>6800159</v>
+        <v>6799838</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6279,10 +6279,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127034263</v>
+        <v>127035441</v>
       </c>
       <c r="B54" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6290,37 +6290,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>428826</v>
+        <v>428586</v>
       </c>
       <c r="R54" t="n">
-        <v>6800180</v>
+        <v>6800175</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6349,7 +6354,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6359,12 +6364,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Garnlav mer eller mindre över hela området.</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6391,10 +6391,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127035441</v>
+        <v>127034263</v>
       </c>
       <c r="B55" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6402,42 +6402,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>428586</v>
+        <v>428826</v>
       </c>
       <c r="R55" t="n">
-        <v>6800175</v>
+        <v>6800180</v>
       </c>
       <c r="S55" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6466,7 +6461,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6476,7 +6471,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Garnlav mer eller mindre över hela området.</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -675,48 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127036675</v>
+        <v>127035882</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>56855</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>428222</v>
+        <v>428512</v>
       </c>
       <c r="R2" t="n">
-        <v>6799847</v>
+        <v>6799960</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,53 +787,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127035882</v>
+        <v>127036675</v>
       </c>
       <c r="B3" t="n">
-        <v>56855</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>428512</v>
+        <v>428222</v>
       </c>
       <c r="R3" t="n">
-        <v>6799960</v>
+        <v>6799847</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127028820</v>
+        <v>127032866</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>79021</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,16 +1119,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>230405</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1139,17 +1139,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>428394</v>
+        <v>428752</v>
       </c>
       <c r="R6" t="n">
-        <v>6799781</v>
+        <v>6799795</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,12 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i hela området.</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127028288</v>
+        <v>127028820</v>
       </c>
       <c r="B7" t="n">
-        <v>79638</v>
+        <v>79020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,21 +1226,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1255,13 +1250,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>428389</v>
+        <v>428394</v>
       </c>
       <c r="R7" t="n">
-        <v>6799724</v>
+        <v>6799781</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1290,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1295,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i hela området.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,7 +1327,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127031272</v>
+        <v>127028288</v>
       </c>
       <c r="B8" t="n">
         <v>79638</v>
@@ -1358,14 +1358,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>428677</v>
+        <v>428389</v>
       </c>
       <c r="R8" t="n">
-        <v>6799834</v>
+        <v>6799724</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127032866</v>
+        <v>127031272</v>
       </c>
       <c r="B9" t="n">
-        <v>79021</v>
+        <v>79638</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,21 +1445,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>230405</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,13 +1469,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>428752</v>
+        <v>428677</v>
       </c>
       <c r="R9" t="n">
-        <v>6799795</v>
+        <v>6799834</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1862,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127029492</v>
+        <v>127028962</v>
       </c>
       <c r="B13" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,21 +1873,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1897,13 +1897,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>428422</v>
+        <v>428394</v>
       </c>
       <c r="R13" t="n">
-        <v>6799802</v>
+        <v>6799781</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2076,10 +2076,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127033062</v>
+        <v>127029492</v>
       </c>
       <c r="B15" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2087,39 +2087,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>428840</v>
+        <v>428422</v>
       </c>
       <c r="R15" t="n">
-        <v>6799855</v>
+        <v>6799802</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2151,7 +2146,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2161,7 +2156,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2188,10 +2183,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127028962</v>
+        <v>127033062</v>
       </c>
       <c r="B16" t="n">
-        <v>78779</v>
+        <v>57660</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2199,37 +2194,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>428394</v>
+        <v>428840</v>
       </c>
       <c r="R16" t="n">
-        <v>6799781</v>
+        <v>6799855</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127030319</v>
+        <v>127028974</v>
       </c>
       <c r="B17" t="n">
-        <v>79609</v>
+        <v>78778</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2306,21 +2306,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2330,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>428422</v>
+        <v>428374</v>
       </c>
       <c r="R17" t="n">
-        <v>6799802</v>
+        <v>6799811</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2402,10 +2402,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127028974</v>
+        <v>127033408</v>
       </c>
       <c r="B18" t="n">
-        <v>78778</v>
+        <v>79020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2413,37 +2413,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>428374</v>
+        <v>428788</v>
       </c>
       <c r="R18" t="n">
-        <v>6799811</v>
+        <v>6799983</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2482,7 +2482,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2509,10 +2509,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127033408</v>
+        <v>127030319</v>
       </c>
       <c r="B19" t="n">
-        <v>79020</v>
+        <v>79609</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,37 +2520,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>428788</v>
+        <v>428422</v>
       </c>
       <c r="R19" t="n">
-        <v>6799983</v>
+        <v>6799802</v>
       </c>
       <c r="S19" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2616,10 +2616,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127032907</v>
+        <v>127033349</v>
       </c>
       <c r="B20" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2627,34 +2627,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>428763</v>
+        <v>428792</v>
       </c>
       <c r="R20" t="n">
-        <v>6799813</v>
+        <v>6799956</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2686,7 +2691,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2696,7 +2701,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2830,7 +2835,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127035403</v>
+        <v>127032907</v>
       </c>
       <c r="B22" t="n">
         <v>79020</v>
@@ -2865,10 +2870,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>428610</v>
+        <v>428763</v>
       </c>
       <c r="R22" t="n">
-        <v>6800197</v>
+        <v>6799813</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2900,7 +2905,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2910,7 +2915,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2937,10 +2942,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127033349</v>
+        <v>127035403</v>
       </c>
       <c r="B23" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2948,39 +2953,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>428792</v>
+        <v>428610</v>
       </c>
       <c r="R23" t="n">
-        <v>6799956</v>
+        <v>6800197</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3482,10 +3482,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127034644</v>
+        <v>127033497</v>
       </c>
       <c r="B28" t="n">
-        <v>91352</v>
+        <v>79020</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3493,21 +3493,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>428786</v>
+        <v>428803</v>
       </c>
       <c r="R28" t="n">
-        <v>6800327</v>
+        <v>6799992</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3589,7 +3589,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127033497</v>
+        <v>127028434</v>
       </c>
       <c r="B29" t="n">
         <v>79020</v>
@@ -3620,17 +3620,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>428803</v>
+        <v>428388</v>
       </c>
       <c r="R29" t="n">
-        <v>6799992</v>
+        <v>6799765</v>
       </c>
       <c r="S29" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3696,10 +3696,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127028434</v>
+        <v>127034644</v>
       </c>
       <c r="B30" t="n">
-        <v>79020</v>
+        <v>91352</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3707,37 +3707,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>428388</v>
+        <v>428786</v>
       </c>
       <c r="R30" t="n">
-        <v>6799765</v>
+        <v>6800327</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -5846,10 +5846,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>127034235</v>
+        <v>127032317</v>
       </c>
       <c r="B50" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5857,42 +5857,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>428843</v>
+        <v>428727</v>
       </c>
       <c r="R50" t="n">
-        <v>6800159</v>
+        <v>6799838</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5921,7 +5916,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5931,7 +5926,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5958,10 +5953,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>127032317</v>
+        <v>127034235</v>
       </c>
       <c r="B51" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5969,37 +5964,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>428727</v>
+        <v>428843</v>
       </c>
       <c r="R51" t="n">
-        <v>6799838</v>
+        <v>6800159</v>
       </c>
       <c r="S51" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6038,7 +6038,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6279,10 +6279,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127035441</v>
+        <v>127034263</v>
       </c>
       <c r="B54" t="n">
-        <v>57660</v>
+        <v>79020</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6290,42 +6290,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>428586</v>
+        <v>428826</v>
       </c>
       <c r="R54" t="n">
-        <v>6800175</v>
+        <v>6800180</v>
       </c>
       <c r="S54" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6354,7 +6349,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6364,7 +6359,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Garnlav mer eller mindre över hela området.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6391,10 +6391,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>127034263</v>
+        <v>127035441</v>
       </c>
       <c r="B55" t="n">
-        <v>79020</v>
+        <v>57660</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6402,37 +6402,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>428826</v>
+        <v>428586</v>
       </c>
       <c r="R55" t="n">
-        <v>6800180</v>
+        <v>6800175</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6461,7 +6466,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6471,12 +6476,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Garnlav mer eller mindre över hela området.</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD55" t="b">

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127035882</v>
+        <v>127036675</v>
       </c>
       <c r="B2" t="n">
-        <v>56855</v>
+        <v>79020</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>428512</v>
+        <v>428222</v>
       </c>
       <c r="R2" t="n">
-        <v>6799960</v>
+        <v>6799847</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,48 +782,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127036675</v>
+        <v>127035882</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>56855</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>428222</v>
+        <v>428512</v>
       </c>
       <c r="R3" t="n">
-        <v>6799847</v>
+        <v>6799960</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>20:05</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127032866</v>
+        <v>127028820</v>
       </c>
       <c r="B6" t="n">
-        <v>79021</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,16 +1119,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>230405</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1139,17 +1139,17 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>428752</v>
+        <v>428394</v>
       </c>
       <c r="R6" t="n">
-        <v>6799795</v>
+        <v>6799781</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,7 +1188,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i hela området.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1215,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127028820</v>
+        <v>127028288</v>
       </c>
       <c r="B7" t="n">
-        <v>79020</v>
+        <v>79638</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1226,21 +1231,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1250,13 +1255,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>428394</v>
+        <v>428389</v>
       </c>
       <c r="R7" t="n">
-        <v>6799781</v>
+        <v>6799724</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1285,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1295,12 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i hela området.</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,7 +1327,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127028288</v>
+        <v>127031272</v>
       </c>
       <c r="B8" t="n">
         <v>79638</v>
@@ -1358,14 +1358,14 @@
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>428389</v>
+        <v>428677</v>
       </c>
       <c r="R8" t="n">
-        <v>6799724</v>
+        <v>6799834</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1434,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127031272</v>
+        <v>127032866</v>
       </c>
       <c r="B9" t="n">
-        <v>79638</v>
+        <v>79021</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1445,21 +1445,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>230405</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1469,13 +1469,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>428677</v>
+        <v>428752</v>
       </c>
       <c r="R9" t="n">
-        <v>6799834</v>
+        <v>6799795</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1514,7 +1514,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1862,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127028962</v>
+        <v>127033062</v>
       </c>
       <c r="B13" t="n">
-        <v>78779</v>
+        <v>57660</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,37 +1873,42 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>428394</v>
+        <v>428840</v>
       </c>
       <c r="R13" t="n">
-        <v>6799781</v>
+        <v>6799855</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1932,7 +1937,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1942,7 +1947,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2183,10 +2188,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127033062</v>
+        <v>127028962</v>
       </c>
       <c r="B16" t="n">
-        <v>57660</v>
+        <v>78779</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2194,42 +2199,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>428840</v>
+        <v>428394</v>
       </c>
       <c r="R16" t="n">
-        <v>6799855</v>
+        <v>6799781</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2268,7 +2268,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2295,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127028974</v>
+        <v>127030319</v>
       </c>
       <c r="B17" t="n">
-        <v>78778</v>
+        <v>79609</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2306,21 +2306,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2330,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>428374</v>
+        <v>428422</v>
       </c>
       <c r="R17" t="n">
-        <v>6799811</v>
+        <v>6799802</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2509,10 +2509,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127030319</v>
+        <v>127028974</v>
       </c>
       <c r="B19" t="n">
-        <v>79609</v>
+        <v>78778</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,21 +2520,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>428422</v>
+        <v>428374</v>
       </c>
       <c r="R19" t="n">
-        <v>6799802</v>
+        <v>6799811</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3482,10 +3482,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127033497</v>
+        <v>127034644</v>
       </c>
       <c r="B28" t="n">
-        <v>79020</v>
+        <v>91358</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3493,21 +3493,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3517,10 +3517,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>428803</v>
+        <v>428786</v>
       </c>
       <c r="R28" t="n">
-        <v>6799992</v>
+        <v>6800327</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3552,7 +3552,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3589,7 +3589,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127028434</v>
+        <v>127033497</v>
       </c>
       <c r="B29" t="n">
         <v>79020</v>
@@ -3620,17 +3620,17 @@
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>428388</v>
+        <v>428803</v>
       </c>
       <c r="R29" t="n">
-        <v>6799765</v>
+        <v>6799992</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3696,10 +3696,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127034644</v>
+        <v>127028434</v>
       </c>
       <c r="B30" t="n">
-        <v>91352</v>
+        <v>79020</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3707,37 +3707,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>428786</v>
+        <v>428388</v>
       </c>
       <c r="R30" t="n">
-        <v>6800327</v>
+        <v>6799765</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3766,7 +3766,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:33</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3803,10 +3803,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127030793</v>
+        <v>127035723</v>
       </c>
       <c r="B31" t="n">
-        <v>56846</v>
+        <v>91358</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3814,42 +3814,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102612</v>
+        <v>5442</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>428603</v>
+        <v>428586</v>
       </c>
       <c r="R31" t="n">
-        <v>6799810</v>
+        <v>6800175</v>
       </c>
       <c r="S31" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3878,7 +3873,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3888,7 +3883,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3915,10 +3910,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127035723</v>
+        <v>127030793</v>
       </c>
       <c r="B32" t="n">
-        <v>91352</v>
+        <v>56846</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3926,37 +3921,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5442</v>
+        <v>102612</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>428586</v>
+        <v>428603</v>
       </c>
       <c r="R32" t="n">
-        <v>6800175</v>
+        <v>6799810</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -5204,10 +5204,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127034191</v>
+        <v>127033191</v>
       </c>
       <c r="B44" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5215,21 +5215,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5239,13 +5239,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>428821</v>
+        <v>428831</v>
       </c>
       <c r="R44" t="n">
-        <v>6800164</v>
+        <v>6799894</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5311,7 +5311,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>127033191</v>
+        <v>127030347</v>
       </c>
       <c r="B45" t="n">
         <v>78779</v>
@@ -5342,14 +5342,14 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>428831</v>
+        <v>428422</v>
       </c>
       <c r="R45" t="n">
-        <v>6799894</v>
+        <v>6799802</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5418,10 +5418,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127030347</v>
+        <v>127034191</v>
       </c>
       <c r="B46" t="n">
-        <v>78779</v>
+        <v>79020</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5429,37 +5429,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>428422</v>
+        <v>428821</v>
       </c>
       <c r="R46" t="n">
-        <v>6799802</v>
+        <v>6800164</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5525,10 +5525,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>127034565</v>
+        <v>127030905</v>
       </c>
       <c r="B47" t="n">
-        <v>79020</v>
+        <v>78779</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5536,37 +5536,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>428780</v>
+        <v>428635</v>
       </c>
       <c r="R47" t="n">
-        <v>6800319</v>
+        <v>6799822</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:29</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5632,10 +5632,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>127030990</v>
+        <v>127034565</v>
       </c>
       <c r="B48" t="n">
-        <v>78778</v>
+        <v>79020</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5643,21 +5643,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5667,13 +5667,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>428677</v>
+        <v>428780</v>
       </c>
       <c r="R48" t="n">
-        <v>6799834</v>
+        <v>6800319</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:31</t>
+          <t>18:29</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5739,10 +5739,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>127030905</v>
+        <v>127030990</v>
       </c>
       <c r="B49" t="n">
-        <v>78779</v>
+        <v>78778</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5750,34 +5750,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>428635</v>
+        <v>428677</v>
       </c>
       <c r="R49" t="n">
-        <v>6799822</v>
+        <v>6799834</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5809,7 +5809,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6172,48 +6172,53 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127033102</v>
+        <v>127033713</v>
       </c>
       <c r="B53" t="n">
-        <v>79020</v>
+        <v>8450</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>428821</v>
+        <v>428806</v>
       </c>
       <c r="R53" t="n">
-        <v>6799886</v>
+        <v>6800045</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6242,7 +6247,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6252,7 +6257,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6279,7 +6284,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127034263</v>
+        <v>127033102</v>
       </c>
       <c r="B54" t="n">
         <v>79020</v>
@@ -6314,10 +6319,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>428826</v>
+        <v>428821</v>
       </c>
       <c r="R54" t="n">
-        <v>6800180</v>
+        <v>6799886</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6349,7 +6354,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6359,12 +6364,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Garnlav mer eller mindre över hela området.</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6503,53 +6503,48 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127033713</v>
+        <v>127034263</v>
       </c>
       <c r="B56" t="n">
-        <v>8450</v>
+        <v>79020</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>428806</v>
+        <v>428826</v>
       </c>
       <c r="R56" t="n">
-        <v>6800045</v>
+        <v>6800180</v>
       </c>
       <c r="S56" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6578,7 +6573,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6588,7 +6583,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Garnlav mer eller mindre över hela området.</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127036675</v>
       </c>
       <c r="B2" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,53 +782,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127035882</v>
+        <v>127034383</v>
       </c>
       <c r="B3" t="n">
-        <v>56855</v>
+        <v>78770</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>428512</v>
+        <v>428839</v>
       </c>
       <c r="R3" t="n">
-        <v>6799960</v>
+        <v>6800310</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>19:29</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127034383</v>
+        <v>127029075</v>
       </c>
       <c r="B4" t="n">
-        <v>78779</v>
+        <v>78770</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,17 +920,17 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>428839</v>
+        <v>428374</v>
       </c>
       <c r="R4" t="n">
-        <v>6800310</v>
+        <v>6799811</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>18:22</t>
+          <t>13:46</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,48 +996,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127029075</v>
+        <v>127035882</v>
       </c>
       <c r="B5" t="n">
-        <v>78779</v>
+        <v>56849</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>428374</v>
+        <v>428512</v>
       </c>
       <c r="R5" t="n">
-        <v>6799811</v>
+        <v>6799960</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:46</t>
+          <t>19:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127028820</v>
+        <v>127028288</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>79629</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1119,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>428394</v>
+        <v>428389</v>
       </c>
       <c r="R6" t="n">
-        <v>6799781</v>
+        <v>6799724</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1188,12 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt med garnlav i hela området.</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,10 +1215,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127028288</v>
+        <v>127031272</v>
       </c>
       <c r="B7" t="n">
-        <v>79638</v>
+        <v>79629</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,14 +1246,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>428389</v>
+        <v>428677</v>
       </c>
       <c r="R7" t="n">
-        <v>6799724</v>
+        <v>6799834</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1290,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,10 +1322,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127031272</v>
+        <v>127028820</v>
       </c>
       <c r="B8" t="n">
-        <v>79638</v>
+        <v>79011</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1338,37 +1333,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>428677</v>
+        <v>428394</v>
       </c>
       <c r="R8" t="n">
-        <v>6799834</v>
+        <v>6799781</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1397,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1407,7 +1402,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt med garnlav i hela området.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1437,7 +1437,7 @@
         <v>127032866</v>
       </c>
       <c r="B9" t="n">
-        <v>79021</v>
+        <v>79012</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>127036174</v>
       </c>
       <c r="B10" t="n">
-        <v>78779</v>
+        <v>78770</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1651,7 +1651,7 @@
         <v>127032352</v>
       </c>
       <c r="B11" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>127030417</v>
       </c>
       <c r="B12" t="n">
-        <v>78778</v>
+        <v>78769</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1862,10 +1862,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127033062</v>
+        <v>127029492</v>
       </c>
       <c r="B13" t="n">
-        <v>57660</v>
+        <v>79011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1873,39 +1873,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>428840</v>
+        <v>428422</v>
       </c>
       <c r="R13" t="n">
-        <v>6799855</v>
+        <v>6799802</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1937,7 +1932,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1947,7 +1942,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1974,10 +1969,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127033222</v>
+        <v>127033062</v>
       </c>
       <c r="B14" t="n">
-        <v>78778</v>
+        <v>57654</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1985,37 +1980,42 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>428831</v>
+        <v>428840</v>
       </c>
       <c r="R14" t="n">
-        <v>6799894</v>
+        <v>6799855</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2044,7 +2044,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2054,7 +2054,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2081,10 +2081,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127029492</v>
+        <v>127033222</v>
       </c>
       <c r="B15" t="n">
-        <v>79020</v>
+        <v>78769</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2092,37 +2092,37 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>428422</v>
+        <v>428831</v>
       </c>
       <c r="R15" t="n">
-        <v>6799802</v>
+        <v>6799894</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2151,7 +2151,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2191,7 +2191,7 @@
         <v>127028962</v>
       </c>
       <c r="B16" t="n">
-        <v>78779</v>
+        <v>78770</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2295,10 +2295,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127030319</v>
+        <v>127028974</v>
       </c>
       <c r="B17" t="n">
-        <v>79609</v>
+        <v>78769</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2306,21 +2306,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2330,10 +2330,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>428422</v>
+        <v>428374</v>
       </c>
       <c r="R17" t="n">
-        <v>6799802</v>
+        <v>6799811</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2405,7 +2405,7 @@
         <v>127033408</v>
       </c>
       <c r="B18" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2509,10 +2509,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127028974</v>
+        <v>127030319</v>
       </c>
       <c r="B19" t="n">
-        <v>78778</v>
+        <v>79600</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2520,21 +2520,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>428374</v>
+        <v>428422</v>
       </c>
       <c r="R19" t="n">
-        <v>6799811</v>
+        <v>6799802</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:38</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2616,10 +2616,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127033349</v>
+        <v>127033867</v>
       </c>
       <c r="B20" t="n">
-        <v>57660</v>
+        <v>78769</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2627,42 +2627,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>428792</v>
+        <v>428801</v>
       </c>
       <c r="R20" t="n">
-        <v>6799956</v>
+        <v>6800075</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2691,7 +2686,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2701,7 +2696,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>17:19</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2728,10 +2723,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127033867</v>
+        <v>127032907</v>
       </c>
       <c r="B21" t="n">
-        <v>78778</v>
+        <v>79011</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2739,21 +2734,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2763,13 +2758,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>428801</v>
+        <v>428763</v>
       </c>
       <c r="R21" t="n">
-        <v>6800075</v>
+        <v>6799813</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2798,7 +2793,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2808,7 +2803,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2835,10 +2830,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127032907</v>
+        <v>127035403</v>
       </c>
       <c r="B22" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2870,10 +2865,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>428763</v>
+        <v>428610</v>
       </c>
       <c r="R22" t="n">
-        <v>6799813</v>
+        <v>6800197</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2905,7 +2900,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2915,7 +2910,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2942,10 +2937,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127035403</v>
+        <v>127033349</v>
       </c>
       <c r="B23" t="n">
-        <v>79020</v>
+        <v>57654</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2953,34 +2948,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>428610</v>
+        <v>428792</v>
       </c>
       <c r="R23" t="n">
-        <v>6800197</v>
+        <v>6799956</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3012,7 +3012,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>17:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3052,7 +3052,7 @@
         <v>127028936</v>
       </c>
       <c r="B24" t="n">
-        <v>8450</v>
+        <v>8447</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3161,10 +3161,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127034314</v>
+        <v>127031042</v>
       </c>
       <c r="B25" t="n">
-        <v>78779</v>
+        <v>78770</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3196,13 +3196,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>428856</v>
+        <v>428677</v>
       </c>
       <c r="R25" t="n">
-        <v>6800220</v>
+        <v>6799834</v>
       </c>
       <c r="S25" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3231,7 +3231,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3268,10 +3268,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127031042</v>
+        <v>127034314</v>
       </c>
       <c r="B26" t="n">
-        <v>78779</v>
+        <v>78770</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3303,13 +3303,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>428677</v>
+        <v>428856</v>
       </c>
       <c r="R26" t="n">
-        <v>6799834</v>
+        <v>6800220</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3338,7 +3338,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3348,7 +3348,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3378,7 +3378,7 @@
         <v>127031710</v>
       </c>
       <c r="B27" t="n">
-        <v>78778</v>
+        <v>78769</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>127034644</v>
       </c>
       <c r="B28" t="n">
-        <v>91358</v>
+        <v>91339</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3592,7 +3592,7 @@
         <v>127033497</v>
       </c>
       <c r="B29" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>127028434</v>
       </c>
       <c r="B30" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3803,10 +3803,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127035723</v>
+        <v>127030793</v>
       </c>
       <c r="B31" t="n">
-        <v>91358</v>
+        <v>56840</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3814,37 +3814,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5442</v>
+        <v>102612</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>428586</v>
+        <v>428603</v>
       </c>
       <c r="R31" t="n">
-        <v>6800175</v>
+        <v>6799810</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3873,7 +3878,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3883,7 +3888,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>19:18</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3910,10 +3915,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127030793</v>
+        <v>127035723</v>
       </c>
       <c r="B32" t="n">
-        <v>56846</v>
+        <v>91339</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3921,42 +3926,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102612</v>
+        <v>5442</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>428603</v>
+        <v>428586</v>
       </c>
       <c r="R32" t="n">
-        <v>6799810</v>
+        <v>6800175</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:15</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4025,7 +4025,7 @@
         <v>127034901</v>
       </c>
       <c r="B33" t="n">
-        <v>78779</v>
+        <v>78770</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4129,10 +4129,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127035734</v>
+        <v>127033824</v>
       </c>
       <c r="B34" t="n">
-        <v>79020</v>
+        <v>78769</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4140,34 +4140,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>428511</v>
+        <v>428807</v>
       </c>
       <c r="R34" t="n">
-        <v>6799990</v>
+        <v>6800084</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4236,10 +4236,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>127033824</v>
+        <v>127035734</v>
       </c>
       <c r="B35" t="n">
-        <v>78778</v>
+        <v>79011</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4247,34 +4247,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>428807</v>
+        <v>428511</v>
       </c>
       <c r="R35" t="n">
-        <v>6800084</v>
+        <v>6799990</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4306,7 +4306,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4316,7 +4316,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4346,7 +4346,7 @@
         <v>127030918</v>
       </c>
       <c r="B36" t="n">
-        <v>78778</v>
+        <v>78769</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4453,7 +4453,7 @@
         <v>127036021</v>
       </c>
       <c r="B37" t="n">
-        <v>78778</v>
+        <v>78769</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>127034208</v>
       </c>
       <c r="B38" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4664,10 +4664,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>127033133</v>
+        <v>127026773</v>
       </c>
       <c r="B39" t="n">
-        <v>79020</v>
+        <v>57654</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4675,37 +4675,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Storholsrannet, Storholsrannet, Dlr</t>
+          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>428813</v>
+        <v>428345</v>
       </c>
       <c r="R39" t="n">
-        <v>6799900</v>
+        <v>6799714</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4734,7 +4739,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4744,7 +4749,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>17:05</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4771,10 +4776,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>127026773</v>
+        <v>127033133</v>
       </c>
       <c r="B40" t="n">
-        <v>57660</v>
+        <v>79011</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4782,42 +4787,37 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ormtjärnen, Ormtjärnen, Dlr</t>
+          <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>428345</v>
+        <v>428813</v>
       </c>
       <c r="R40" t="n">
-        <v>6799714</v>
+        <v>6799900</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4856,7 +4856,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>17:05</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4886,7 +4886,7 @@
         <v>127032393</v>
       </c>
       <c r="B41" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4993,7 +4993,7 @@
         <v>127032439</v>
       </c>
       <c r="B42" t="n">
-        <v>78778</v>
+        <v>78769</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5100,7 +5100,7 @@
         <v>127035229</v>
       </c>
       <c r="B43" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5204,10 +5204,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>127033191</v>
+        <v>127034191</v>
       </c>
       <c r="B44" t="n">
-        <v>78779</v>
+        <v>79011</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5215,21 +5215,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5239,13 +5239,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>428831</v>
+        <v>428821</v>
       </c>
       <c r="R44" t="n">
-        <v>6799894</v>
+        <v>6800164</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5274,7 +5274,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5314,7 +5314,7 @@
         <v>127030347</v>
       </c>
       <c r="B45" t="n">
-        <v>78779</v>
+        <v>78770</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5418,10 +5418,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>127034191</v>
+        <v>127033191</v>
       </c>
       <c r="B46" t="n">
-        <v>79020</v>
+        <v>78770</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5429,21 +5429,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5453,13 +5453,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>428821</v>
+        <v>428831</v>
       </c>
       <c r="R46" t="n">
-        <v>6800164</v>
+        <v>6799894</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5528,7 +5528,7 @@
         <v>127030905</v>
       </c>
       <c r="B47" t="n">
-        <v>78779</v>
+        <v>78770</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5635,7 +5635,7 @@
         <v>127034565</v>
       </c>
       <c r="B48" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>127030990</v>
       </c>
       <c r="B49" t="n">
-        <v>78778</v>
+        <v>78769</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>127032317</v>
       </c>
       <c r="B50" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         <v>127034235</v>
       </c>
       <c r="B51" t="n">
-        <v>57660</v>
+        <v>57654</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>127027998</v>
       </c>
       <c r="B52" t="n">
-        <v>78778</v>
+        <v>78769</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6172,53 +6172,48 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>127033713</v>
+        <v>127033102</v>
       </c>
       <c r="B53" t="n">
-        <v>8450</v>
+        <v>79011</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>428806</v>
+        <v>428821</v>
       </c>
       <c r="R53" t="n">
-        <v>6800045</v>
+        <v>6799886</v>
       </c>
       <c r="S53" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6247,7 +6242,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6257,7 +6252,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6284,10 +6279,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>127033102</v>
+        <v>127034263</v>
       </c>
       <c r="B54" t="n">
-        <v>79020</v>
+        <v>79011</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6319,10 +6314,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>428821</v>
+        <v>428826</v>
       </c>
       <c r="R54" t="n">
-        <v>6799886</v>
+        <v>6800180</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6354,7 +6349,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:09</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6364,7 +6359,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:04</t>
+          <t>18:09</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Garnlav mer eller mindre över hela området.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6394,7 +6394,7 @@
         <v>127035441</v>
       </c>
       <c r="B55" t="n">
-        <v>57660</v>
+        <v>57654</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6503,48 +6503,53 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>127034263</v>
+        <v>127033713</v>
       </c>
       <c r="B56" t="n">
-        <v>79020</v>
+        <v>8447</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Storholsrannet, Storholsrannet, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>428826</v>
+        <v>428806</v>
       </c>
       <c r="R56" t="n">
-        <v>6800180</v>
+        <v>6800045</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6573,7 +6578,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>18:09</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6583,12 +6588,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>18:09</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Garnlav mer eller mindre över hela området.</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY70"/>
+  <dimension ref="A1:AZ70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127034644</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127035723</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127026729</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127026950</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127027652</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1314,6 +1344,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127028434</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1426,6 +1461,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127028820</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1533,6 +1573,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127029492</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1640,6 +1685,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127032317</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1747,6 +1797,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127032352</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1854,6 +1909,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127032393</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1961,6 +2021,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127032907</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2068,6 +2133,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127033102</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2175,6 +2245,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127033133</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2282,6 +2357,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127033408</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2389,6 +2469,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127033497</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2496,6 +2581,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127034191</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2603,6 +2693,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127034208</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2715,6 +2810,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127034263</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2822,6 +2922,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127034565</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2929,6 +3034,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127035229</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3036,6 +3146,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127035403</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3143,6 +3258,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127035734</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3250,6 +3370,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127036141</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3357,6 +3482,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127036236</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3464,6 +3594,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127036293</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3571,6 +3706,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127036449</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3678,6 +3818,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127036675</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3785,6 +3930,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127027998</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3892,6 +4042,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127028974</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3999,6 +4154,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127030417</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4106,6 +4266,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127030918</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4213,6 +4378,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127030990</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4320,6 +4490,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127031710</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4427,6 +4602,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127032439</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4534,6 +4714,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127033222</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4641,6 +4826,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127033824</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4748,6 +4938,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127033867</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4855,6 +5050,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127034709</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4962,6 +5162,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127035058</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5069,6 +5274,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127035144</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5176,6 +5386,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127036021</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5283,6 +5498,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127036190</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5390,6 +5610,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127028288</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5497,6 +5722,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127031272</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5609,6 +5839,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127026773</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5721,6 +5956,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127033062</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5833,6 +6073,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127033349</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5945,6 +6190,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127034235</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6057,6 +6307,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127035441</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6169,6 +6424,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127027544</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6281,6 +6541,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127035882</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6393,6 +6658,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127030793</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6505,6 +6775,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127028936</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6617,6 +6892,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127033713</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6724,6 +7004,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127028962</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6831,6 +7116,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127029075</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6938,6 +7228,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127030347</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7045,6 +7340,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127030905</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7152,6 +7452,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127031042</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7259,6 +7564,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127033191</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7366,6 +7676,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127034314</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7473,6 +7788,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127034383</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7580,6 +7900,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127034693</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7687,6 +8012,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127034901</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7794,6 +8124,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127035136</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7901,6 +8236,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127036174</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8008,6 +8348,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127030319</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8115,8 +8460,84 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127032866</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136402433</v>
       </c>
       <c r="B2" t="n">
-        <v>92333</v>
+        <v>92334</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>136392821</v>
       </c>
       <c r="B16" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>136396104</v>
       </c>
       <c r="B17" t="n">
-        <v>91857</v>
+        <v>91858</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>136386035</v>
       </c>
       <c r="B18" t="n">
-        <v>93379</v>
+        <v>93380</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>136376836</v>
       </c>
       <c r="B19" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>136380121</v>
       </c>
       <c r="B20" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>136381954</v>
       </c>
       <c r="B21" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>136384925</v>
       </c>
       <c r="B22" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>136386039</v>
       </c>
       <c r="B23" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>136386054</v>
       </c>
       <c r="B24" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>136386055</v>
       </c>
       <c r="B25" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>136386073</v>
       </c>
       <c r="B26" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>136386075</v>
       </c>
       <c r="B27" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>136386082</v>
       </c>
       <c r="B28" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>136386084</v>
       </c>
       <c r="B29" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>136386090</v>
       </c>
       <c r="B30" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>136392727</v>
       </c>
       <c r="B31" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>136392735</v>
       </c>
       <c r="B32" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>136392741</v>
       </c>
       <c r="B33" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>136392756</v>
       </c>
       <c r="B34" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>136392771</v>
       </c>
       <c r="B35" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>136392794</v>
       </c>
       <c r="B36" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>136392800</v>
       </c>
       <c r="B37" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>136392803</v>
       </c>
       <c r="B38" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>136392811</v>
       </c>
       <c r="B39" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>136392812</v>
       </c>
       <c r="B40" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         <v>136392813</v>
       </c>
       <c r="B41" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>136392823</v>
       </c>
       <c r="B42" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         <v>136392828</v>
       </c>
       <c r="B43" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>136393469</v>
       </c>
       <c r="B44" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>136396101</v>
       </c>
       <c r="B45" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>136396122</v>
       </c>
       <c r="B46" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>136396125</v>
       </c>
       <c r="B47" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>136396129</v>
       </c>
       <c r="B48" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>136396130</v>
       </c>
       <c r="B49" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>136396135</v>
       </c>
       <c r="B50" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         <v>136396148</v>
       </c>
       <c r="B51" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>136396149</v>
       </c>
       <c r="B52" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>136396152</v>
       </c>
       <c r="B53" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>136396154</v>
       </c>
       <c r="B54" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>136396155</v>
       </c>
       <c r="B55" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>136396156</v>
       </c>
       <c r="B56" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>136402412</v>
       </c>
       <c r="B57" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>136402421</v>
       </c>
       <c r="B58" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7553,7 +7553,7 @@
         <v>136402428</v>
       </c>
       <c r="B59" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>136402429</v>
       </c>
       <c r="B60" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>136402434</v>
       </c>
       <c r="B61" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>136402436</v>
       </c>
       <c r="B62" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>136402438</v>
       </c>
       <c r="B63" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>136402439</v>
       </c>
       <c r="B64" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>136402441</v>
       </c>
       <c r="B65" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>136402442</v>
       </c>
       <c r="B66" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>136405164</v>
       </c>
       <c r="B67" t="n">
-        <v>93385</v>
+        <v>93386</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>136402408</v>
       </c>
       <c r="B68" t="n">
-        <v>93397</v>
+        <v>93398</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>136386041</v>
       </c>
       <c r="B69" t="n">
-        <v>89299</v>
+        <v>89300</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>136386050</v>
       </c>
       <c r="B70" t="n">
-        <v>89299</v>
+        <v>89300</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         <v>136392816</v>
       </c>
       <c r="B71" t="n">
-        <v>93057</v>
+        <v>93058</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>136402409</v>
       </c>
       <c r="B72" t="n">
-        <v>93057</v>
+        <v>93058</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>136382713</v>
       </c>
       <c r="B75" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>136392764</v>
       </c>
       <c r="B76" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>136396142</v>
       </c>
       <c r="B77" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>136396143</v>
       </c>
       <c r="B78" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>136402426</v>
       </c>
       <c r="B79" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>136402422</v>
       </c>
       <c r="B80" t="n">
-        <v>91446</v>
+        <v>91447</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>136392786</v>
       </c>
       <c r="B81" t="n">
-        <v>93369</v>
+        <v>93370</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -36978,7 +36978,7 @@
         <v>136392810</v>
       </c>
       <c r="B316" t="n">
-        <v>99244</v>
+        <v>99245</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -37090,7 +37090,7 @@
         <v>136392787</v>
       </c>
       <c r="B317" t="n">
-        <v>98195</v>
+        <v>98196</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -37211,7 +37211,7 @@
         <v>136396123</v>
       </c>
       <c r="B318" t="n">
-        <v>98195</v>
+        <v>98196</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -37323,7 +37323,7 @@
         <v>136392749</v>
       </c>
       <c r="B319" t="n">
-        <v>98189</v>
+        <v>98190</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136402433</v>
       </c>
       <c r="B2" t="n">
-        <v>92334</v>
+        <v>92347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136392725</v>
       </c>
       <c r="B3" t="n">
-        <v>79492</v>
+        <v>79505</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136379790</v>
       </c>
       <c r="B4" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136384395</v>
       </c>
       <c r="B5" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136392737</v>
       </c>
       <c r="B6" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>136392768</v>
       </c>
       <c r="B7" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>136392775</v>
       </c>
       <c r="B8" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>136392792</v>
       </c>
       <c r="B9" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136392793</v>
       </c>
       <c r="B10" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>136396115</v>
       </c>
       <c r="B11" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>136396133</v>
       </c>
       <c r="B12" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>136402411</v>
       </c>
       <c r="B13" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>136402419</v>
       </c>
       <c r="B14" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136402423</v>
       </c>
       <c r="B15" t="n">
-        <v>79126</v>
+        <v>79139</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>136392821</v>
       </c>
       <c r="B16" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>136396104</v>
       </c>
       <c r="B17" t="n">
-        <v>91858</v>
+        <v>91871</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>136386035</v>
       </c>
       <c r="B18" t="n">
-        <v>93380</v>
+        <v>93393</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>136376836</v>
       </c>
       <c r="B19" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>136380121</v>
       </c>
       <c r="B20" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>136381954</v>
       </c>
       <c r="B21" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>136384925</v>
       </c>
       <c r="B22" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>136386039</v>
       </c>
       <c r="B23" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>136386054</v>
       </c>
       <c r="B24" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>136386055</v>
       </c>
       <c r="B25" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>136386073</v>
       </c>
       <c r="B26" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>136386075</v>
       </c>
       <c r="B27" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>136386082</v>
       </c>
       <c r="B28" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>136386084</v>
       </c>
       <c r="B29" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>136386090</v>
       </c>
       <c r="B30" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>136392727</v>
       </c>
       <c r="B31" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>136392735</v>
       </c>
       <c r="B32" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>136392741</v>
       </c>
       <c r="B33" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>136392756</v>
       </c>
       <c r="B34" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>136392771</v>
       </c>
       <c r="B35" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>136392794</v>
       </c>
       <c r="B36" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>136392800</v>
       </c>
       <c r="B37" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>136392803</v>
       </c>
       <c r="B38" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>136392811</v>
       </c>
       <c r="B39" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>136392812</v>
       </c>
       <c r="B40" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         <v>136392813</v>
       </c>
       <c r="B41" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>136392823</v>
       </c>
       <c r="B42" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         <v>136392828</v>
       </c>
       <c r="B43" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>136393469</v>
       </c>
       <c r="B44" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>136396101</v>
       </c>
       <c r="B45" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>136396122</v>
       </c>
       <c r="B46" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>136396125</v>
       </c>
       <c r="B47" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>136396129</v>
       </c>
       <c r="B48" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>136396130</v>
       </c>
       <c r="B49" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>136396135</v>
       </c>
       <c r="B50" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         <v>136396148</v>
       </c>
       <c r="B51" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>136396149</v>
       </c>
       <c r="B52" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>136396152</v>
       </c>
       <c r="B53" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>136396154</v>
       </c>
       <c r="B54" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>136396155</v>
       </c>
       <c r="B55" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>136396156</v>
       </c>
       <c r="B56" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>136402412</v>
       </c>
       <c r="B57" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>136402421</v>
       </c>
       <c r="B58" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7553,7 +7553,7 @@
         <v>136402428</v>
       </c>
       <c r="B59" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>136402429</v>
       </c>
       <c r="B60" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>136402434</v>
       </c>
       <c r="B61" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>136402436</v>
       </c>
       <c r="B62" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>136402438</v>
       </c>
       <c r="B63" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>136402439</v>
       </c>
       <c r="B64" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>136402441</v>
       </c>
       <c r="B65" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>136402442</v>
       </c>
       <c r="B66" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>136405164</v>
       </c>
       <c r="B67" t="n">
-        <v>93386</v>
+        <v>93399</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>136402408</v>
       </c>
       <c r="B68" t="n">
-        <v>93398</v>
+        <v>93411</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>136386041</v>
       </c>
       <c r="B69" t="n">
-        <v>89300</v>
+        <v>89313</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>136386050</v>
       </c>
       <c r="B70" t="n">
-        <v>89300</v>
+        <v>89313</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         <v>136392816</v>
       </c>
       <c r="B71" t="n">
-        <v>93058</v>
+        <v>93071</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>136402409</v>
       </c>
       <c r="B72" t="n">
-        <v>93058</v>
+        <v>93071</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>136382713</v>
       </c>
       <c r="B75" t="n">
-        <v>92109</v>
+        <v>92122</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>136392764</v>
       </c>
       <c r="B76" t="n">
-        <v>92109</v>
+        <v>92122</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>136396142</v>
       </c>
       <c r="B77" t="n">
-        <v>92109</v>
+        <v>92122</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>136396143</v>
       </c>
       <c r="B78" t="n">
-        <v>92109</v>
+        <v>92122</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>136402426</v>
       </c>
       <c r="B79" t="n">
-        <v>92109</v>
+        <v>92122</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>136402422</v>
       </c>
       <c r="B80" t="n">
-        <v>91447</v>
+        <v>91460</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>136392786</v>
       </c>
       <c r="B81" t="n">
-        <v>93370</v>
+        <v>93383</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         <v>136376332</v>
       </c>
       <c r="B108" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>136376665</v>
       </c>
       <c r="B109" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>136377035</v>
       </c>
       <c r="B110" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>136382303</v>
       </c>
       <c r="B111" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>136386037</v>
       </c>
       <c r="B112" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>136386040</v>
       </c>
       <c r="B113" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>136386051</v>
       </c>
       <c r="B114" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>136386056</v>
       </c>
       <c r="B115" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>136386057</v>
       </c>
       <c r="B116" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>136386058</v>
       </c>
       <c r="B117" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>136386059</v>
       </c>
       <c r="B118" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>136386060</v>
       </c>
       <c r="B119" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>136386061</v>
       </c>
       <c r="B120" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>136386064</v>
       </c>
       <c r="B121" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>136386066</v>
       </c>
       <c r="B122" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14875,7 +14875,7 @@
         <v>136386067</v>
       </c>
       <c r="B123" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>136386070</v>
       </c>
       <c r="B124" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         <v>136386071</v>
       </c>
       <c r="B125" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>136386072</v>
       </c>
       <c r="B126" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>136386087</v>
       </c>
       <c r="B127" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15460,7 +15460,7 @@
         <v>136386089</v>
       </c>
       <c r="B128" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>136392705</v>
       </c>
       <c r="B129" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15689,7 +15689,7 @@
         <v>136392738</v>
       </c>
       <c r="B130" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>136392752</v>
       </c>
       <c r="B131" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>136392755</v>
       </c>
       <c r="B132" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>136392757</v>
       </c>
       <c r="B133" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16137,7 +16137,7 @@
         <v>136392769</v>
       </c>
       <c r="B134" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>136392772</v>
       </c>
       <c r="B135" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>136392773</v>
       </c>
       <c r="B136" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>136392779</v>
       </c>
       <c r="B137" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>136392780</v>
       </c>
       <c r="B138" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>136392790</v>
       </c>
       <c r="B139" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>136392795</v>
       </c>
       <c r="B140" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>136392796</v>
       </c>
       <c r="B141" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>136392805</v>
       </c>
       <c r="B142" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17150,7 +17150,7 @@
         <v>136392818</v>
       </c>
       <c r="B143" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>136392820</v>
       </c>
       <c r="B144" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17374,7 +17374,7 @@
         <v>136392827</v>
       </c>
       <c r="B145" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>136392829</v>
       </c>
       <c r="B146" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17598,7 +17598,7 @@
         <v>136393453</v>
       </c>
       <c r="B147" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>136393455</v>
       </c>
       <c r="B148" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
         <v>136393456</v>
       </c>
       <c r="B149" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>136393458</v>
       </c>
       <c r="B150" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18046,7 +18046,7 @@
         <v>136393459</v>
       </c>
       <c r="B151" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18158,7 +18158,7 @@
         <v>136393460</v>
       </c>
       <c r="B152" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         <v>136393461</v>
       </c>
       <c r="B153" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         <v>136393462</v>
       </c>
       <c r="B154" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>136393463</v>
       </c>
       <c r="B155" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18606,7 +18606,7 @@
         <v>136393464</v>
       </c>
       <c r="B156" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18718,7 +18718,7 @@
         <v>136393465</v>
       </c>
       <c r="B157" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>136393468</v>
       </c>
       <c r="B158" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18942,7 +18942,7 @@
         <v>136393472</v>
       </c>
       <c r="B159" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19054,7 +19054,7 @@
         <v>136393475</v>
       </c>
       <c r="B160" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>136393482</v>
       </c>
       <c r="B161" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>136393483</v>
       </c>
       <c r="B162" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>136393484</v>
       </c>
       <c r="B163" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19502,7 +19502,7 @@
         <v>136393485</v>
       </c>
       <c r="B164" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>136393489</v>
       </c>
       <c r="B165" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19726,7 +19726,7 @@
         <v>136393490</v>
       </c>
       <c r="B166" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>136393492</v>
       </c>
       <c r="B167" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>136393493</v>
       </c>
       <c r="B168" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>136393496</v>
       </c>
       <c r="B169" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20174,7 +20174,7 @@
         <v>136393497</v>
       </c>
       <c r="B170" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20286,7 +20286,7 @@
         <v>136393498</v>
       </c>
       <c r="B171" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20398,7 +20398,7 @@
         <v>136393500</v>
       </c>
       <c r="B172" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>136393503</v>
       </c>
       <c r="B173" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20622,7 +20622,7 @@
         <v>136393505</v>
       </c>
       <c r="B174" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>136393506</v>
       </c>
       <c r="B175" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20846,7 +20846,7 @@
         <v>136393509</v>
       </c>
       <c r="B176" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>136393512</v>
       </c>
       <c r="B177" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21070,7 +21070,7 @@
         <v>136393515</v>
       </c>
       <c r="B178" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21182,7 +21182,7 @@
         <v>136393518</v>
       </c>
       <c r="B179" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>136393519</v>
       </c>
       <c r="B180" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>136393520</v>
       </c>
       <c r="B181" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>136393524</v>
       </c>
       <c r="B182" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>136393525</v>
       </c>
       <c r="B183" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21742,7 +21742,7 @@
         <v>136393527</v>
       </c>
       <c r="B184" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>136396107</v>
       </c>
       <c r="B185" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>136396109</v>
       </c>
       <c r="B186" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22078,7 +22078,7 @@
         <v>136396112</v>
       </c>
       <c r="B187" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22190,7 +22190,7 @@
         <v>136396113</v>
       </c>
       <c r="B188" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>136396118</v>
       </c>
       <c r="B189" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
         <v>136396119</v>
       </c>
       <c r="B190" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>136396128</v>
       </c>
       <c r="B191" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>136396132</v>
       </c>
       <c r="B192" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>136396136</v>
       </c>
       <c r="B193" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>136396138</v>
       </c>
       <c r="B194" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>136396140</v>
       </c>
       <c r="B195" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>136396145</v>
       </c>
       <c r="B196" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23198,7 +23198,7 @@
         <v>136396150</v>
       </c>
       <c r="B197" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>136396159</v>
       </c>
       <c r="B198" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23422,7 +23422,7 @@
         <v>136402413</v>
       </c>
       <c r="B199" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>136402430</v>
       </c>
       <c r="B200" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23651,7 +23651,7 @@
         <v>136386074</v>
       </c>
       <c r="B201" t="n">
-        <v>79484</v>
+        <v>79497</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>136392732</v>
       </c>
       <c r="B202" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>136392798</v>
       </c>
       <c r="B203" t="n">
-        <v>78863</v>
+        <v>78876</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -25691,7 +25691,7 @@
         <v>136383035</v>
       </c>
       <c r="B219" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -25812,7 +25812,7 @@
         <v>136386044</v>
       </c>
       <c r="B220" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -25924,7 +25924,7 @@
         <v>136386047</v>
       </c>
       <c r="B221" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>136386053</v>
       </c>
       <c r="B222" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26148,7 +26148,7 @@
         <v>136386062</v>
       </c>
       <c r="B223" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26260,7 +26260,7 @@
         <v>136386069</v>
       </c>
       <c r="B224" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>136386077</v>
       </c>
       <c r="B225" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>136392744</v>
       </c>
       <c r="B226" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -26606,7 +26606,7 @@
         <v>136392746</v>
       </c>
       <c r="B227" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26728,7 +26728,7 @@
         <v>136393467</v>
       </c>
       <c r="B228" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>136393476</v>
       </c>
       <c r="B229" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -26952,7 +26952,7 @@
         <v>136393487</v>
       </c>
       <c r="B230" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>136393502</v>
       </c>
       <c r="B231" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -27176,7 +27176,7 @@
         <v>136393504</v>
       </c>
       <c r="B232" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>136393513</v>
       </c>
       <c r="B233" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -27400,7 +27400,7 @@
         <v>136393516</v>
       </c>
       <c r="B234" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         <v>136393522</v>
       </c>
       <c r="B235" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -27624,7 +27624,7 @@
         <v>136396153</v>
       </c>
       <c r="B236" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -27736,7 +27736,7 @@
         <v>136402414</v>
       </c>
       <c r="B237" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -27848,7 +27848,7 @@
         <v>136402437</v>
       </c>
       <c r="B238" t="n">
-        <v>79217</v>
+        <v>79230</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>136386042</v>
       </c>
       <c r="B241" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -28296,7 +28296,7 @@
         <v>136386043</v>
       </c>
       <c r="B242" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>136386045</v>
       </c>
       <c r="B243" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>136386048</v>
       </c>
       <c r="B244" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -28632,7 +28632,7 @@
         <v>136386052</v>
       </c>
       <c r="B245" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -28744,7 +28744,7 @@
         <v>136386063</v>
       </c>
       <c r="B246" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>136386065</v>
       </c>
       <c r="B247" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -28968,7 +28968,7 @@
         <v>136386068</v>
       </c>
       <c r="B248" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29080,7 +29080,7 @@
         <v>136386078</v>
       </c>
       <c r="B249" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29192,7 +29192,7 @@
         <v>136386081</v>
       </c>
       <c r="B250" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29304,7 +29304,7 @@
         <v>136386083</v>
       </c>
       <c r="B251" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29416,7 +29416,7 @@
         <v>136392720</v>
       </c>
       <c r="B252" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>136392742</v>
       </c>
       <c r="B253" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -29640,7 +29640,7 @@
         <v>136392753</v>
       </c>
       <c r="B254" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -29762,7 +29762,7 @@
         <v>136392804</v>
       </c>
       <c r="B255" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -29884,7 +29884,7 @@
         <v>136393486</v>
       </c>
       <c r="B256" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>136393508</v>
       </c>
       <c r="B257" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -30108,7 +30108,7 @@
         <v>136393510</v>
       </c>
       <c r="B258" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30220,7 +30220,7 @@
         <v>136396158</v>
       </c>
       <c r="B259" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -30332,7 +30332,7 @@
         <v>136402420</v>
       </c>
       <c r="B260" t="n">
-        <v>80079</v>
+        <v>80092</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>136386086</v>
       </c>
       <c r="B266" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -31146,7 +31146,7 @@
         <v>136392750</v>
       </c>
       <c r="B267" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -31263,7 +31263,7 @@
         <v>136392758</v>
       </c>
       <c r="B268" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>136392759</v>
       </c>
       <c r="B269" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -31497,7 +31497,7 @@
         <v>136392762</v>
       </c>
       <c r="B270" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>136392774</v>
       </c>
       <c r="B271" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -31731,7 +31731,7 @@
         <v>136392788</v>
       </c>
       <c r="B272" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>136392791</v>
       </c>
       <c r="B273" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -31965,7 +31965,7 @@
         <v>136392797</v>
       </c>
       <c r="B274" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>136392807</v>
       </c>
       <c r="B275" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -32199,7 +32199,7 @@
         <v>136392822</v>
       </c>
       <c r="B276" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -32316,7 +32316,7 @@
         <v>136396103</v>
       </c>
       <c r="B277" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -32441,7 +32441,7 @@
         <v>136386036</v>
       </c>
       <c r="B278" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>136386088</v>
       </c>
       <c r="B279" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -32685,7 +32685,7 @@
         <v>136392707</v>
       </c>
       <c r="B280" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -32807,7 +32807,7 @@
         <v>136392713</v>
       </c>
       <c r="B281" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -32932,7 +32932,7 @@
         <v>136392819</v>
       </c>
       <c r="B282" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -33052,7 +33052,7 @@
         <v>136392824</v>
       </c>
       <c r="B283" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -33177,7 +33177,7 @@
         <v>136392825</v>
       </c>
       <c r="B284" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -33302,7 +33302,7 @@
         <v>136393478</v>
       </c>
       <c r="B285" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -33661,7 +33661,7 @@
         <v>136376480</v>
       </c>
       <c r="B288" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -33778,7 +33778,7 @@
         <v>136376605</v>
       </c>
       <c r="B289" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -33895,7 +33895,7 @@
         <v>136377407</v>
       </c>
       <c r="B290" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -34016,7 +34016,7 @@
         <v>136383403</v>
       </c>
       <c r="B291" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -34137,7 +34137,7 @@
         <v>136384834</v>
       </c>
       <c r="B292" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -34258,7 +34258,7 @@
         <v>136386076</v>
       </c>
       <c r="B293" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -34379,7 +34379,7 @@
         <v>136392711</v>
       </c>
       <c r="B294" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -34496,7 +34496,7 @@
         <v>136392716</v>
       </c>
       <c r="B295" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -34613,7 +34613,7 @@
         <v>136392718</v>
       </c>
       <c r="B296" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -34730,7 +34730,7 @@
         <v>136392722</v>
       </c>
       <c r="B297" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -34847,7 +34847,7 @@
         <v>136392734</v>
       </c>
       <c r="B298" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>136392736</v>
       </c>
       <c r="B299" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -35081,7 +35081,7 @@
         <v>136392751</v>
       </c>
       <c r="B300" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -35198,7 +35198,7 @@
         <v>136392781</v>
       </c>
       <c r="B301" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -35320,7 +35320,7 @@
         <v>136392782</v>
       </c>
       <c r="B302" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -35437,7 +35437,7 @@
         <v>136392785</v>
       </c>
       <c r="B303" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -35554,7 +35554,7 @@
         <v>136392826</v>
       </c>
       <c r="B304" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -35671,7 +35671,7 @@
         <v>136393474</v>
       </c>
       <c r="B305" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -35796,7 +35796,7 @@
         <v>136396121</v>
       </c>
       <c r="B306" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -35921,7 +35921,7 @@
         <v>136402418</v>
       </c>
       <c r="B307" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -36272,7 +36272,7 @@
         <v>136392761</v>
       </c>
       <c r="B310" t="n">
-        <v>58154</v>
+        <v>58167</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -36398,7 +36398,7 @@
         <v>136402424</v>
       </c>
       <c r="B311" t="n">
-        <v>58149</v>
+        <v>58162</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -36978,7 +36978,7 @@
         <v>136392810</v>
       </c>
       <c r="B316" t="n">
-        <v>99245</v>
+        <v>99258</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -37090,7 +37090,7 @@
         <v>136392787</v>
       </c>
       <c r="B317" t="n">
-        <v>98196</v>
+        <v>98209</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -37211,7 +37211,7 @@
         <v>136396123</v>
       </c>
       <c r="B318" t="n">
-        <v>98196</v>
+        <v>98209</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -37323,7 +37323,7 @@
         <v>136392749</v>
       </c>
       <c r="B319" t="n">
-        <v>98190</v>
+        <v>98203</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -38779,7 +38779,7 @@
         <v>136377218</v>
       </c>
       <c r="B332" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -38900,7 +38900,7 @@
         <v>136383007</v>
       </c>
       <c r="B333" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -39021,7 +39021,7 @@
         <v>136392743</v>
       </c>
       <c r="B334" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -39143,7 +39143,7 @@
         <v>136392745</v>
       </c>
       <c r="B335" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         <v>136392747</v>
       </c>
       <c r="B336" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -39387,7 +39387,7 @@
         <v>136392754</v>
       </c>
       <c r="B337" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -39509,7 +39509,7 @@
         <v>136392763</v>
       </c>
       <c r="B338" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -39631,7 +39631,7 @@
         <v>136393470</v>
       </c>
       <c r="B339" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -39743,7 +39743,7 @@
         <v>136393488</v>
       </c>
       <c r="B340" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -39855,7 +39855,7 @@
         <v>136393491</v>
       </c>
       <c r="B341" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -39967,7 +39967,7 @@
         <v>136393501</v>
       </c>
       <c r="B342" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -40079,7 +40079,7 @@
         <v>136393514</v>
       </c>
       <c r="B343" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -40191,7 +40191,7 @@
         <v>136393517</v>
       </c>
       <c r="B344" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -40303,7 +40303,7 @@
         <v>136393523</v>
       </c>
       <c r="B345" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -40415,7 +40415,7 @@
         <v>136396151</v>
       </c>
       <c r="B346" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>136396157</v>
       </c>
       <c r="B347" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -40639,7 +40639,7 @@
         <v>136402410</v>
       </c>
       <c r="B348" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -40751,7 +40751,7 @@
         <v>136402417</v>
       </c>
       <c r="B349" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -40863,7 +40863,7 @@
         <v>136402432</v>
       </c>
       <c r="B350" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -40975,7 +40975,7 @@
         <v>136402444</v>
       </c>
       <c r="B351" t="n">
-        <v>79218</v>
+        <v>79231</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -41199,7 +41199,7 @@
         <v>136392748</v>
       </c>
       <c r="B353" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -41321,7 +41321,7 @@
         <v>136392799</v>
       </c>
       <c r="B354" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -41443,7 +41443,7 @@
         <v>136392801</v>
       </c>
       <c r="B355" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -41565,7 +41565,7 @@
         <v>136392806</v>
       </c>
       <c r="B356" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -41687,7 +41687,7 @@
         <v>136396116</v>
       </c>
       <c r="B357" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>136402440</v>
       </c>
       <c r="B358" t="n">
-        <v>80050</v>
+        <v>80063</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -42023,7 +42023,7 @@
         <v>136392770</v>
       </c>
       <c r="B360" t="n">
-        <v>79483</v>
+        <v>79496</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -42140,7 +42140,7 @@
         <v>136392776</v>
       </c>
       <c r="B361" t="n">
-        <v>79483</v>
+        <v>79496</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>136402425</v>
       </c>
       <c r="B362" t="n">
-        <v>79483</v>
+        <v>79496</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>

--- a/artfynd/A 34765-2025 artfynd.xlsx
+++ b/artfynd/A 34765-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136402433</v>
       </c>
       <c r="B2" t="n">
-        <v>92347</v>
+        <v>92348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>136392725</v>
       </c>
       <c r="B3" t="n">
-        <v>79505</v>
+        <v>79506</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>136379790</v>
       </c>
       <c r="B4" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1028,7 +1028,7 @@
         <v>136384395</v>
       </c>
       <c r="B5" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>136392737</v>
       </c>
       <c r="B6" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1271,7 +1271,7 @@
         <v>136392768</v>
       </c>
       <c r="B7" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         <v>136392775</v>
       </c>
       <c r="B8" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1515,7 +1515,7 @@
         <v>136392792</v>
       </c>
       <c r="B9" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>136392793</v>
       </c>
       <c r="B10" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1759,7 +1759,7 @@
         <v>136396115</v>
       </c>
       <c r="B11" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>136396133</v>
       </c>
       <c r="B12" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         <v>136402411</v>
       </c>
       <c r="B13" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2095,7 +2095,7 @@
         <v>136402419</v>
       </c>
       <c r="B14" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>136402423</v>
       </c>
       <c r="B15" t="n">
-        <v>79139</v>
+        <v>79140</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2319,7 +2319,7 @@
         <v>136392821</v>
       </c>
       <c r="B16" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>136396104</v>
       </c>
       <c r="B17" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>136386035</v>
       </c>
       <c r="B18" t="n">
-        <v>93393</v>
+        <v>93394</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2679,7 +2679,7 @@
         <v>136376836</v>
       </c>
       <c r="B19" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>136380121</v>
       </c>
       <c r="B20" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>136381954</v>
       </c>
       <c r="B21" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3052,7 +3052,7 @@
         <v>136384925</v>
       </c>
       <c r="B22" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3178,7 +3178,7 @@
         <v>136386039</v>
       </c>
       <c r="B23" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3299,7 +3299,7 @@
         <v>136386054</v>
       </c>
       <c r="B24" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3420,7 +3420,7 @@
         <v>136386055</v>
       </c>
       <c r="B25" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>136386073</v>
       </c>
       <c r="B26" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3662,7 +3662,7 @@
         <v>136386075</v>
       </c>
       <c r="B27" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3783,7 +3783,7 @@
         <v>136386082</v>
       </c>
       <c r="B28" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>136386084</v>
       </c>
       <c r="B29" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>136386090</v>
       </c>
       <c r="B30" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4146,7 +4146,7 @@
         <v>136392727</v>
       </c>
       <c r="B31" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4272,7 +4272,7 @@
         <v>136392735</v>
       </c>
       <c r="B32" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4393,7 +4393,7 @@
         <v>136392741</v>
       </c>
       <c r="B33" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>136392756</v>
       </c>
       <c r="B34" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4635,7 +4635,7 @@
         <v>136392771</v>
       </c>
       <c r="B35" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4756,7 +4756,7 @@
         <v>136392794</v>
       </c>
       <c r="B36" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4882,7 +4882,7 @@
         <v>136392800</v>
       </c>
       <c r="B37" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5008,7 +5008,7 @@
         <v>136392803</v>
       </c>
       <c r="B38" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>136392811</v>
       </c>
       <c r="B39" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -5258,7 +5258,7 @@
         <v>136392812</v>
       </c>
       <c r="B40" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5382,7 +5382,7 @@
         <v>136392813</v>
       </c>
       <c r="B41" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5506,7 +5506,7 @@
         <v>136392823</v>
       </c>
       <c r="B42" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5627,7 +5627,7 @@
         <v>136392828</v>
       </c>
       <c r="B43" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>136393469</v>
       </c>
       <c r="B44" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>136396101</v>
       </c>
       <c r="B45" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>136396122</v>
       </c>
       <c r="B46" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>136396125</v>
       </c>
       <c r="B47" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -6247,7 +6247,7 @@
         <v>136396129</v>
       </c>
       <c r="B48" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         <v>136396130</v>
       </c>
       <c r="B49" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6497,7 +6497,7 @@
         <v>136396135</v>
       </c>
       <c r="B50" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6622,7 +6622,7 @@
         <v>136396148</v>
       </c>
       <c r="B51" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>136396149</v>
       </c>
       <c r="B52" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>136396152</v>
       </c>
       <c r="B53" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6968,7 +6968,7 @@
         <v>136396154</v>
       </c>
       <c r="B54" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7085,7 +7085,7 @@
         <v>136396155</v>
       </c>
       <c r="B55" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>136396156</v>
       </c>
       <c r="B56" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7319,7 +7319,7 @@
         <v>136402412</v>
       </c>
       <c r="B57" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7436,7 +7436,7 @@
         <v>136402421</v>
       </c>
       <c r="B58" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7553,7 +7553,7 @@
         <v>136402428</v>
       </c>
       <c r="B59" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7670,7 +7670,7 @@
         <v>136402429</v>
       </c>
       <c r="B60" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7787,7 +7787,7 @@
         <v>136402434</v>
       </c>
       <c r="B61" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7904,7 +7904,7 @@
         <v>136402436</v>
       </c>
       <c r="B62" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -8021,7 +8021,7 @@
         <v>136402438</v>
       </c>
       <c r="B63" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -8133,7 +8133,7 @@
         <v>136402439</v>
       </c>
       <c r="B64" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8250,7 +8250,7 @@
         <v>136402441</v>
       </c>
       <c r="B65" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8367,7 +8367,7 @@
         <v>136402442</v>
       </c>
       <c r="B66" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8484,7 +8484,7 @@
         <v>136405164</v>
       </c>
       <c r="B67" t="n">
-        <v>93399</v>
+        <v>93400</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>136402408</v>
       </c>
       <c r="B68" t="n">
-        <v>93411</v>
+        <v>93412</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>136386041</v>
       </c>
       <c r="B69" t="n">
-        <v>89313</v>
+        <v>89314</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>136386050</v>
       </c>
       <c r="B70" t="n">
-        <v>89313</v>
+        <v>89314</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         <v>136392816</v>
       </c>
       <c r="B71" t="n">
-        <v>93071</v>
+        <v>93072</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -9063,7 +9063,7 @@
         <v>136402409</v>
       </c>
       <c r="B72" t="n">
-        <v>93071</v>
+        <v>93072</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>136382713</v>
       </c>
       <c r="B75" t="n">
-        <v>92122</v>
+        <v>92123</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -9515,7 +9515,7 @@
         <v>136392764</v>
       </c>
       <c r="B76" t="n">
-        <v>92122</v>
+        <v>92123</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>136396142</v>
       </c>
       <c r="B77" t="n">
-        <v>92122</v>
+        <v>92123</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9743,7 +9743,7 @@
         <v>136396143</v>
       </c>
       <c r="B78" t="n">
-        <v>92122</v>
+        <v>92123</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>136402426</v>
       </c>
       <c r="B79" t="n">
-        <v>92122</v>
+        <v>92123</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9967,7 +9967,7 @@
         <v>136402422</v>
       </c>
       <c r="B80" t="n">
-        <v>91460</v>
+        <v>91461</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -10079,7 +10079,7 @@
         <v>136392786</v>
       </c>
       <c r="B81" t="n">
-        <v>93383</v>
+        <v>93384</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         <v>136376332</v>
       </c>
       <c r="B108" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>136376665</v>
       </c>
       <c r="B109" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>136377035</v>
       </c>
       <c r="B110" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>136382303</v>
       </c>
       <c r="B111" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13588,7 +13588,7 @@
         <v>136386037</v>
       </c>
       <c r="B112" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13705,7 +13705,7 @@
         <v>136386040</v>
       </c>
       <c r="B113" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13822,7 +13822,7 @@
         <v>136386051</v>
       </c>
       <c r="B114" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>136386056</v>
       </c>
       <c r="B115" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -14056,7 +14056,7 @@
         <v>136386057</v>
       </c>
       <c r="B116" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -14173,7 +14173,7 @@
         <v>136386058</v>
       </c>
       <c r="B117" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -14290,7 +14290,7 @@
         <v>136386059</v>
       </c>
       <c r="B118" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -14407,7 +14407,7 @@
         <v>136386060</v>
       </c>
       <c r="B119" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>136386061</v>
       </c>
       <c r="B120" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14641,7 +14641,7 @@
         <v>136386064</v>
       </c>
       <c r="B121" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>136386066</v>
       </c>
       <c r="B122" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14875,7 +14875,7 @@
         <v>136386067</v>
       </c>
       <c r="B123" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>136386070</v>
       </c>
       <c r="B124" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -15109,7 +15109,7 @@
         <v>136386071</v>
       </c>
       <c r="B125" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>136386072</v>
       </c>
       <c r="B126" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -15343,7 +15343,7 @@
         <v>136386087</v>
       </c>
       <c r="B127" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -15460,7 +15460,7 @@
         <v>136386089</v>
       </c>
       <c r="B128" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -15577,7 +15577,7 @@
         <v>136392705</v>
       </c>
       <c r="B129" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15689,7 +15689,7 @@
         <v>136392738</v>
       </c>
       <c r="B130" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>136392752</v>
       </c>
       <c r="B131" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>136392755</v>
       </c>
       <c r="B132" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -16025,7 +16025,7 @@
         <v>136392757</v>
       </c>
       <c r="B133" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -16137,7 +16137,7 @@
         <v>136392769</v>
       </c>
       <c r="B134" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>136392772</v>
       </c>
       <c r="B135" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>136392773</v>
       </c>
       <c r="B136" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -16478,7 +16478,7 @@
         <v>136392779</v>
       </c>
       <c r="B137" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -16590,7 +16590,7 @@
         <v>136392780</v>
       </c>
       <c r="B138" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16702,7 +16702,7 @@
         <v>136392790</v>
       </c>
       <c r="B139" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16814,7 +16814,7 @@
         <v>136392795</v>
       </c>
       <c r="B140" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>136392796</v>
       </c>
       <c r="B141" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>136392805</v>
       </c>
       <c r="B142" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -17150,7 +17150,7 @@
         <v>136392818</v>
       </c>
       <c r="B143" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>136392820</v>
       </c>
       <c r="B144" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17374,7 +17374,7 @@
         <v>136392827</v>
       </c>
       <c r="B145" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>136392829</v>
       </c>
       <c r="B146" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -17598,7 +17598,7 @@
         <v>136393453</v>
       </c>
       <c r="B147" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17710,7 +17710,7 @@
         <v>136393455</v>
       </c>
       <c r="B148" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17822,7 +17822,7 @@
         <v>136393456</v>
       </c>
       <c r="B149" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
         <v>136393458</v>
       </c>
       <c r="B150" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -18046,7 +18046,7 @@
         <v>136393459</v>
       </c>
       <c r="B151" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -18158,7 +18158,7 @@
         <v>136393460</v>
       </c>
       <c r="B152" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
         <v>136393461</v>
       </c>
       <c r="B153" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -18382,7 +18382,7 @@
         <v>136393462</v>
       </c>
       <c r="B154" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>136393463</v>
       </c>
       <c r="B155" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18606,7 +18606,7 @@
         <v>136393464</v>
       </c>
       <c r="B156" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18718,7 +18718,7 @@
         <v>136393465</v>
       </c>
       <c r="B157" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>136393468</v>
       </c>
       <c r="B158" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18942,7 +18942,7 @@
         <v>136393472</v>
       </c>
       <c r="B159" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -19054,7 +19054,7 @@
         <v>136393475</v>
       </c>
       <c r="B160" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -19166,7 +19166,7 @@
         <v>136393482</v>
       </c>
       <c r="B161" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -19278,7 +19278,7 @@
         <v>136393483</v>
       </c>
       <c r="B162" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -19390,7 +19390,7 @@
         <v>136393484</v>
       </c>
       <c r="B163" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -19502,7 +19502,7 @@
         <v>136393485</v>
       </c>
       <c r="B164" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19614,7 +19614,7 @@
         <v>136393489</v>
       </c>
       <c r="B165" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19726,7 +19726,7 @@
         <v>136393490</v>
       </c>
       <c r="B166" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>136393492</v>
       </c>
       <c r="B167" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19950,7 +19950,7 @@
         <v>136393493</v>
       </c>
       <c r="B168" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -20062,7 +20062,7 @@
         <v>136393496</v>
       </c>
       <c r="B169" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -20174,7 +20174,7 @@
         <v>136393497</v>
       </c>
       <c r="B170" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -20286,7 +20286,7 @@
         <v>136393498</v>
       </c>
       <c r="B171" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -20398,7 +20398,7 @@
         <v>136393500</v>
       </c>
       <c r="B172" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -20510,7 +20510,7 @@
         <v>136393503</v>
       </c>
       <c r="B173" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -20622,7 +20622,7 @@
         <v>136393505</v>
       </c>
       <c r="B174" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>136393506</v>
       </c>
       <c r="B175" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -20846,7 +20846,7 @@
         <v>136393509</v>
       </c>
       <c r="B176" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>136393512</v>
       </c>
       <c r="B177" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -21070,7 +21070,7 @@
         <v>136393515</v>
       </c>
       <c r="B178" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -21182,7 +21182,7 @@
         <v>136393518</v>
       </c>
       <c r="B179" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>136393519</v>
       </c>
       <c r="B180" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -21406,7 +21406,7 @@
         <v>136393520</v>
       </c>
       <c r="B181" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -21518,7 +21518,7 @@
         <v>136393524</v>
       </c>
       <c r="B182" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -21630,7 +21630,7 @@
         <v>136393525</v>
       </c>
       <c r="B183" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -21742,7 +21742,7 @@
         <v>136393527</v>
       </c>
       <c r="B184" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>136396107</v>
       </c>
       <c r="B185" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -21966,7 +21966,7 @@
         <v>136396109</v>
       </c>
       <c r="B186" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -22078,7 +22078,7 @@
         <v>136396112</v>
       </c>
       <c r="B187" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -22190,7 +22190,7 @@
         <v>136396113</v>
       </c>
       <c r="B188" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -22302,7 +22302,7 @@
         <v>136396118</v>
       </c>
       <c r="B189" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
         <v>136396119</v>
       </c>
       <c r="B190" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -22526,7 +22526,7 @@
         <v>136396128</v>
       </c>
       <c r="B191" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>136396132</v>
       </c>
       <c r="B192" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -22750,7 +22750,7 @@
         <v>136396136</v>
       </c>
       <c r="B193" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>136396138</v>
       </c>
       <c r="B194" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -22974,7 +22974,7 @@
         <v>136396140</v>
       </c>
       <c r="B195" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -23086,7 +23086,7 @@
         <v>136396145</v>
       </c>
       <c r="B196" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -23198,7 +23198,7 @@
         <v>136396150</v>
       </c>
       <c r="B197" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>136396159</v>
       </c>
       <c r="B198" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -23422,7 +23422,7 @@
         <v>136402413</v>
       </c>
       <c r="B199" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -23534,7 +23534,7 @@
         <v>136402430</v>
       </c>
       <c r="B200" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -23651,7 +23651,7 @@
         <v>136386074</v>
       </c>
       <c r="B201" t="n">
-        <v>79497</v>
+        <v>79498</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -23763,7 +23763,7 @@
         <v>136392732</v>
       </c>
       <c r="B202" t="n">
-        <v>78876</v>
+        <v>78877</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>136392798</v>
       </c>
       <c r="B203" t="n">
-        <v>78876</v>
+        <v>78877</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -25691,7 +25691,7 @@
         <v>136383035</v>
       </c>
       <c r="B219" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -25812,7 +25812,7 @@
         <v>136386044</v>
       </c>
       <c r="B220" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -25924,7 +25924,7 @@
         <v>136386047</v>
       </c>
       <c r="B221" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>136386053</v>
       </c>
       <c r="B222" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -26148,7 +26148,7 @@
         <v>136386062</v>
       </c>
       <c r="B223" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -26260,7 +26260,7 @@
         <v>136386069</v>
       </c>
       <c r="B224" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -26372,7 +26372,7 @@
         <v>136386077</v>
       </c>
       <c r="B225" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>136392744</v>
       </c>
       <c r="B226" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -26606,7 +26606,7 @@
         <v>136392746</v>
       </c>
       <c r="B227" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26728,7 +26728,7 @@
         <v>136393467</v>
       </c>
       <c r="B228" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>136393476</v>
       </c>
       <c r="B229" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -26952,7 +26952,7 @@
         <v>136393487</v>
       </c>
       <c r="B230" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -27064,7 +27064,7 @@
         <v>136393502</v>
       </c>
       <c r="B231" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -27176,7 +27176,7 @@
         <v>136393504</v>
       </c>
       <c r="B232" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>136393513</v>
       </c>
       <c r="B233" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -27400,7 +27400,7 @@
         <v>136393516</v>
       </c>
       <c r="B234" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -27512,7 +27512,7 @@
         <v>136393522</v>
       </c>
       <c r="B235" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -27624,7 +27624,7 @@
         <v>136396153</v>
       </c>
       <c r="B236" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -27736,7 +27736,7 @@
         <v>136402414</v>
       </c>
       <c r="B237" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -27848,7 +27848,7 @@
         <v>136402437</v>
       </c>
       <c r="B238" t="n">
-        <v>79230</v>
+        <v>79231</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>136386042</v>
       </c>
       <c r="B241" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -28296,7 +28296,7 @@
         <v>136386043</v>
       </c>
       <c r="B242" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -28408,7 +28408,7 @@
         <v>136386045</v>
       </c>
       <c r="B243" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>136386048</v>
       </c>
       <c r="B244" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -28632,7 +28632,7 @@
         <v>136386052</v>
       </c>
       <c r="B245" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -28744,7 +28744,7 @@
         <v>136386063</v>
       </c>
       <c r="B246" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>136386065</v>
       </c>
       <c r="B247" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -28968,7 +28968,7 @@
         <v>136386068</v>
       </c>
       <c r="B248" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -29080,7 +29080,7 @@
         <v>136386078</v>
       </c>
       <c r="B249" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -29192,7 +29192,7 @@
         <v>136386081</v>
       </c>
       <c r="B250" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -29304,7 +29304,7 @@
         <v>136386083</v>
       </c>
       <c r="B251" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -29416,7 +29416,7 @@
         <v>136392720</v>
       </c>
       <c r="B252" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -29528,7 +29528,7 @@
         <v>136392742</v>
       </c>
       <c r="B253" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -29640,7 +29640,7 @@
         <v>136392753</v>
       </c>
       <c r="B254" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -29762,7 +29762,7 @@
         <v>136392804</v>
       </c>
       <c r="B255" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -29884,7 +29884,7 @@
         <v>136393486</v>
       </c>
       <c r="B256" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -29996,7 +29996,7 @@
         <v>136393508</v>
       </c>
       <c r="B257" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -30108,7 +30108,7 @@
         <v>136393510</v>
       </c>
       <c r="B258" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -30220,7 +30220,7 @@
         <v>136396158</v>
       </c>
       <c r="B259" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -30332,7 +30332,7 @@
         <v>136402420</v>
       </c>
       <c r="B260" t="n">
-        <v>80092</v>
+        <v>80093</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -36978,7 +36978,7 @@
         <v>136392810</v>
       </c>
       <c r="B316" t="n">
-        <v>99258</v>
+        <v>99259</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -37090,7 +37090,7 @@
         <v>136392787</v>
       </c>
       <c r="B317" t="n">
-        <v>98209</v>
+        <v>98210</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -37211,7 +37211,7 @@
         <v>136396123</v>
       </c>
       <c r="B318" t="n">
-        <v>98209</v>
+        <v>98210</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -37323,7 +37323,7 @@
         <v>136392749</v>
       </c>
       <c r="B319" t="n">
-        <v>98203</v>
+        <v>98204</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -38779,7 +38779,7 @@
         <v>136377218</v>
       </c>
       <c r="B332" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -38900,7 +38900,7 @@
         <v>136383007</v>
       </c>
       <c r="B333" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -39021,7 +39021,7 @@
         <v>136392743</v>
       </c>
       <c r="B334" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -39143,7 +39143,7 @@
         <v>136392745</v>
       </c>
       <c r="B335" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         <v>136392747</v>
       </c>
       <c r="B336" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -39387,7 +39387,7 @@
         <v>136392754</v>
       </c>
       <c r="B337" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -39509,7 +39509,7 @@
         <v>136392763</v>
       </c>
       <c r="B338" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -39631,7 +39631,7 @@
         <v>136393470</v>
       </c>
       <c r="B339" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -39743,7 +39743,7 @@
         <v>136393488</v>
       </c>
       <c r="B340" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -39855,7 +39855,7 @@
         <v>136393491</v>
       </c>
       <c r="B341" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -39967,7 +39967,7 @@
         <v>136393501</v>
       </c>
       <c r="B342" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -40079,7 +40079,7 @@
         <v>136393514</v>
       </c>
       <c r="B343" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -40191,7 +40191,7 @@
         <v>136393517</v>
       </c>
       <c r="B344" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -40303,7 +40303,7 @@
         <v>136393523</v>
       </c>
       <c r="B345" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -40415,7 +40415,7 @@
         <v>136396151</v>
       </c>
       <c r="B346" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>136396157</v>
       </c>
       <c r="B347" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -40639,7 +40639,7 @@
         <v>136402410</v>
       </c>
       <c r="B348" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -40751,7 +40751,7 @@
         <v>136402417</v>
       </c>
       <c r="B349" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -40863,7 +40863,7 @@
         <v>136402432</v>
       </c>
       <c r="B350" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -40975,7 +40975,7 @@
         <v>136402444</v>
       </c>
       <c r="B351" t="n">
-        <v>79231</v>
+        <v>79232</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -41199,7 +41199,7 @@
         <v>136392748</v>
       </c>
       <c r="B353" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -41321,7 +41321,7 @@
         <v>136392799</v>
       </c>
       <c r="B354" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -41443,7 +41443,7 @@
         <v>136392801</v>
       </c>
       <c r="B355" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -41565,7 +41565,7 @@
         <v>136392806</v>
       </c>
       <c r="B356" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -41687,7 +41687,7 @@
         <v>136396116</v>
       </c>
       <c r="B357" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>136402440</v>
       </c>
       <c r="B358" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -42023,7 +42023,7 @@
         <v>136392770</v>
       </c>
       <c r="B360" t="n">
-        <v>79496</v>
+        <v>79497</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -42140,7 +42140,7 @@
         <v>136392776</v>
       </c>
       <c r="B361" t="n">
-        <v>79496</v>
+        <v>79497</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>136402425</v>
       </c>
       <c r="B362" t="n">
-        <v>79496</v>
+        <v>79497</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
